--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124372234</v>
+        <v>124366246</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496384</v>
+        <v>496045</v>
       </c>
       <c r="R2" t="n">
-        <v>7018864</v>
+        <v>7018931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124373102</v>
+        <v>124374413</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496574</v>
+        <v>496449</v>
       </c>
       <c r="R3" t="n">
-        <v>7018897</v>
+        <v>7018988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124372826</v>
+        <v>124368930</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496446</v>
+        <v>496185</v>
       </c>
       <c r="R4" t="n">
-        <v>7018884</v>
+        <v>7018934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,14 +952,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,6 +975,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375041</v>
+        <v>124372694</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496343</v>
+        <v>496555</v>
       </c>
       <c r="R5" t="n">
-        <v>7018997</v>
+        <v>7018901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,9 +1089,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374980</v>
+        <v>124372213</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496356</v>
+        <v>496392</v>
       </c>
       <c r="R6" t="n">
-        <v>7018988</v>
+        <v>7018866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,19 +1206,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>20:22</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374892</v>
+        <v>124372949</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496365</v>
+        <v>496504</v>
       </c>
       <c r="R7" t="n">
-        <v>7018964</v>
+        <v>7018879</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,6 +1321,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374616</v>
+        <v>124374892</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496506</v>
+        <v>496365</v>
       </c>
       <c r="R8" t="n">
-        <v>7018942</v>
+        <v>7018964</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,21 +1425,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1423,31 +1438,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1464,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124375665</v>
+        <v>124367729</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496298</v>
+        <v>496047</v>
       </c>
       <c r="R9" t="n">
-        <v>7018981</v>
+        <v>7018892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,24 +1527,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1544,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375602</v>
+        <v>124370557</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,37 +1572,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496297</v>
+        <v>496338</v>
       </c>
       <c r="R10" t="n">
-        <v>7018948</v>
+        <v>7018951</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,21 +1643,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1677,31 +1656,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124369063</v>
+        <v>124372986</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,31 +1684,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1763,13 +1717,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496203</v>
+        <v>496526</v>
       </c>
       <c r="R11" t="n">
-        <v>7018907</v>
+        <v>7018886</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,19 +1750,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,31 +1768,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1860,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124371804</v>
+        <v>124373203</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1876,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1900,13 +1824,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496319</v>
+        <v>496570</v>
       </c>
       <c r="R12" t="n">
-        <v>7018893</v>
+        <v>7018914</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,11 +1857,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1946,6 +1880,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1962,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124366461</v>
+        <v>124367848</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,51 +1933,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495944</v>
+        <v>496067</v>
       </c>
       <c r="R13" t="n">
-        <v>7018967</v>
+        <v>7018881</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2047,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,6 +2021,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2089,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124372406</v>
+        <v>124368130</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,39 +2074,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496324</v>
+        <v>496089</v>
       </c>
       <c r="R14" t="n">
-        <v>7018859</v>
+        <v>7018863</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,11 +2134,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124373142</v>
+        <v>124372203</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,44 +2176,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496560</v>
+        <v>496503</v>
       </c>
       <c r="R15" t="n">
-        <v>7018917</v>
+        <v>7018898</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,12 +2245,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,51 +2256,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124364887</v>
+        <v>124365804</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2393,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496078</v>
+        <v>496020</v>
       </c>
       <c r="R16" t="n">
-        <v>7018964</v>
+        <v>7018934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2455,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124368223</v>
+        <v>124372906</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2471,34 +2390,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496103</v>
+        <v>496496</v>
       </c>
       <c r="R17" t="n">
-        <v>7018878</v>
+        <v>7018887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,6 +2455,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2557,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124365439</v>
+        <v>124373030</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,34 +2502,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496029</v>
+        <v>496538</v>
       </c>
       <c r="R18" t="n">
-        <v>7018964</v>
+        <v>7018895</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,6 +2567,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124372906</v>
+        <v>124366461</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2671,20 +2610,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,9 +2632,14 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2704,13 +2648,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496496</v>
+        <v>495944</v>
       </c>
       <c r="R19" t="n">
-        <v>7018887</v>
+        <v>7018967</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,14 +2681,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,6 +2704,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2771,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124372169</v>
+        <v>124373902</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2783,43 +2737,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496446</v>
+        <v>496634</v>
       </c>
       <c r="R20" t="n">
-        <v>7018897</v>
+        <v>7019012</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2849,14 +2798,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,22 +2825,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124364937</v>
+        <v>124365253</v>
       </c>
       <c r="B21" t="n">
-        <v>91026</v>
+        <v>100279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,38 +2849,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496075</v>
+        <v>496029</v>
       </c>
       <c r="R21" t="n">
-        <v>7018977</v>
+        <v>7018921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,11 +2915,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2969,6 +2938,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2985,7 +2959,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124372986</v>
+        <v>124373091</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3030,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496526</v>
+        <v>496553</v>
       </c>
       <c r="R22" t="n">
-        <v>7018886</v>
+        <v>7018888</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3199,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124369981</v>
+        <v>124368504</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,21 +3189,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3239,13 +3213,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496293</v>
+        <v>496112</v>
       </c>
       <c r="R24" t="n">
-        <v>7018882</v>
+        <v>7018885</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3272,21 +3246,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3295,31 +3259,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3336,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124367729</v>
+        <v>124374980</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3352,21 +3291,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3376,10 +3315,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496047</v>
+        <v>496356</v>
       </c>
       <c r="R25" t="n">
-        <v>7018892</v>
+        <v>7018988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3409,9 +3348,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3426,22 +3375,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374769</v>
+        <v>124372245</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,37 +3403,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496465</v>
+        <v>496380</v>
       </c>
       <c r="R26" t="n">
-        <v>7018933</v>
+        <v>7018867</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,19 +3465,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>20:15</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,31 +3483,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3575,7 +3499,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124373091</v>
+        <v>124372382</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3620,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496553</v>
+        <v>496322</v>
       </c>
       <c r="R27" t="n">
-        <v>7018888</v>
+        <v>7018864</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3687,10 +3611,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375158</v>
+        <v>124365867</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>82597</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,55 +3623,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496311</v>
+        <v>496012</v>
       </c>
       <c r="R28" t="n">
-        <v>7018994</v>
+        <v>7018928</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3774,21 +3684,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3797,11 +3697,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3818,10 +3713,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365867</v>
+        <v>124365832</v>
       </c>
       <c r="B29" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3834,21 +3729,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3858,10 +3753,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496012</v>
+        <v>496020</v>
       </c>
       <c r="R29" t="n">
-        <v>7018928</v>
+        <v>7018936</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3920,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124368504</v>
+        <v>124370553</v>
       </c>
       <c r="B30" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3932,41 +3827,60 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496112</v>
+        <v>496283</v>
       </c>
       <c r="R30" t="n">
-        <v>7018885</v>
+        <v>7018896</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3993,11 +3907,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4006,6 +3935,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4022,10 +3956,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124366230</v>
+        <v>124372714</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4038,27 +3972,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4067,13 +4001,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495918</v>
+        <v>496416</v>
       </c>
       <c r="R31" t="n">
-        <v>7018928</v>
+        <v>7018877</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,24 +4034,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4128,31 +4052,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4169,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124367876</v>
+        <v>124375041</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4181,25 +4080,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4209,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496096</v>
+        <v>496343</v>
       </c>
       <c r="R32" t="n">
-        <v>7018871</v>
+        <v>7018997</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4271,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374413</v>
+        <v>124370431</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4287,21 +4186,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4311,10 +4210,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496449</v>
+        <v>496343</v>
       </c>
       <c r="R33" t="n">
-        <v>7018988</v>
+        <v>7018868</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4373,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124370553</v>
+        <v>124369222</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4385,60 +4284,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496283</v>
+        <v>496155</v>
       </c>
       <c r="R34" t="n">
-        <v>7018896</v>
+        <v>7018842</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4465,26 +4345,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4493,11 +4358,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4514,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124372196</v>
+        <v>124366230</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4530,27 +4390,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4559,10 +4419,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496444</v>
+        <v>495918</v>
       </c>
       <c r="R35" t="n">
-        <v>7018877</v>
+        <v>7018928</v>
       </c>
       <c r="S35" t="n">
         <v>8</v>
@@ -4594,7 +4454,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4604,12 +4464,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,12 +4498,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4661,10 +4521,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124373122</v>
+        <v>124367876</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4673,43 +4533,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496571</v>
+        <v>496096</v>
       </c>
       <c r="R36" t="n">
-        <v>7018892</v>
+        <v>7018871</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4742,11 +4597,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4773,10 +4623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124366502</v>
+        <v>124369981</v>
       </c>
       <c r="B37" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4785,25 +4635,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4813,13 +4663,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495918</v>
+        <v>496293</v>
       </c>
       <c r="R37" t="n">
-        <v>7018925</v>
+        <v>7018882</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4848,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4858,7 +4708,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4877,22 +4727,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4910,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124375105</v>
+        <v>124373047</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4926,37 +4776,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496343</v>
+        <v>496551</v>
       </c>
       <c r="R38" t="n">
-        <v>7018997</v>
+        <v>7018894</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4983,19 +4838,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>20:25</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5006,31 +4856,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5047,10 +4872,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124372868</v>
+        <v>124369957</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5063,39 +4888,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496485</v>
+        <v>496287</v>
       </c>
       <c r="R39" t="n">
-        <v>7018881</v>
+        <v>7018882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5128,11 +4948,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5159,10 +4974,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124368893</v>
+        <v>124375411</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5171,41 +4986,60 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496152</v>
+        <v>496320</v>
       </c>
       <c r="R40" t="n">
-        <v>7018906</v>
+        <v>7018988</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5232,11 +5066,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5245,6 +5094,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5261,10 +5115,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124366246</v>
+        <v>124373649</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5273,41 +5127,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496045</v>
+        <v>496649</v>
       </c>
       <c r="R41" t="n">
-        <v>7018931</v>
+        <v>7018995</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5334,11 +5193,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5347,6 +5216,11 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5363,7 +5237,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124365917</v>
+        <v>124368788</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5397,24 +5271,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496005</v>
+        <v>496168</v>
       </c>
       <c r="R42" t="n">
-        <v>7018959</v>
+        <v>7018906</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5441,11 +5310,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5454,6 +5333,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5470,10 +5374,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124370557</v>
+        <v>124372778</v>
       </c>
       <c r="B43" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5486,16 +5390,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5503,19 +5407,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5524,10 +5419,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496338</v>
+        <v>496426</v>
       </c>
       <c r="R43" t="n">
-        <v>7018951</v>
+        <v>7018876</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5560,6 +5455,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5586,10 +5486,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124372052</v>
+        <v>124372460</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5602,34 +5502,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496397</v>
+        <v>496311</v>
       </c>
       <c r="R44" t="n">
-        <v>7018931</v>
+        <v>7018869</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5659,19 +5564,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>19:03</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5686,22 +5586,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124370431</v>
+        <v>124365230</v>
       </c>
       <c r="B45" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5710,25 +5610,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5738,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496343</v>
+        <v>496029</v>
       </c>
       <c r="R45" t="n">
-        <v>7018868</v>
+        <v>7018962</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5800,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124365832</v>
+        <v>124365032</v>
       </c>
       <c r="B46" t="n">
-        <v>74901</v>
+        <v>96354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5816,21 +5716,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5840,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496020</v>
+        <v>496041</v>
       </c>
       <c r="R46" t="n">
-        <v>7018936</v>
+        <v>7018962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5902,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124373047</v>
+        <v>124375105</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5918,42 +5818,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496551</v>
+        <v>496343</v>
       </c>
       <c r="R47" t="n">
-        <v>7018894</v>
+        <v>7018997</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5980,14 +5875,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5998,6 +5898,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6014,7 +5939,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124373030</v>
+        <v>124372184</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6059,10 +5984,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496538</v>
+        <v>496392</v>
       </c>
       <c r="R48" t="n">
-        <v>7018895</v>
+        <v>7018873</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6126,7 +6051,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124372213</v>
+        <v>124372343</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6171,7 +6096,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496392</v>
+        <v>496345</v>
       </c>
       <c r="R49" t="n">
         <v>7018866</v>
@@ -6238,7 +6163,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375411</v>
+        <v>124375665</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6271,39 +6196,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496320</v>
+        <v>496298</v>
       </c>
       <c r="R50" t="n">
-        <v>7018988</v>
+        <v>7018981</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6332,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6342,12 +6248,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6358,28 +6264,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124371845</v>
+        <v>124369001</v>
       </c>
       <c r="B51" t="n">
         <v>91012</v>
@@ -6419,10 +6320,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496327</v>
+        <v>496205</v>
       </c>
       <c r="R51" t="n">
-        <v>7018893</v>
+        <v>7018858</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6481,10 +6382,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124365804</v>
+        <v>124373102</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6497,34 +6398,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496020</v>
+        <v>496574</v>
       </c>
       <c r="R52" t="n">
-        <v>7018934</v>
+        <v>7018897</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6557,6 +6463,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6583,10 +6494,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124373649</v>
+        <v>124372169</v>
       </c>
       <c r="B53" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6595,31 +6506,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6628,13 +6539,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496649</v>
+        <v>496446</v>
       </c>
       <c r="R53" t="n">
-        <v>7018995</v>
+        <v>7018897</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6661,19 +6572,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>19:52</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6684,11 +6590,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6705,10 +6606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124367848</v>
+        <v>124372810</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6721,34 +6622,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496067</v>
+        <v>496460</v>
       </c>
       <c r="R54" t="n">
-        <v>7018881</v>
+        <v>7018885</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6778,19 +6684,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:05</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6801,31 +6702,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6842,10 +6718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372203</v>
+        <v>124373142</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6858,34 +6734,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496503</v>
+        <v>496560</v>
       </c>
       <c r="R55" t="n">
-        <v>7018898</v>
+        <v>7018917</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6917,7 +6803,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6927,7 +6813,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6938,26 +6829,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372184</v>
+        <v>124368223</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6970,39 +6886,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496392</v>
+        <v>496103</v>
       </c>
       <c r="R56" t="n">
-        <v>7018873</v>
+        <v>7018878</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7035,11 +6946,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7066,10 +6972,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372714</v>
+        <v>124365917</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7082,27 +6988,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7111,10 +7017,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496416</v>
+        <v>496005</v>
       </c>
       <c r="R57" t="n">
-        <v>7018877</v>
+        <v>7018959</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7147,11 +7053,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7178,7 +7079,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124369001</v>
+        <v>124368893</v>
       </c>
       <c r="B58" t="n">
         <v>91012</v>
@@ -7218,10 +7119,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496205</v>
+        <v>496152</v>
       </c>
       <c r="R58" t="n">
-        <v>7018858</v>
+        <v>7018906</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7280,10 +7181,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124368930</v>
+        <v>124375158</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7292,38 +7193,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496185</v>
+        <v>496311</v>
       </c>
       <c r="R59" t="n">
-        <v>7018934</v>
+        <v>7018994</v>
       </c>
       <c r="S59" t="n">
         <v>7</v>
@@ -7355,7 +7270,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7365,7 +7280,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7380,26 +7295,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7417,10 +7312,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372245</v>
+        <v>124375602</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7433,42 +7328,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496380</v>
+        <v>496297</v>
       </c>
       <c r="R60" t="n">
-        <v>7018867</v>
+        <v>7018948</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7495,14 +7385,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7513,6 +7408,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7529,10 +7449,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372778</v>
+        <v>124371845</v>
       </c>
       <c r="B61" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7545,39 +7465,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496426</v>
+        <v>496327</v>
       </c>
       <c r="R61" t="n">
-        <v>7018876</v>
+        <v>7018893</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7610,11 +7525,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7641,10 +7551,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124368130</v>
+        <v>124366031</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7657,21 +7567,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7681,10 +7591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496089</v>
+        <v>495986</v>
       </c>
       <c r="R62" t="n">
-        <v>7018863</v>
+        <v>7018958</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7743,10 +7653,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124366031</v>
+        <v>124374769</v>
       </c>
       <c r="B63" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7759,21 +7669,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7783,13 +7693,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>495986</v>
+        <v>496465</v>
       </c>
       <c r="R63" t="n">
-        <v>7018958</v>
+        <v>7018933</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7816,11 +7726,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7829,6 +7749,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7845,10 +7790,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124370135</v>
+        <v>124372891</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7861,34 +7806,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496395</v>
+        <v>496487</v>
       </c>
       <c r="R64" t="n">
-        <v>7018910</v>
+        <v>7018890</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7921,6 +7871,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7947,10 +7902,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124365230</v>
+        <v>124369665</v>
       </c>
       <c r="B65" t="n">
-        <v>100279</v>
+        <v>91008</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7959,25 +7914,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7987,10 +7942,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496029</v>
+        <v>496219</v>
       </c>
       <c r="R65" t="n">
-        <v>7018962</v>
+        <v>7018883</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8049,10 +8004,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124365253</v>
+        <v>124372052</v>
       </c>
       <c r="B66" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8061,43 +8016,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496029</v>
+        <v>496397</v>
       </c>
       <c r="R66" t="n">
-        <v>7018921</v>
+        <v>7018931</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8129,7 +8079,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8139,7 +8089,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8150,31 +8100,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372810</v>
+        <v>124366502</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8183,46 +8128,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496460</v>
+        <v>495918</v>
       </c>
       <c r="R67" t="n">
-        <v>7018885</v>
+        <v>7018925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8249,14 +8189,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8267,6 +8212,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8283,7 +8253,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372460</v>
+        <v>124372196</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8328,13 +8298,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496311</v>
+        <v>496444</v>
       </c>
       <c r="R68" t="n">
-        <v>7018869</v>
+        <v>7018877</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8361,14 +8331,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8379,6 +8359,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8395,7 +8400,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372949</v>
+        <v>124372234</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8440,10 +8445,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496504</v>
+        <v>496384</v>
       </c>
       <c r="R69" t="n">
-        <v>7018879</v>
+        <v>7018864</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8507,7 +8512,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372291</v>
+        <v>124372868</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8543,7 +8548,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8552,10 +8557,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496371</v>
+        <v>496485</v>
       </c>
       <c r="R70" t="n">
-        <v>7018862</v>
+        <v>7018881</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8619,10 +8624,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124369665</v>
+        <v>124364937</v>
       </c>
       <c r="B71" t="n">
-        <v>91008</v>
+        <v>91026</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8635,21 +8640,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8659,10 +8664,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496219</v>
+        <v>496075</v>
       </c>
       <c r="R71" t="n">
-        <v>7018883</v>
+        <v>7018977</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8721,10 +8726,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372694</v>
+        <v>124373122</v>
       </c>
       <c r="B72" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8737,34 +8742,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496555</v>
+        <v>496571</v>
       </c>
       <c r="R72" t="n">
-        <v>7018901</v>
+        <v>7018892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8794,19 +8804,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>19:23</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8821,22 +8826,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124373902</v>
+        <v>124366868</v>
       </c>
       <c r="B73" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8845,38 +8850,62 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496634</v>
+        <v>496023</v>
       </c>
       <c r="R73" t="n">
-        <v>7019012</v>
+        <v>7018919</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8908,7 +8937,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8918,7 +8947,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8929,23 +8963,28 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372353</v>
+        <v>124372826</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -8990,10 +9029,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496338</v>
+        <v>496446</v>
       </c>
       <c r="R74" t="n">
-        <v>7018864</v>
+        <v>7018884</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9057,10 +9096,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124366868</v>
+        <v>124370135</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9073,58 +9112,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496023</v>
+        <v>496395</v>
       </c>
       <c r="R75" t="n">
-        <v>7018919</v>
+        <v>7018910</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9154,26 +9169,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9182,11 +9182,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9203,7 +9198,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124369957</v>
+        <v>124364887</v>
       </c>
       <c r="B76" t="n">
         <v>91012</v>
@@ -9243,10 +9238,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496287</v>
+        <v>496078</v>
       </c>
       <c r="R76" t="n">
-        <v>7018882</v>
+        <v>7018964</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9305,10 +9300,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124373203</v>
+        <v>124365439</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9321,21 +9316,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9345,13 +9340,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496570</v>
+        <v>496029</v>
       </c>
       <c r="R77" t="n">
-        <v>7018914</v>
+        <v>7018964</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9378,21 +9373,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9401,31 +9386,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9442,10 +9402,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372343</v>
+        <v>124371804</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9458,39 +9418,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496345</v>
+        <v>496319</v>
       </c>
       <c r="R78" t="n">
-        <v>7018866</v>
+        <v>7018893</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9523,11 +9478,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9554,10 +9504,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124376085</v>
+        <v>124369063</v>
       </c>
       <c r="B79" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9566,31 +9516,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9599,13 +9549,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496204</v>
+        <v>496203</v>
       </c>
       <c r="R79" t="n">
-        <v>7018992</v>
+        <v>7018907</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9632,14 +9582,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9650,6 +9605,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9666,10 +9646,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372382</v>
+        <v>124374616</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9682,42 +9662,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496322</v>
+        <v>496506</v>
       </c>
       <c r="R80" t="n">
-        <v>7018864</v>
+        <v>7018942</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9744,14 +9719,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9762,6 +9742,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9778,10 +9783,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124365032</v>
+        <v>124372353</v>
       </c>
       <c r="B81" t="n">
-        <v>96354</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9794,34 +9799,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496041</v>
+        <v>496338</v>
       </c>
       <c r="R81" t="n">
-        <v>7018962</v>
+        <v>7018864</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9854,6 +9864,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9880,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372891</v>
+        <v>124376085</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9925,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496487</v>
+        <v>496204</v>
       </c>
       <c r="R82" t="n">
-        <v>7018890</v>
+        <v>7018992</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9992,10 +10007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124369222</v>
+        <v>124372406</v>
       </c>
       <c r="B83" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10008,34 +10023,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496155</v>
+        <v>496324</v>
       </c>
       <c r="R83" t="n">
-        <v>7018842</v>
+        <v>7018859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10068,6 +10088,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10094,10 +10119,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124368788</v>
+        <v>124372291</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10110,37 +10135,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496168</v>
+        <v>496371</v>
       </c>
       <c r="R84" t="n">
-        <v>7018906</v>
+        <v>7018862</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10167,19 +10197,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10190,31 +10215,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124366246</v>
+        <v>124374980</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496045</v>
+        <v>496356</v>
       </c>
       <c r="R2" t="n">
-        <v>7018931</v>
+        <v>7018988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +748,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374413</v>
+        <v>124366230</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496449</v>
+        <v>495918</v>
       </c>
       <c r="R3" t="n">
-        <v>7018988</v>
+        <v>7018928</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,11 +865,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124368930</v>
+        <v>124365832</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +950,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496185</v>
+        <v>496020</v>
       </c>
       <c r="R4" t="n">
-        <v>7018934</v>
+        <v>7018936</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,21 +1007,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,31 +1020,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124372694</v>
+        <v>124369001</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496555</v>
+        <v>496205</v>
       </c>
       <c r="R5" t="n">
-        <v>7018901</v>
+        <v>7018858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1109,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,19 +1126,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124372213</v>
+        <v>124373102</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1173,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496392</v>
+        <v>496574</v>
       </c>
       <c r="R6" t="n">
-        <v>7018866</v>
+        <v>7018897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124372949</v>
+        <v>124365804</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496504</v>
+        <v>496020</v>
       </c>
       <c r="R7" t="n">
-        <v>7018879</v>
+        <v>7018934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,11 +1326,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374892</v>
+        <v>124372694</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496365</v>
+        <v>496555</v>
       </c>
       <c r="R8" t="n">
-        <v>7018964</v>
+        <v>7018901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,9 +1425,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124367729</v>
+        <v>124374616</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496047</v>
+        <v>496506</v>
       </c>
       <c r="R9" t="n">
-        <v>7018892</v>
+        <v>7018942</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,11 +1537,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1540,6 +1560,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124370557</v>
+        <v>124372986</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,16 +1617,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1589,19 +1634,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1610,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496338</v>
+        <v>496526</v>
       </c>
       <c r="R10" t="n">
-        <v>7018951</v>
+        <v>7018886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,6 +1682,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124372986</v>
+        <v>124368788</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,42 +1729,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496526</v>
+        <v>496168</v>
       </c>
       <c r="R11" t="n">
-        <v>7018886</v>
+        <v>7018906</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,14 +1786,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,6 +1809,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1784,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124373203</v>
+        <v>124372184</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,37 +1866,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496570</v>
+        <v>496392</v>
       </c>
       <c r="R12" t="n">
-        <v>7018914</v>
+        <v>7018873</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,19 +1928,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:39</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,31 +1946,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1921,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124367848</v>
+        <v>124372810</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,34 +1978,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496067</v>
+        <v>496460</v>
       </c>
       <c r="R13" t="n">
-        <v>7018881</v>
+        <v>7018885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,19 +2040,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:05</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,31 +2058,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2058,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124368130</v>
+        <v>124372778</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,34 +2090,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496089</v>
+        <v>496426</v>
       </c>
       <c r="R14" t="n">
-        <v>7018863</v>
+        <v>7018876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,6 +2155,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,10 +2186,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124372203</v>
+        <v>124372460</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,34 +2202,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496503</v>
+        <v>496311</v>
       </c>
       <c r="R15" t="n">
-        <v>7018898</v>
+        <v>7018869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,19 +2264,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:12</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,22 +2286,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124365804</v>
+        <v>124371845</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,21 +2314,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2312,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496020</v>
+        <v>496327</v>
       </c>
       <c r="R16" t="n">
-        <v>7018934</v>
+        <v>7018893</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124372906</v>
+        <v>124372245</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2419,10 +2445,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496496</v>
+        <v>496380</v>
       </c>
       <c r="R17" t="n">
-        <v>7018887</v>
+        <v>7018867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124373030</v>
+        <v>124365230</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,43 +2524,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496538</v>
+        <v>496029</v>
       </c>
       <c r="R18" t="n">
-        <v>7018895</v>
+        <v>7018962</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,11 +2588,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124366461</v>
+        <v>124366031</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,51 +2626,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495944</v>
+        <v>495986</v>
       </c>
       <c r="R19" t="n">
-        <v>7018967</v>
+        <v>7018958</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,21 +2687,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2704,11 +2700,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2725,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124373902</v>
+        <v>124369822</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,25 +2728,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496634</v>
+        <v>496245</v>
       </c>
       <c r="R20" t="n">
-        <v>7019012</v>
+        <v>7018876</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2798,19 +2789,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>19:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,22 +2806,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124365253</v>
+        <v>124370557</v>
       </c>
       <c r="B21" t="n">
-        <v>100279</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,31 +2830,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2882,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496029</v>
+        <v>496338</v>
       </c>
       <c r="R21" t="n">
-        <v>7018921</v>
+        <v>7018951</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,21 +2905,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2938,11 +2918,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2959,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124373091</v>
+        <v>124368223</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,39 +2950,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496553</v>
+        <v>496103</v>
       </c>
       <c r="R22" t="n">
-        <v>7018888</v>
+        <v>7018878</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3040,11 +3010,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369822</v>
+        <v>124367729</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,21 +3052,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3111,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496245</v>
+        <v>496047</v>
       </c>
       <c r="R23" t="n">
-        <v>7018876</v>
+        <v>7018892</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,7 +3138,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124368504</v>
+        <v>124365867</v>
       </c>
       <c r="B24" t="n">
         <v>82597</v>
@@ -3213,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496112</v>
+        <v>496012</v>
       </c>
       <c r="R24" t="n">
-        <v>7018885</v>
+        <v>7018928</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3275,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374980</v>
+        <v>124372196</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3291,37 +3256,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496356</v>
+        <v>496444</v>
       </c>
       <c r="R25" t="n">
-        <v>7018988</v>
+        <v>7018877</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3350,7 +3320,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3360,7 +3330,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,26 +3346,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124372245</v>
+        <v>124373902</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,43 +3399,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496380</v>
+        <v>496634</v>
       </c>
       <c r="R26" t="n">
-        <v>7018867</v>
+        <v>7019012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,14 +3460,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3487,22 +3487,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124372382</v>
+        <v>124370431</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3515,39 +3515,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496322</v>
+        <v>496343</v>
       </c>
       <c r="R27" t="n">
-        <v>7018864</v>
+        <v>7018868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3580,11 +3575,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365867</v>
+        <v>124369063</v>
       </c>
       <c r="B28" t="n">
-        <v>82597</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,41 +3613,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496012</v>
+        <v>496203</v>
       </c>
       <c r="R28" t="n">
-        <v>7018928</v>
+        <v>7018907</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,11 +3679,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3697,6 +3702,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3713,10 +3743,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365832</v>
+        <v>124369981</v>
       </c>
       <c r="B29" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,21 +3759,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3753,13 +3783,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496020</v>
+        <v>496293</v>
       </c>
       <c r="R29" t="n">
-        <v>7018936</v>
+        <v>7018882</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,11 +3816,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3799,6 +3839,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3815,7 +3880,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370553</v>
+        <v>124375411</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3850,7 +3915,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3874,13 +3939,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496283</v>
+        <v>496320</v>
       </c>
       <c r="R30" t="n">
-        <v>7018896</v>
+        <v>7018988</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,12 +3984,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124372714</v>
+        <v>124373203</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3972,42 +4037,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496416</v>
+        <v>496570</v>
       </c>
       <c r="R31" t="n">
-        <v>7018877</v>
+        <v>7018914</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4034,14 +4094,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4052,6 +4117,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4068,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375041</v>
+        <v>124367876</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,25 +4170,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4198,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496343</v>
+        <v>496096</v>
       </c>
       <c r="R32" t="n">
-        <v>7018997</v>
+        <v>7018871</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4170,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370431</v>
+        <v>124372826</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,34 +4276,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496343</v>
+        <v>496446</v>
       </c>
       <c r="R33" t="n">
-        <v>7018868</v>
+        <v>7018884</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4246,6 +4341,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124369222</v>
+        <v>124372213</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4288,34 +4388,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496155</v>
+        <v>496392</v>
       </c>
       <c r="R34" t="n">
-        <v>7018842</v>
+        <v>7018866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4348,6 +4453,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,10 +4484,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124366230</v>
+        <v>124373142</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,27 +4500,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4419,13 +4534,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495918</v>
+        <v>496560</v>
       </c>
       <c r="R35" t="n">
-        <v>7018928</v>
+        <v>7018917</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4454,7 +4569,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4464,12 +4579,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,12 +4613,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4521,10 +4636,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124367876</v>
+        <v>124375041</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4533,25 +4648,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4561,10 +4676,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496096</v>
+        <v>496343</v>
       </c>
       <c r="R36" t="n">
-        <v>7018871</v>
+        <v>7018997</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4623,10 +4738,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124369981</v>
+        <v>124364887</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4639,21 +4754,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4663,13 +4778,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496293</v>
+        <v>496078</v>
       </c>
       <c r="R37" t="n">
-        <v>7018882</v>
+        <v>7018964</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4696,21 +4811,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4719,31 +4824,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4760,10 +4840,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124373047</v>
+        <v>124375665</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4772,43 +4852,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496551</v>
+        <v>496298</v>
       </c>
       <c r="R38" t="n">
-        <v>7018894</v>
+        <v>7018981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4838,14 +4913,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4860,19 +4945,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124369957</v>
+        <v>124365439</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4912,10 +4997,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496287</v>
+        <v>496029</v>
       </c>
       <c r="R39" t="n">
-        <v>7018882</v>
+        <v>7018964</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4974,10 +5059,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375411</v>
+        <v>124372291</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4986,45 +5071,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5033,13 +5104,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496320</v>
+        <v>496371</v>
       </c>
       <c r="R40" t="n">
-        <v>7018988</v>
+        <v>7018862</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5066,24 +5137,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5094,11 +5155,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5115,7 +5171,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124373649</v>
+        <v>124365253</v>
       </c>
       <c r="B41" t="n">
         <v>100279</v>
@@ -5160,13 +5216,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496649</v>
+        <v>496029</v>
       </c>
       <c r="R41" t="n">
-        <v>7018995</v>
+        <v>7018921</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5195,7 +5251,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5205,7 +5261,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5237,7 +5293,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124368788</v>
+        <v>124367848</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5277,13 +5333,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496168</v>
+        <v>496067</v>
       </c>
       <c r="R42" t="n">
-        <v>7018906</v>
+        <v>7018881</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5312,7 +5368,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5322,7 +5378,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5374,7 +5430,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124372778</v>
+        <v>124372906</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5419,10 +5475,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496426</v>
+        <v>496496</v>
       </c>
       <c r="R43" t="n">
-        <v>7018876</v>
+        <v>7018887</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5486,7 +5542,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124372460</v>
+        <v>124372382</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5531,10 +5587,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496311</v>
+        <v>496322</v>
       </c>
       <c r="R44" t="n">
-        <v>7018869</v>
+        <v>7018864</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5598,10 +5654,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124365230</v>
+        <v>124372714</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,38 +5666,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496029</v>
+        <v>496416</v>
       </c>
       <c r="R45" t="n">
-        <v>7018962</v>
+        <v>7018877</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5674,6 +5735,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,10 +5766,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124365032</v>
+        <v>124366246</v>
       </c>
       <c r="B46" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5716,21 +5782,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5806,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496041</v>
+        <v>496045</v>
       </c>
       <c r="R46" t="n">
-        <v>7018962</v>
+        <v>7018931</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5802,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375105</v>
+        <v>124369222</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,21 +5884,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,13 +5908,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496343</v>
+        <v>496155</v>
       </c>
       <c r="R47" t="n">
-        <v>7018997</v>
+        <v>7018842</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5875,21 +5941,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5898,31 +5954,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5939,7 +5970,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124372184</v>
+        <v>124372169</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5984,10 +6015,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496392</v>
+        <v>496446</v>
       </c>
       <c r="R48" t="n">
-        <v>7018873</v>
+        <v>7018897</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6051,7 +6082,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124372343</v>
+        <v>124373030</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6096,10 +6127,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496345</v>
+        <v>496538</v>
       </c>
       <c r="R49" t="n">
-        <v>7018866</v>
+        <v>7018895</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6163,10 +6194,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375665</v>
+        <v>124366868</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6175,38 +6206,62 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496298</v>
+        <v>496023</v>
       </c>
       <c r="R50" t="n">
-        <v>7018981</v>
+        <v>7018919</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6293,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,12 +6303,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 50 ex på en halv kvm2</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,26 +6319,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124369001</v>
+        <v>124372052</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6296,21 +6356,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6320,10 +6380,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496205</v>
+        <v>496397</v>
       </c>
       <c r="R51" t="n">
-        <v>7018858</v>
+        <v>7018931</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6353,9 +6413,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6370,22 +6440,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124373102</v>
+        <v>124375105</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6398,42 +6468,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496574</v>
+        <v>496343</v>
       </c>
       <c r="R52" t="n">
-        <v>7018897</v>
+        <v>7018997</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6460,14 +6525,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6478,6 +6548,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6494,10 +6589,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124372169</v>
+        <v>124371804</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6510,39 +6605,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496446</v>
+        <v>496319</v>
       </c>
       <c r="R53" t="n">
-        <v>7018897</v>
+        <v>7018893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6575,11 +6665,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6606,7 +6691,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372810</v>
+        <v>124373047</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -6651,10 +6736,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496460</v>
+        <v>496551</v>
       </c>
       <c r="R54" t="n">
-        <v>7018885</v>
+        <v>7018894</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6718,7 +6803,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124373142</v>
+        <v>124372868</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -6757,21 +6842,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496560</v>
+        <v>496485</v>
       </c>
       <c r="R55" t="n">
-        <v>7018917</v>
+        <v>7018881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6801,24 +6881,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6829,31 +6899,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6870,10 +6915,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124368223</v>
+        <v>124375158</v>
       </c>
       <c r="B56" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6882,41 +6927,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496103</v>
+        <v>496311</v>
       </c>
       <c r="R56" t="n">
-        <v>7018878</v>
+        <v>7018994</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6943,11 +7002,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6956,6 +7025,11 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6972,10 +7046,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124365917</v>
+        <v>124366502</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6984,46 +7058,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496005</v>
+        <v>495918</v>
       </c>
       <c r="R57" t="n">
-        <v>7018959</v>
+        <v>7018925</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7050,11 +7119,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7063,6 +7142,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7079,7 +7183,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124368893</v>
+        <v>124368130</v>
       </c>
       <c r="B58" t="n">
         <v>91012</v>
@@ -7119,10 +7223,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496152</v>
+        <v>496089</v>
       </c>
       <c r="R58" t="n">
-        <v>7018906</v>
+        <v>7018863</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7181,10 +7285,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375158</v>
+        <v>124365917</v>
       </c>
       <c r="B59" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7193,40 +7297,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7235,13 +7330,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496311</v>
+        <v>496005</v>
       </c>
       <c r="R59" t="n">
-        <v>7018994</v>
+        <v>7018959</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7268,21 +7363,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7291,11 +7376,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7312,7 +7392,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124375602</v>
+        <v>124374769</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7352,13 +7432,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496297</v>
+        <v>496465</v>
       </c>
       <c r="R60" t="n">
-        <v>7018948</v>
+        <v>7018933</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7387,7 +7467,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7397,7 +7477,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7449,10 +7529,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124371845</v>
+        <v>124372234</v>
       </c>
       <c r="B61" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7465,34 +7545,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496327</v>
+        <v>496384</v>
       </c>
       <c r="R61" t="n">
-        <v>7018893</v>
+        <v>7018864</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7525,6 +7610,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7551,10 +7641,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124366031</v>
+        <v>124373122</v>
       </c>
       <c r="B62" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7567,34 +7657,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>495986</v>
+        <v>496571</v>
       </c>
       <c r="R62" t="n">
-        <v>7018958</v>
+        <v>7018892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7627,6 +7722,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7653,10 +7753,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124374769</v>
+        <v>124369665</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7669,21 +7769,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7693,13 +7793,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496465</v>
+        <v>496219</v>
       </c>
       <c r="R63" t="n">
-        <v>7018933</v>
+        <v>7018883</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7726,21 +7826,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7749,31 +7839,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7790,10 +7855,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372891</v>
+        <v>124374413</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7806,39 +7871,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496487</v>
+        <v>496449</v>
       </c>
       <c r="R64" t="n">
-        <v>7018890</v>
+        <v>7018988</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7871,11 +7931,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7902,10 +7957,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124369665</v>
+        <v>124376085</v>
       </c>
       <c r="B65" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7918,34 +7973,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496219</v>
+        <v>496204</v>
       </c>
       <c r="R65" t="n">
-        <v>7018883</v>
+        <v>7018992</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7978,6 +8038,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8004,10 +8069,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372052</v>
+        <v>124365032</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8020,21 +8085,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8044,10 +8109,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496397</v>
+        <v>496041</v>
       </c>
       <c r="R66" t="n">
-        <v>7018931</v>
+        <v>7018962</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8077,19 +8142,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8104,22 +8159,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124366502</v>
+        <v>124375602</v>
       </c>
       <c r="B67" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8128,25 +8183,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8156,13 +8211,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>495918</v>
+        <v>496297</v>
       </c>
       <c r="R67" t="n">
-        <v>7018925</v>
+        <v>7018948</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8191,7 +8246,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8201,7 +8256,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8220,22 +8275,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8253,10 +8308,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372196</v>
+        <v>124372203</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8269,42 +8324,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496444</v>
+        <v>496503</v>
       </c>
       <c r="R68" t="n">
-        <v>7018877</v>
+        <v>7018898</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8333,7 +8383,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8343,12 +8393,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8359,51 +8404,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372234</v>
+        <v>124368504</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8416,39 +8436,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496384</v>
+        <v>496112</v>
       </c>
       <c r="R69" t="n">
-        <v>7018864</v>
+        <v>7018885</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8481,11 +8496,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8512,10 +8522,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372868</v>
+        <v>124374892</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8528,39 +8538,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496485</v>
+        <v>496365</v>
       </c>
       <c r="R70" t="n">
-        <v>7018881</v>
+        <v>7018964</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8593,11 +8598,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8624,10 +8624,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124364937</v>
+        <v>124370553</v>
       </c>
       <c r="B71" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8636,41 +8636,60 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496075</v>
+        <v>496283</v>
       </c>
       <c r="R71" t="n">
-        <v>7018977</v>
+        <v>7018896</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8697,11 +8716,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8710,6 +8744,11 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8726,7 +8765,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373122</v>
+        <v>124373091</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8771,10 +8810,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496571</v>
+        <v>496553</v>
       </c>
       <c r="R72" t="n">
-        <v>7018892</v>
+        <v>7018888</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8838,7 +8877,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124366868</v>
+        <v>124372949</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8871,29 +8910,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8902,10 +8922,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496023</v>
+        <v>496504</v>
       </c>
       <c r="R73" t="n">
-        <v>7018919</v>
+        <v>7018879</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8935,24 +8955,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8963,11 +8973,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8984,10 +8989,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372826</v>
+        <v>124368930</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9000,42 +9005,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496446</v>
+        <v>496185</v>
       </c>
       <c r="R74" t="n">
-        <v>7018884</v>
+        <v>7018934</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9062,14 +9062,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9080,6 +9085,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9096,10 +9126,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124370135</v>
+        <v>124364937</v>
       </c>
       <c r="B75" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9112,21 +9142,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9136,10 +9166,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496395</v>
+        <v>496075</v>
       </c>
       <c r="R75" t="n">
-        <v>7018910</v>
+        <v>7018977</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9198,7 +9228,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124364887</v>
+        <v>124368893</v>
       </c>
       <c r="B76" t="n">
         <v>91012</v>
@@ -9238,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496078</v>
+        <v>496152</v>
       </c>
       <c r="R76" t="n">
-        <v>7018964</v>
+        <v>7018906</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9300,7 +9330,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124365439</v>
+        <v>124370135</v>
       </c>
       <c r="B77" t="n">
         <v>91012</v>
@@ -9340,10 +9370,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496029</v>
+        <v>496395</v>
       </c>
       <c r="R77" t="n">
-        <v>7018964</v>
+        <v>7018910</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9402,10 +9432,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124371804</v>
+        <v>124373649</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9414,41 +9444,46 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496319</v>
+        <v>496649</v>
       </c>
       <c r="R78" t="n">
-        <v>7018893</v>
+        <v>7018995</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9475,11 +9510,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9488,6 +9533,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9504,10 +9554,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124369063</v>
+        <v>124372343</v>
       </c>
       <c r="B79" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9516,31 +9566,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9549,13 +9599,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496203</v>
+        <v>496345</v>
       </c>
       <c r="R79" t="n">
-        <v>7018907</v>
+        <v>7018866</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9582,19 +9632,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9605,31 +9650,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9646,10 +9666,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124374616</v>
+        <v>124372891</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9662,37 +9682,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496506</v>
+        <v>496487</v>
       </c>
       <c r="R80" t="n">
-        <v>7018942</v>
+        <v>7018890</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9719,19 +9744,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>20:11</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9742,31 +9762,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9895,7 +9890,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124376085</v>
+        <v>124372406</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9935,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496204</v>
+        <v>496324</v>
       </c>
       <c r="R82" t="n">
-        <v>7018992</v>
+        <v>7018859</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,10 +10002,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372406</v>
+        <v>124366461</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10019,20 +10014,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10041,9 +10036,14 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496324</v>
+        <v>495944</v>
       </c>
       <c r="R83" t="n">
-        <v>7018859</v>
+        <v>7018967</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10085,14 +10085,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10103,6 +10108,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10119,10 +10129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372291</v>
+        <v>124369957</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10135,39 +10145,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496371</v>
+        <v>496287</v>
       </c>
       <c r="R84" t="n">
-        <v>7018862</v>
+        <v>7018882</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10200,11 +10205,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374980</v>
+        <v>124367876</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496356</v>
+        <v>496096</v>
       </c>
       <c r="R2" t="n">
-        <v>7018988</v>
+        <v>7018871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124366230</v>
+        <v>124373649</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495918</v>
+        <v>496649</v>
       </c>
       <c r="R3" t="n">
-        <v>7018928</v>
+        <v>7018995</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,26 +882,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124365832</v>
+        <v>124372949</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496020</v>
+        <v>496504</v>
       </c>
       <c r="R4" t="n">
-        <v>7018936</v>
+        <v>7018879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +980,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124369001</v>
+        <v>124365867</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496205</v>
+        <v>496012</v>
       </c>
       <c r="R5" t="n">
-        <v>7018858</v>
+        <v>7018928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124373102</v>
+        <v>124369222</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496574</v>
+        <v>496155</v>
       </c>
       <c r="R6" t="n">
-        <v>7018897</v>
+        <v>7018842</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124365804</v>
+        <v>124372986</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496020</v>
+        <v>496526</v>
       </c>
       <c r="R7" t="n">
-        <v>7018934</v>
+        <v>7018886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124372694</v>
+        <v>124374616</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496555</v>
+        <v>496506</v>
       </c>
       <c r="R8" t="n">
-        <v>7018901</v>
+        <v>7018942</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,26 +1423,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124374616</v>
+        <v>124375665</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496506</v>
+        <v>496298</v>
       </c>
       <c r="R9" t="n">
-        <v>7018942</v>
+        <v>7018981</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,51 +1565,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124372986</v>
+        <v>124367729</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496526</v>
+        <v>496047</v>
       </c>
       <c r="R10" t="n">
-        <v>7018886</v>
+        <v>7018892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,11 +1657,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124368788</v>
+        <v>124372245</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,37 +1699,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496168</v>
+        <v>496380</v>
       </c>
       <c r="R11" t="n">
-        <v>7018906</v>
+        <v>7018867</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,19 +1761,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,31 +1779,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1850,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124372184</v>
+        <v>124366461</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,20 +1807,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1884,9 +1829,14 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1895,13 +1845,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496392</v>
+        <v>495944</v>
       </c>
       <c r="R12" t="n">
-        <v>7018873</v>
+        <v>7018967</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,14 +1878,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,6 +1901,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1962,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124372810</v>
+        <v>124370135</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,39 +1938,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496460</v>
+        <v>496395</v>
       </c>
       <c r="R13" t="n">
-        <v>7018885</v>
+        <v>7018910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,11 +1998,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124372778</v>
+        <v>124368223</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,39 +2040,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496426</v>
+        <v>496103</v>
       </c>
       <c r="R14" t="n">
-        <v>7018876</v>
+        <v>7018878</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,11 +2100,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124372460</v>
+        <v>124365253</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,31 +2138,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496311</v>
+        <v>496029</v>
       </c>
       <c r="R15" t="n">
-        <v>7018869</v>
+        <v>7018921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,14 +2204,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,6 +2227,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2298,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124371845</v>
+        <v>124372052</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2338,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496327</v>
+        <v>496397</v>
       </c>
       <c r="R16" t="n">
-        <v>7018893</v>
+        <v>7018931</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,9 +2321,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2348,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124372245</v>
+        <v>124365917</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,27 +2376,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2445,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496380</v>
+        <v>496005</v>
       </c>
       <c r="R17" t="n">
-        <v>7018867</v>
+        <v>7018959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,11 +2441,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124365230</v>
+        <v>124368893</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496029</v>
+        <v>496152</v>
       </c>
       <c r="R18" t="n">
-        <v>7018962</v>
+        <v>7018906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124366031</v>
+        <v>124372406</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,34 +2585,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495986</v>
+        <v>496324</v>
       </c>
       <c r="R19" t="n">
-        <v>7018958</v>
+        <v>7018859</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,6 +2650,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124369822</v>
+        <v>124372234</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,34 +2697,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496245</v>
+        <v>496384</v>
       </c>
       <c r="R20" t="n">
-        <v>7018876</v>
+        <v>7018864</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,6 +2762,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370557</v>
+        <v>124366868</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,16 +2809,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2861,9 +2836,19 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2872,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496338</v>
+        <v>496023</v>
       </c>
       <c r="R21" t="n">
-        <v>7018951</v>
+        <v>7018919</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,11 +2890,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2918,6 +2918,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2934,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124368223</v>
+        <v>124372460</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,34 +2955,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496103</v>
+        <v>496311</v>
       </c>
       <c r="R22" t="n">
-        <v>7018878</v>
+        <v>7018869</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,6 +3020,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124367729</v>
+        <v>124374892</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,21 +3067,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3091,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496047</v>
+        <v>496365</v>
       </c>
       <c r="R23" t="n">
-        <v>7018892</v>
+        <v>7018964</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124365867</v>
+        <v>124375602</v>
       </c>
       <c r="B24" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3154,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3178,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496012</v>
+        <v>496297</v>
       </c>
       <c r="R24" t="n">
-        <v>7018928</v>
+        <v>7018948</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3211,11 +3226,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3224,6 +3249,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3240,10 +3290,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124372196</v>
+        <v>124370431</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3256,42 +3306,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496444</v>
+        <v>496343</v>
       </c>
       <c r="R25" t="n">
-        <v>7018877</v>
+        <v>7018868</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3318,26 +3363,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3346,31 +3376,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3387,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124373902</v>
+        <v>124365832</v>
       </c>
       <c r="B26" t="n">
-        <v>100279</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,25 +3404,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3427,10 +3432,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496634</v>
+        <v>496020</v>
       </c>
       <c r="R26" t="n">
-        <v>7019012</v>
+        <v>7018936</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,19 +3465,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>19:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3487,22 +3482,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370431</v>
+        <v>124365804</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3515,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3539,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496343</v>
+        <v>496020</v>
       </c>
       <c r="R27" t="n">
-        <v>7018868</v>
+        <v>7018934</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3601,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369063</v>
+        <v>124365230</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,42 +3612,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496203</v>
+        <v>496029</v>
       </c>
       <c r="R28" t="n">
-        <v>7018907</v>
+        <v>7018962</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3679,21 +3669,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,31 +3682,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3743,7 +3698,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124369981</v>
+        <v>124366230</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3777,16 +3732,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496293</v>
+        <v>495918</v>
       </c>
       <c r="R29" t="n">
-        <v>7018882</v>
+        <v>7018928</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -3818,7 +3778,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3828,7 +3788,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3845,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375411</v>
+        <v>124369822</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3892,60 +3857,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496320</v>
+        <v>496245</v>
       </c>
       <c r="R30" t="n">
-        <v>7018988</v>
+        <v>7018876</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3972,26 +3918,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4000,11 +3931,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4021,7 +3947,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124373203</v>
+        <v>124374769</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -4061,13 +3987,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496570</v>
+        <v>496465</v>
       </c>
       <c r="R31" t="n">
-        <v>7018914</v>
+        <v>7018933</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4096,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4106,7 +4032,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4158,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124367876</v>
+        <v>124373047</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4170,38 +4096,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496096</v>
+        <v>496551</v>
       </c>
       <c r="R32" t="n">
-        <v>7018871</v>
+        <v>7018894</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4234,6 +4165,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4196,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124372826</v>
+        <v>124370553</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4272,31 +4208,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4305,13 +4255,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496446</v>
+        <v>496283</v>
       </c>
       <c r="R33" t="n">
-        <v>7018884</v>
+        <v>7018896</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4338,14 +4288,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4356,6 +4316,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4372,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124372213</v>
+        <v>124367848</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,39 +4353,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496392</v>
+        <v>496067</v>
       </c>
       <c r="R34" t="n">
-        <v>7018866</v>
+        <v>7018881</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4450,14 +4410,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4468,6 +4433,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4484,10 +4474,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124373142</v>
+        <v>124372694</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4500,44 +4490,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496560</v>
+        <v>496555</v>
       </c>
       <c r="R35" t="n">
-        <v>7018917</v>
+        <v>7018901</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4569,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4579,12 +4559,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4595,51 +4570,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375041</v>
+        <v>124372714</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4652,34 +4602,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496343</v>
+        <v>496416</v>
       </c>
       <c r="R36" t="n">
-        <v>7018997</v>
+        <v>7018877</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4712,6 +4667,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4738,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124364887</v>
+        <v>124372291</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4754,34 +4714,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496078</v>
+        <v>496371</v>
       </c>
       <c r="R37" t="n">
-        <v>7018964</v>
+        <v>7018862</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4814,6 +4779,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4840,10 +4810,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124375665</v>
+        <v>124374980</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4852,25 +4822,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4880,10 +4850,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496298</v>
+        <v>496356</v>
       </c>
       <c r="R38" t="n">
-        <v>7018981</v>
+        <v>7018988</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4915,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4925,12 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4957,7 +4922,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124365439</v>
+        <v>124364887</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4997,7 +4962,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496029</v>
+        <v>496078</v>
       </c>
       <c r="R39" t="n">
         <v>7018964</v>
@@ -5059,10 +5024,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124372291</v>
+        <v>124375105</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5075,42 +5040,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496371</v>
+        <v>496343</v>
       </c>
       <c r="R40" t="n">
-        <v>7018862</v>
+        <v>7018997</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5137,14 +5097,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5155,6 +5120,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5171,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124365253</v>
+        <v>124370557</v>
       </c>
       <c r="B41" t="n">
-        <v>100279</v>
+        <v>56714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5183,31 +5173,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5216,10 +5215,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496029</v>
+        <v>496338</v>
       </c>
       <c r="R41" t="n">
-        <v>7018921</v>
+        <v>7018951</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5249,21 +5248,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5272,11 +5261,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5293,10 +5277,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124367848</v>
+        <v>124365439</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5309,21 +5293,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5333,10 +5317,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496067</v>
+        <v>496029</v>
       </c>
       <c r="R42" t="n">
-        <v>7018881</v>
+        <v>7018964</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5366,21 +5350,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5389,31 +5363,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5430,7 +5379,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124372906</v>
+        <v>124372891</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5475,10 +5424,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496496</v>
+        <v>496487</v>
       </c>
       <c r="R43" t="n">
-        <v>7018887</v>
+        <v>7018890</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5542,10 +5491,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124372382</v>
+        <v>124364937</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91026</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5558,39 +5507,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496322</v>
+        <v>496075</v>
       </c>
       <c r="R44" t="n">
-        <v>7018864</v>
+        <v>7018977</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5623,11 +5567,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5654,10 +5593,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124372714</v>
+        <v>124368504</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5670,39 +5609,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496416</v>
+        <v>496112</v>
       </c>
       <c r="R45" t="n">
-        <v>7018877</v>
+        <v>7018885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5735,11 +5669,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5766,7 +5695,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124366246</v>
+        <v>124374413</v>
       </c>
       <c r="B46" t="n">
         <v>91012</v>
@@ -5806,10 +5735,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496045</v>
+        <v>496449</v>
       </c>
       <c r="R46" t="n">
-        <v>7018931</v>
+        <v>7018988</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5868,10 +5797,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124369222</v>
+        <v>124366502</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,25 +5809,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5908,13 +5837,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496155</v>
+        <v>495918</v>
       </c>
       <c r="R47" t="n">
-        <v>7018842</v>
+        <v>7018925</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5941,11 +5870,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5954,6 +5893,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5970,10 +5934,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124372169</v>
+        <v>124368930</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5986,42 +5950,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496446</v>
+        <v>496185</v>
       </c>
       <c r="R48" t="n">
-        <v>7018897</v>
+        <v>7018934</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6048,14 +6007,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6066,6 +6030,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6082,10 +6071,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124373030</v>
+        <v>124373203</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6098,42 +6087,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496538</v>
+        <v>496570</v>
       </c>
       <c r="R49" t="n">
-        <v>7018895</v>
+        <v>7018914</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6160,14 +6144,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6178,6 +6167,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6194,7 +6208,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124366868</v>
+        <v>124372169</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6227,29 +6241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496023</v>
+        <v>496446</v>
       </c>
       <c r="R50" t="n">
-        <v>7018919</v>
+        <v>7018897</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,24 +6286,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6319,11 +6304,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6340,10 +6320,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124372052</v>
+        <v>124372810</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6356,34 +6336,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496397</v>
+        <v>496460</v>
       </c>
       <c r="R51" t="n">
-        <v>7018931</v>
+        <v>7018885</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6413,19 +6398,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>19:03</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6440,22 +6420,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375105</v>
+        <v>124373122</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6468,37 +6448,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496343</v>
+        <v>496571</v>
       </c>
       <c r="R52" t="n">
-        <v>7018997</v>
+        <v>7018892</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6525,19 +6510,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>20:25</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,31 +6528,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6589,10 +6544,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124371804</v>
+        <v>124372213</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6605,34 +6560,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496319</v>
+        <v>496392</v>
       </c>
       <c r="R53" t="n">
-        <v>7018893</v>
+        <v>7018866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6665,6 +6625,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6691,7 +6656,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124373047</v>
+        <v>124373142</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -6730,16 +6695,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496551</v>
+        <v>496560</v>
       </c>
       <c r="R54" t="n">
-        <v>7018894</v>
+        <v>7018917</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6769,14 +6739,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6787,6 +6767,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6803,10 +6808,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372868</v>
+        <v>124366031</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6819,39 +6824,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496485</v>
+        <v>495986</v>
       </c>
       <c r="R55" t="n">
-        <v>7018881</v>
+        <v>7018958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6884,11 +6884,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6915,10 +6910,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124375158</v>
+        <v>124368788</v>
       </c>
       <c r="B56" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6927,55 +6922,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496311</v>
+        <v>496168</v>
       </c>
       <c r="R56" t="n">
-        <v>7018994</v>
+        <v>7018906</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7004,7 +6985,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7014,7 +6995,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7029,6 +7010,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7046,10 +7047,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124366502</v>
+        <v>124373902</v>
       </c>
       <c r="B57" t="n">
-        <v>79795</v>
+        <v>100279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7062,21 +7063,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7086,13 +7087,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495918</v>
+        <v>496634</v>
       </c>
       <c r="R57" t="n">
-        <v>7018925</v>
+        <v>7019012</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7121,7 +7122,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7131,7 +7132,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7142,51 +7143,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124368130</v>
+        <v>124375158</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7195,41 +7171,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496089</v>
+        <v>496311</v>
       </c>
       <c r="R58" t="n">
-        <v>7018863</v>
+        <v>7018994</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7256,11 +7246,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7269,6 +7269,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7285,10 +7290,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124365917</v>
+        <v>124372343</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7301,27 +7306,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7330,10 +7335,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496005</v>
+        <v>496345</v>
       </c>
       <c r="R59" t="n">
-        <v>7018959</v>
+        <v>7018866</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7366,6 +7371,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7392,10 +7402,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124374769</v>
+        <v>124372778</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7408,37 +7418,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496465</v>
+        <v>496426</v>
       </c>
       <c r="R60" t="n">
-        <v>7018933</v>
+        <v>7018876</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7465,19 +7480,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>20:15</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7488,31 +7498,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7529,10 +7514,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372234</v>
+        <v>124365032</v>
       </c>
       <c r="B61" t="n">
-        <v>57513</v>
+        <v>96354</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7545,39 +7530,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496384</v>
+        <v>496041</v>
       </c>
       <c r="R61" t="n">
-        <v>7018864</v>
+        <v>7018962</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7610,11 +7590,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7641,10 +7616,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124373122</v>
+        <v>124369001</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7657,39 +7632,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496571</v>
+        <v>496205</v>
       </c>
       <c r="R62" t="n">
-        <v>7018892</v>
+        <v>7018858</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7722,11 +7692,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7753,10 +7718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124369665</v>
+        <v>124372184</v>
       </c>
       <c r="B63" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7769,34 +7734,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496219</v>
+        <v>496392</v>
       </c>
       <c r="R63" t="n">
-        <v>7018883</v>
+        <v>7018873</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7829,6 +7799,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7855,10 +7830,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124374413</v>
+        <v>124372906</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7871,34 +7846,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496449</v>
+        <v>496496</v>
       </c>
       <c r="R64" t="n">
-        <v>7018988</v>
+        <v>7018887</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7931,6 +7911,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7957,7 +7942,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124376085</v>
+        <v>124373030</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -8002,10 +7987,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496204</v>
+        <v>496538</v>
       </c>
       <c r="R65" t="n">
-        <v>7018992</v>
+        <v>7018895</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8069,10 +8054,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124365032</v>
+        <v>124372868</v>
       </c>
       <c r="B66" t="n">
-        <v>96354</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8085,34 +8070,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496041</v>
+        <v>496485</v>
       </c>
       <c r="R66" t="n">
-        <v>7018962</v>
+        <v>7018881</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8145,6 +8135,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8171,10 +8166,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375602</v>
+        <v>124372826</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8187,37 +8182,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496297</v>
+        <v>496446</v>
       </c>
       <c r="R67" t="n">
-        <v>7018948</v>
+        <v>7018884</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8244,19 +8244,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>20:43</t>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8267,31 +8262,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8308,10 +8278,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372203</v>
+        <v>124373091</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8324,34 +8294,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496503</v>
+        <v>496553</v>
       </c>
       <c r="R68" t="n">
-        <v>7018898</v>
+        <v>7018888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8381,19 +8356,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:12</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8408,22 +8378,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124368504</v>
+        <v>124369665</v>
       </c>
       <c r="B69" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8436,21 +8406,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8460,10 +8430,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496112</v>
+        <v>496219</v>
       </c>
       <c r="R69" t="n">
-        <v>7018885</v>
+        <v>7018883</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8522,7 +8492,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124374892</v>
+        <v>124375041</v>
       </c>
       <c r="B70" t="n">
         <v>91012</v>
@@ -8562,10 +8532,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496365</v>
+        <v>496343</v>
       </c>
       <c r="R70" t="n">
-        <v>7018964</v>
+        <v>7018997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8624,10 +8594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124370553</v>
+        <v>124369957</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8636,60 +8606,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496283</v>
+        <v>496287</v>
       </c>
       <c r="R71" t="n">
-        <v>7018896</v>
+        <v>7018882</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8716,26 +8667,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8744,11 +8680,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8765,10 +8696,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373091</v>
+        <v>124371804</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8781,39 +8712,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496553</v>
+        <v>496319</v>
       </c>
       <c r="R72" t="n">
-        <v>7018888</v>
+        <v>7018893</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8846,11 +8772,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8877,7 +8798,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372949</v>
+        <v>124372196</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8922,13 +8843,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496504</v>
+        <v>496444</v>
       </c>
       <c r="R73" t="n">
-        <v>7018879</v>
+        <v>7018877</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8955,14 +8876,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8973,6 +8904,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8989,10 +8945,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124368930</v>
+        <v>124373102</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9005,37 +8961,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496185</v>
+        <v>496574</v>
       </c>
       <c r="R74" t="n">
-        <v>7018934</v>
+        <v>7018897</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9062,19 +9023,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:35</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9085,31 +9041,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9126,10 +9057,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124364937</v>
+        <v>124372382</v>
       </c>
       <c r="B75" t="n">
-        <v>91026</v>
+        <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9142,34 +9073,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496075</v>
+        <v>496322</v>
       </c>
       <c r="R75" t="n">
-        <v>7018977</v>
+        <v>7018864</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9202,6 +9138,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9228,10 +9169,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124368893</v>
+        <v>124375411</v>
       </c>
       <c r="B76" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9240,41 +9181,60 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496152</v>
+        <v>496320</v>
       </c>
       <c r="R76" t="n">
-        <v>7018906</v>
+        <v>7018988</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9301,11 +9261,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9314,6 +9289,11 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9330,7 +9310,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124370135</v>
+        <v>124366246</v>
       </c>
       <c r="B77" t="n">
         <v>91012</v>
@@ -9370,10 +9350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496395</v>
+        <v>496045</v>
       </c>
       <c r="R77" t="n">
-        <v>7018910</v>
+        <v>7018931</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9432,10 +9412,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124373649</v>
+        <v>124368130</v>
       </c>
       <c r="B78" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9444,46 +9424,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496649</v>
+        <v>496089</v>
       </c>
       <c r="R78" t="n">
-        <v>7018995</v>
+        <v>7018863</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9510,21 +9485,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9533,11 +9498,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9554,10 +9514,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372343</v>
+        <v>124371845</v>
       </c>
       <c r="B79" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9570,39 +9530,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496345</v>
+        <v>496327</v>
       </c>
       <c r="R79" t="n">
-        <v>7018866</v>
+        <v>7018893</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9635,11 +9590,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9666,10 +9616,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372891</v>
+        <v>124369981</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9682,42 +9632,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496487</v>
+        <v>496293</v>
       </c>
       <c r="R80" t="n">
-        <v>7018890</v>
+        <v>7018882</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9744,14 +9689,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9762,6 +9712,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9778,10 +9753,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372353</v>
+        <v>124369063</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9790,31 +9765,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9823,13 +9798,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496338</v>
+        <v>496203</v>
       </c>
       <c r="R81" t="n">
-        <v>7018864</v>
+        <v>7018907</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9856,14 +9831,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9874,6 +9854,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9890,10 +9895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372406</v>
+        <v>124372203</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9906,39 +9911,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496324</v>
+        <v>496503</v>
       </c>
       <c r="R82" t="n">
-        <v>7018859</v>
+        <v>7018898</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9968,14 +9968,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9990,22 +9995,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124366461</v>
+        <v>124372353</v>
       </c>
       <c r="B83" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10014,20 +10019,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10036,14 +10041,9 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>495944</v>
+        <v>496338</v>
       </c>
       <c r="R83" t="n">
-        <v>7018967</v>
+        <v>7018864</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10085,19 +10085,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>16:21</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10108,11 +10103,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10129,10 +10119,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124369957</v>
+        <v>124376085</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10145,34 +10135,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496287</v>
+        <v>496204</v>
       </c>
       <c r="R84" t="n">
-        <v>7018882</v>
+        <v>7018992</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10205,6 +10200,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124367876</v>
+        <v>124373203</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496096</v>
+        <v>496570</v>
       </c>
       <c r="R2" t="n">
-        <v>7018871</v>
+        <v>7018914</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +748,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124373649</v>
+        <v>124369665</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +824,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496649</v>
+        <v>496219</v>
       </c>
       <c r="R3" t="n">
-        <v>7018995</v>
+        <v>7018883</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,21 +885,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,11 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124372949</v>
+        <v>124373047</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -944,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496504</v>
+        <v>496551</v>
       </c>
       <c r="R4" t="n">
-        <v>7018879</v>
+        <v>7018894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124365867</v>
+        <v>124376085</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496012</v>
+        <v>496204</v>
       </c>
       <c r="R5" t="n">
-        <v>7018928</v>
+        <v>7018992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,6 +1107,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124369222</v>
+        <v>124366230</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,37 +1154,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496155</v>
+        <v>495918</v>
       </c>
       <c r="R6" t="n">
-        <v>7018842</v>
+        <v>7018928</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,11 +1216,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1199,6 +1244,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1215,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124372986</v>
+        <v>124375158</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,20 +1297,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1248,10 +1318,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,13 +1339,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496526</v>
+        <v>496311</v>
       </c>
       <c r="R7" t="n">
-        <v>7018886</v>
+        <v>7018994</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,14 +1372,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,6 +1395,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1464,10 +1553,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124375665</v>
+        <v>124365804</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1565,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1593,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496298</v>
+        <v>496020</v>
       </c>
       <c r="R9" t="n">
-        <v>7018981</v>
+        <v>7018934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,24 +1626,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1643,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124367729</v>
+        <v>124368788</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1671,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,13 +1695,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496047</v>
+        <v>496168</v>
       </c>
       <c r="R10" t="n">
-        <v>7018892</v>
+        <v>7018906</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,11 +1728,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1667,6 +1751,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1683,10 +1792,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124372245</v>
+        <v>124368893</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,39 +1808,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496380</v>
+        <v>496152</v>
       </c>
       <c r="R11" t="n">
-        <v>7018867</v>
+        <v>7018906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,11 +1868,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124366461</v>
+        <v>124371845</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,51 +1906,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495944</v>
+        <v>496327</v>
       </c>
       <c r="R12" t="n">
-        <v>7018967</v>
+        <v>7018893</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,21 +1967,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1901,11 +1980,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,7 +1996,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124370135</v>
+        <v>124374892</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1962,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496395</v>
+        <v>496365</v>
       </c>
       <c r="R13" t="n">
-        <v>7018910</v>
+        <v>7018964</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,10 +2098,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124368223</v>
+        <v>124374413</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2114,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496103</v>
+        <v>496449</v>
       </c>
       <c r="R14" t="n">
-        <v>7018878</v>
+        <v>7018988</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124365253</v>
+        <v>124366868</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,31 +2212,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2171,10 +2264,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496029</v>
+        <v>496023</v>
       </c>
       <c r="R15" t="n">
-        <v>7018921</v>
+        <v>7018919</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2299,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2309,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124372052</v>
+        <v>124372714</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,34 +2362,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496397</v>
+        <v>496416</v>
       </c>
       <c r="R16" t="n">
-        <v>7018931</v>
+        <v>7018877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,19 +2424,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>19:03</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,19 +2446,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124365917</v>
+        <v>124367848</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2394,21 +2492,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496005</v>
+        <v>496067</v>
       </c>
       <c r="R17" t="n">
-        <v>7018959</v>
+        <v>7018881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,11 +2531,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2451,6 +2554,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2467,10 +2595,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124368893</v>
+        <v>124372203</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2611,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2635,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496152</v>
+        <v>496503</v>
       </c>
       <c r="R18" t="n">
-        <v>7018906</v>
+        <v>7018898</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,9 +2668,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,22 +2695,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124372406</v>
+        <v>124370557</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,16 +2723,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2602,10 +2740,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2614,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496324</v>
+        <v>496338</v>
       </c>
       <c r="R19" t="n">
-        <v>7018859</v>
+        <v>7018951</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,11 +2797,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124372234</v>
+        <v>124365032</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>96354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2697,39 +2839,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496384</v>
+        <v>496041</v>
       </c>
       <c r="R20" t="n">
-        <v>7018864</v>
+        <v>7018962</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2762,11 +2899,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,7 +2925,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124366868</v>
+        <v>124372949</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2826,29 +2958,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2857,10 +2970,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496023</v>
+        <v>496504</v>
       </c>
       <c r="R21" t="n">
-        <v>7018919</v>
+        <v>7018879</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,24 +3003,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,11 +3021,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2939,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124372460</v>
+        <v>124366461</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,20 +3049,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2973,9 +3071,14 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2984,13 +3087,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496311</v>
+        <v>495944</v>
       </c>
       <c r="R22" t="n">
-        <v>7018869</v>
+        <v>7018967</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3017,14 +3120,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,6 +3143,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3051,10 +3164,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374892</v>
+        <v>124369063</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,41 +3176,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496365</v>
+        <v>496203</v>
       </c>
       <c r="R23" t="n">
-        <v>7018964</v>
+        <v>7018907</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3124,11 +3242,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3137,6 +3265,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3153,7 +3306,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375602</v>
+        <v>124374769</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3193,13 +3346,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496297</v>
+        <v>496465</v>
       </c>
       <c r="R24" t="n">
-        <v>7018948</v>
+        <v>7018933</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3228,7 +3381,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3391,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3290,10 +3443,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370431</v>
+        <v>124373091</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,34 +3459,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496343</v>
+        <v>496553</v>
       </c>
       <c r="R25" t="n">
-        <v>7018868</v>
+        <v>7018888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3366,6 +3524,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,10 +3555,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365832</v>
+        <v>124368504</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,21 +3571,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3432,10 +3595,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496020</v>
+        <v>496112</v>
       </c>
       <c r="R26" t="n">
-        <v>7018936</v>
+        <v>7018885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3494,10 +3657,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365804</v>
+        <v>124368130</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3673,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3697,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496020</v>
+        <v>496089</v>
       </c>
       <c r="R27" t="n">
-        <v>7018934</v>
+        <v>7018863</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3759,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124365230</v>
+        <v>124372986</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,38 +3771,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496029</v>
+        <v>496526</v>
       </c>
       <c r="R28" t="n">
-        <v>7018962</v>
+        <v>7018886</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,6 +3840,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,10 +3871,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124366230</v>
+        <v>124375411</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3710,31 +3883,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3743,13 +3930,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495918</v>
+        <v>496320</v>
       </c>
       <c r="R29" t="n">
-        <v>7018928</v>
+        <v>7018988</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3778,7 +3965,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3788,12 +3975,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,26 +3995,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3845,10 +4012,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369822</v>
+        <v>124365867</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3861,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3885,10 +4052,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496245</v>
+        <v>496012</v>
       </c>
       <c r="R30" t="n">
-        <v>7018876</v>
+        <v>7018928</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,10 +4114,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124374769</v>
+        <v>124373102</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3963,37 +4130,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496465</v>
+        <v>496574</v>
       </c>
       <c r="R31" t="n">
-        <v>7018933</v>
+        <v>7018897</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4020,19 +4192,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>20:15</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4043,31 +4210,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4084,7 +4226,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124373047</v>
+        <v>124372868</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4129,10 +4271,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496551</v>
+        <v>496485</v>
       </c>
       <c r="R32" t="n">
-        <v>7018894</v>
+        <v>7018881</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4196,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370553</v>
+        <v>124369001</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4208,60 +4350,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496283</v>
+        <v>496205</v>
       </c>
       <c r="R33" t="n">
-        <v>7018896</v>
+        <v>7018858</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4288,26 +4411,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4316,11 +4424,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4337,10 +4440,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124367848</v>
+        <v>124367729</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4353,21 +4456,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496067</v>
+        <v>496047</v>
       </c>
       <c r="R34" t="n">
-        <v>7018881</v>
+        <v>7018892</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4410,21 +4513,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4433,31 +4526,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4474,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124372694</v>
+        <v>124371804</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4490,21 +4558,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4514,10 +4582,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496555</v>
+        <v>496319</v>
       </c>
       <c r="R35" t="n">
-        <v>7018901</v>
+        <v>7018893</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4547,19 +4615,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>19:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4574,19 +4632,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124372714</v>
+        <v>124372343</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4631,10 +4689,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496416</v>
+        <v>496345</v>
       </c>
       <c r="R36" t="n">
-        <v>7018877</v>
+        <v>7018866</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4698,7 +4756,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124372291</v>
+        <v>124372906</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4734,7 +4792,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4743,10 +4801,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496371</v>
+        <v>496496</v>
       </c>
       <c r="R37" t="n">
-        <v>7018862</v>
+        <v>7018887</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4810,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124374980</v>
+        <v>124370553</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4822,41 +4880,60 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496356</v>
+        <v>496283</v>
       </c>
       <c r="R38" t="n">
-        <v>7018988</v>
+        <v>7018896</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4885,7 +4962,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4895,7 +4972,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4906,26 +4988,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124364887</v>
+        <v>124372406</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4938,34 +5025,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496078</v>
+        <v>496324</v>
       </c>
       <c r="R39" t="n">
-        <v>7018964</v>
+        <v>7018859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4998,6 +5090,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5024,10 +5121,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375105</v>
+        <v>124364937</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5040,21 +5137,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5064,13 +5161,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496343</v>
+        <v>496075</v>
       </c>
       <c r="R40" t="n">
-        <v>7018997</v>
+        <v>7018977</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5097,21 +5194,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5120,31 +5207,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5161,10 +5223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124370557</v>
+        <v>124370135</v>
       </c>
       <c r="B41" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,48 +5239,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496338</v>
+        <v>496395</v>
       </c>
       <c r="R41" t="n">
-        <v>7018951</v>
+        <v>7018910</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5277,10 +5325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124365439</v>
+        <v>124372382</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5293,34 +5341,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496029</v>
+        <v>496322</v>
       </c>
       <c r="R42" t="n">
-        <v>7018964</v>
+        <v>7018864</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5353,6 +5406,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5379,10 +5437,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124372891</v>
+        <v>124375041</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5395,39 +5453,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496487</v>
+        <v>496343</v>
       </c>
       <c r="R43" t="n">
-        <v>7018890</v>
+        <v>7018997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5460,11 +5513,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5491,10 +5539,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124364937</v>
+        <v>124368223</v>
       </c>
       <c r="B44" t="n">
-        <v>91026</v>
+        <v>74901</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5507,21 +5555,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5531,10 +5579,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496075</v>
+        <v>496103</v>
       </c>
       <c r="R44" t="n">
-        <v>7018977</v>
+        <v>7018878</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5593,10 +5641,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124368504</v>
+        <v>124372891</v>
       </c>
       <c r="B45" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5609,34 +5657,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496112</v>
+        <v>496487</v>
       </c>
       <c r="R45" t="n">
-        <v>7018885</v>
+        <v>7018890</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,6 +5722,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5695,10 +5753,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124374413</v>
+        <v>124372196</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5711,37 +5769,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496449</v>
+        <v>496444</v>
       </c>
       <c r="R46" t="n">
-        <v>7018988</v>
+        <v>7018877</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5768,11 +5831,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5781,6 +5859,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5797,10 +5900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124366502</v>
+        <v>124372460</v>
       </c>
       <c r="B47" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5809,41 +5912,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495918</v>
+        <v>496311</v>
       </c>
       <c r="R47" t="n">
-        <v>7018925</v>
+        <v>7018869</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5870,19 +5978,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:23</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5893,31 +5996,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5934,10 +6012,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124368930</v>
+        <v>124365253</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5946,41 +6024,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496185</v>
+        <v>496029</v>
       </c>
       <c r="R48" t="n">
-        <v>7018934</v>
+        <v>7018921</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6009,7 +6092,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6019,7 +6102,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6034,26 +6117,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6071,10 +6134,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124373203</v>
+        <v>124372778</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6087,37 +6150,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496570</v>
+        <v>496426</v>
       </c>
       <c r="R49" t="n">
-        <v>7018914</v>
+        <v>7018876</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6144,19 +6212,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>19:39</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6167,31 +6230,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6208,7 +6246,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124372169</v>
+        <v>124373142</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6247,16 +6285,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496446</v>
+        <v>496560</v>
       </c>
       <c r="R50" t="n">
-        <v>7018897</v>
+        <v>7018917</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6286,14 +6329,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,6 +6357,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6320,10 +6398,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124372810</v>
+        <v>124373649</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6332,31 +6410,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6365,13 +6443,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496460</v>
+        <v>496649</v>
       </c>
       <c r="R51" t="n">
-        <v>7018885</v>
+        <v>7018995</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6398,14 +6476,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6416,6 +6499,11 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6432,10 +6520,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124373122</v>
+        <v>124366502</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6444,46 +6532,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496571</v>
+        <v>495918</v>
       </c>
       <c r="R52" t="n">
-        <v>7018892</v>
+        <v>7018925</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6510,14 +6593,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6528,6 +6616,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6544,10 +6657,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124372213</v>
+        <v>124369981</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6560,42 +6673,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496392</v>
+        <v>496293</v>
       </c>
       <c r="R53" t="n">
-        <v>7018866</v>
+        <v>7018882</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6622,14 +6730,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6640,6 +6753,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6656,10 +6794,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124373142</v>
+        <v>124374980</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6672,44 +6810,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496560</v>
+        <v>496356</v>
       </c>
       <c r="R54" t="n">
-        <v>7018917</v>
+        <v>7018988</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6741,7 +6869,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6751,12 +6879,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6767,51 +6890,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124366031</v>
+        <v>124372234</v>
       </c>
       <c r="B55" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6824,34 +6922,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495986</v>
+        <v>496384</v>
       </c>
       <c r="R55" t="n">
-        <v>7018958</v>
+        <v>7018864</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6884,6 +6987,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6910,10 +7018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124368788</v>
+        <v>124372291</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6926,37 +7034,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496168</v>
+        <v>496371</v>
       </c>
       <c r="R56" t="n">
-        <v>7018906</v>
+        <v>7018862</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6983,19 +7096,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7006,31 +7114,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7159,10 +7242,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375158</v>
+        <v>124372826</v>
       </c>
       <c r="B58" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7171,20 +7254,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7192,19 +7275,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7213,13 +7287,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496311</v>
+        <v>496446</v>
       </c>
       <c r="R58" t="n">
-        <v>7018994</v>
+        <v>7018884</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7246,19 +7320,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>20:28</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7269,11 +7338,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7290,10 +7354,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372343</v>
+        <v>124367876</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7302,43 +7366,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496345</v>
+        <v>496096</v>
       </c>
       <c r="R59" t="n">
-        <v>7018866</v>
+        <v>7018871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7371,11 +7430,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7402,10 +7456,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372778</v>
+        <v>124365917</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7418,27 +7472,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7447,10 +7501,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496426</v>
+        <v>496005</v>
       </c>
       <c r="R60" t="n">
-        <v>7018876</v>
+        <v>7018959</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7483,11 +7537,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7514,10 +7563,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124365032</v>
+        <v>124373030</v>
       </c>
       <c r="B61" t="n">
-        <v>96354</v>
+        <v>57513</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7530,34 +7579,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496041</v>
+        <v>496538</v>
       </c>
       <c r="R61" t="n">
-        <v>7018962</v>
+        <v>7018895</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7590,6 +7644,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7616,10 +7675,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124369001</v>
+        <v>124372213</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7632,34 +7691,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496205</v>
+        <v>496392</v>
       </c>
       <c r="R62" t="n">
-        <v>7018858</v>
+        <v>7018866</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7692,6 +7756,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7718,10 +7787,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372184</v>
+        <v>124369222</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7734,39 +7803,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496392</v>
+        <v>496155</v>
       </c>
       <c r="R63" t="n">
-        <v>7018873</v>
+        <v>7018842</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7799,11 +7863,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7830,10 +7889,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372906</v>
+        <v>124365230</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7842,43 +7901,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496496</v>
+        <v>496029</v>
       </c>
       <c r="R64" t="n">
-        <v>7018887</v>
+        <v>7018962</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7911,11 +7965,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7942,10 +7991,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124373030</v>
+        <v>124372052</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7958,39 +8007,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496538</v>
+        <v>496397</v>
       </c>
       <c r="R65" t="n">
-        <v>7018895</v>
+        <v>7018931</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8020,14 +8064,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8042,22 +8091,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372868</v>
+        <v>124375602</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8070,42 +8119,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496485</v>
+        <v>496297</v>
       </c>
       <c r="R66" t="n">
-        <v>7018881</v>
+        <v>7018948</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8132,14 +8176,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8150,6 +8199,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8166,7 +8240,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372826</v>
+        <v>124373122</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8211,10 +8285,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496446</v>
+        <v>496571</v>
       </c>
       <c r="R67" t="n">
-        <v>7018884</v>
+        <v>7018892</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8278,10 +8352,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124373091</v>
+        <v>124366031</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8294,39 +8368,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496553</v>
+        <v>495986</v>
       </c>
       <c r="R68" t="n">
-        <v>7018888</v>
+        <v>7018958</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8359,11 +8428,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8390,10 +8454,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124369665</v>
+        <v>124366246</v>
       </c>
       <c r="B69" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8406,21 +8470,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8430,10 +8494,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496219</v>
+        <v>496045</v>
       </c>
       <c r="R69" t="n">
-        <v>7018883</v>
+        <v>7018931</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8492,10 +8556,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124375041</v>
+        <v>124372245</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8508,34 +8572,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496343</v>
+        <v>496380</v>
       </c>
       <c r="R70" t="n">
-        <v>7018997</v>
+        <v>7018867</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8568,6 +8637,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8594,10 +8668,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124369957</v>
+        <v>124372169</v>
       </c>
       <c r="B71" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8610,34 +8684,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496287</v>
+        <v>496446</v>
       </c>
       <c r="R71" t="n">
-        <v>7018882</v>
+        <v>7018897</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8670,6 +8749,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8696,10 +8780,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124371804</v>
+        <v>124372810</v>
       </c>
       <c r="B72" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8712,34 +8796,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496319</v>
+        <v>496460</v>
       </c>
       <c r="R72" t="n">
-        <v>7018893</v>
+        <v>7018885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8772,6 +8861,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8798,10 +8892,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372196</v>
+        <v>124369957</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8814,42 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496444</v>
+        <v>496287</v>
       </c>
       <c r="R73" t="n">
-        <v>7018877</v>
+        <v>7018882</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8876,26 +8965,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8904,31 +8978,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8945,7 +8994,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124373102</v>
+        <v>124372184</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -8990,10 +9039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496574</v>
+        <v>496392</v>
       </c>
       <c r="R74" t="n">
-        <v>7018897</v>
+        <v>7018873</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9057,7 +9106,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372382</v>
+        <v>124372353</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9102,7 +9151,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496322</v>
+        <v>496338</v>
       </c>
       <c r="R75" t="n">
         <v>7018864</v>
@@ -9169,7 +9218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124375411</v>
+        <v>124375665</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -9202,39 +9251,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496320</v>
+        <v>496298</v>
       </c>
       <c r="R76" t="n">
-        <v>7018988</v>
+        <v>7018981</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9263,7 +9293,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9273,12 +9303,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9289,31 +9319,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124366246</v>
+        <v>124365832</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9326,21 +9351,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9350,10 +9375,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496045</v>
+        <v>496020</v>
       </c>
       <c r="R77" t="n">
-        <v>7018931</v>
+        <v>7018936</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9412,10 +9437,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124368130</v>
+        <v>124372694</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9428,21 +9453,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9452,10 +9477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496089</v>
+        <v>496555</v>
       </c>
       <c r="R78" t="n">
-        <v>7018863</v>
+        <v>7018901</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9485,9 +9510,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9502,19 +9537,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124371845</v>
+        <v>124364887</v>
       </c>
       <c r="B79" t="n">
         <v>91012</v>
@@ -9554,10 +9589,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496327</v>
+        <v>496078</v>
       </c>
       <c r="R79" t="n">
-        <v>7018893</v>
+        <v>7018964</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9616,10 +9651,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124369981</v>
+        <v>124370431</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9632,21 +9667,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9656,13 +9691,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496293</v>
+        <v>496343</v>
       </c>
       <c r="R80" t="n">
-        <v>7018882</v>
+        <v>7018868</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9689,21 +9724,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9712,31 +9737,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9753,10 +9753,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124369063</v>
+        <v>124375105</v>
       </c>
       <c r="B81" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9765,43 +9765,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496203</v>
+        <v>496343</v>
       </c>
       <c r="R81" t="n">
-        <v>7018907</v>
+        <v>7018997</v>
       </c>
       <c r="S81" t="n">
         <v>7</v>
@@ -9833,7 +9828,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9843,7 +9838,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9872,12 +9867,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9895,7 +9890,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372203</v>
+        <v>124369822</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9935,10 +9930,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496503</v>
+        <v>496245</v>
       </c>
       <c r="R82" t="n">
-        <v>7018898</v>
+        <v>7018876</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9968,19 +9963,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9995,22 +9980,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372353</v>
+        <v>124368930</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10023,42 +10008,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496338</v>
+        <v>496185</v>
       </c>
       <c r="R83" t="n">
-        <v>7018864</v>
+        <v>7018934</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10085,14 +10065,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10103,6 +10088,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10119,10 +10129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124376085</v>
+        <v>124365439</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10135,39 +10145,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496204</v>
+        <v>496029</v>
       </c>
       <c r="R84" t="n">
-        <v>7018992</v>
+        <v>7018964</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10200,11 +10205,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374616</v>
+        <v>124368893</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,21 +1432,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496506</v>
+        <v>496152</v>
       </c>
       <c r="R8" t="n">
-        <v>7018942</v>
+        <v>7018906</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,21 +1489,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1512,31 +1502,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1553,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124365804</v>
+        <v>124371845</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,21 +1534,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1593,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496020</v>
+        <v>496327</v>
       </c>
       <c r="R9" t="n">
-        <v>7018934</v>
+        <v>7018893</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124368788</v>
+        <v>124374892</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1695,13 +1660,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496168</v>
+        <v>496365</v>
       </c>
       <c r="R10" t="n">
-        <v>7018906</v>
+        <v>7018964</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,21 +1693,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1751,31 +1706,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1792,7 +1722,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124368893</v>
+        <v>124374413</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1832,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496152</v>
+        <v>496449</v>
       </c>
       <c r="R11" t="n">
-        <v>7018906</v>
+        <v>7018988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1894,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124371845</v>
+        <v>124374616</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,21 +1840,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,13 +1864,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496327</v>
+        <v>496506</v>
       </c>
       <c r="R12" t="n">
-        <v>7018893</v>
+        <v>7018942</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1967,11 +1897,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1980,6 +1920,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1996,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124374892</v>
+        <v>124365804</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,21 +1977,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2036,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496365</v>
+        <v>496020</v>
       </c>
       <c r="R13" t="n">
-        <v>7018964</v>
+        <v>7018934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2098,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374413</v>
+        <v>124368788</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,21 +2079,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2138,13 +2103,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496449</v>
+        <v>496168</v>
       </c>
       <c r="R14" t="n">
-        <v>7018988</v>
+        <v>7018906</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,11 +2136,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2184,6 +2159,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2458,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124367848</v>
+        <v>124365032</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496067</v>
+        <v>496041</v>
       </c>
       <c r="R17" t="n">
-        <v>7018881</v>
+        <v>7018962</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,21 +2531,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2554,31 +2544,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124372203</v>
+        <v>124372949</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,34 +2576,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496503</v>
+        <v>496504</v>
       </c>
       <c r="R18" t="n">
-        <v>7018898</v>
+        <v>7018879</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,19 +2638,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:12</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,12 +2660,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2823,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124365032</v>
+        <v>124366461</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>57883</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2835,41 +2800,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496041</v>
+        <v>495944</v>
       </c>
       <c r="R20" t="n">
-        <v>7018962</v>
+        <v>7018967</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2896,11 +2871,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2909,6 +2894,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2925,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124372949</v>
+        <v>124367848</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,39 +2931,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496504</v>
+        <v>496067</v>
       </c>
       <c r="R21" t="n">
-        <v>7018879</v>
+        <v>7018881</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,14 +2988,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,6 +3011,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3037,10 +3052,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124366461</v>
+        <v>124372203</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,51 +3064,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495944</v>
+        <v>496503</v>
       </c>
       <c r="R22" t="n">
-        <v>7018967</v>
+        <v>7018898</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,21 +3148,16 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124365867</v>
+        <v>124373102</v>
       </c>
       <c r="B30" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4028,34 +4028,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496012</v>
+        <v>496574</v>
       </c>
       <c r="R30" t="n">
-        <v>7018928</v>
+        <v>7018897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4088,6 +4093,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4114,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124373102</v>
+        <v>124365867</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4130,39 +4140,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496574</v>
+        <v>496012</v>
       </c>
       <c r="R31" t="n">
-        <v>7018897</v>
+        <v>7018928</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4195,11 +4200,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124370553</v>
+        <v>124364937</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4880,60 +4880,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496283</v>
+        <v>496075</v>
       </c>
       <c r="R38" t="n">
-        <v>7018896</v>
+        <v>7018977</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4960,26 +4941,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4988,11 +4954,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5009,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124372406</v>
+        <v>124370553</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5021,31 +4982,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5054,13 +5029,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496324</v>
+        <v>496283</v>
       </c>
       <c r="R39" t="n">
-        <v>7018859</v>
+        <v>7018896</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5087,14 +5062,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,6 +5090,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5121,10 +5111,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124364937</v>
+        <v>124372406</v>
       </c>
       <c r="B40" t="n">
-        <v>91026</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5137,34 +5127,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496075</v>
+        <v>496324</v>
       </c>
       <c r="R40" t="n">
-        <v>7018977</v>
+        <v>7018859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5197,6 +5192,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124373203</v>
+        <v>124374769</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496570</v>
+        <v>496465</v>
       </c>
       <c r="R2" t="n">
-        <v>7018914</v>
+        <v>7018933</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124369665</v>
+        <v>124368788</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,21 +828,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496219</v>
+        <v>496168</v>
       </c>
       <c r="R3" t="n">
-        <v>7018883</v>
+        <v>7018906</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +885,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,6 +908,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,7 +949,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124373047</v>
+        <v>124372382</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -959,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496551</v>
+        <v>496322</v>
       </c>
       <c r="R4" t="n">
-        <v>7018894</v>
+        <v>7018864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376085</v>
+        <v>124372949</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1071,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496204</v>
+        <v>496504</v>
       </c>
       <c r="R5" t="n">
-        <v>7018992</v>
+        <v>7018879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124366230</v>
+        <v>124365804</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1172,24 +1207,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495918</v>
+        <v>496020</v>
       </c>
       <c r="R6" t="n">
-        <v>7018928</v>
+        <v>7018934</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,26 +1246,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,31 +1259,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1285,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124375158</v>
+        <v>124374413</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,55 +1287,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496311</v>
+        <v>496449</v>
       </c>
       <c r="R7" t="n">
-        <v>7018994</v>
+        <v>7018988</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,21 +1348,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1395,11 +1361,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1416,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124368893</v>
+        <v>124375158</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,41 +1389,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496152</v>
+        <v>496311</v>
       </c>
       <c r="R8" t="n">
-        <v>7018906</v>
+        <v>7018994</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,11 +1464,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1502,6 +1487,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1518,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124371845</v>
+        <v>124369665</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,21 +1524,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496327</v>
+        <v>496219</v>
       </c>
       <c r="R9" t="n">
-        <v>7018893</v>
+        <v>7018883</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,7 +1610,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124374892</v>
+        <v>124366246</v>
       </c>
       <c r="B10" t="n">
         <v>91012</v>
@@ -1660,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496365</v>
+        <v>496045</v>
       </c>
       <c r="R10" t="n">
-        <v>7018964</v>
+        <v>7018931</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374413</v>
+        <v>124371804</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1762,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496449</v>
+        <v>496319</v>
       </c>
       <c r="R11" t="n">
-        <v>7018988</v>
+        <v>7018893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124374616</v>
+        <v>124372213</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,37 +1830,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496506</v>
+        <v>496392</v>
       </c>
       <c r="R12" t="n">
-        <v>7018942</v>
+        <v>7018866</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,19 +1892,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>20:11</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,31 +1910,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1961,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124365804</v>
+        <v>124368504</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496020</v>
+        <v>496112</v>
       </c>
       <c r="R13" t="n">
-        <v>7018934</v>
+        <v>7018885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124368788</v>
+        <v>124367876</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2103,13 +2068,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496168</v>
+        <v>496096</v>
       </c>
       <c r="R14" t="n">
-        <v>7018906</v>
+        <v>7018871</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,21 +2101,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2159,31 +2114,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2200,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124366868</v>
+        <v>124372868</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2233,29 +2163,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2264,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496023</v>
+        <v>496485</v>
       </c>
       <c r="R15" t="n">
-        <v>7018919</v>
+        <v>7018881</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,24 +2208,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,11 +2226,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2346,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124372714</v>
+        <v>124365230</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,43 +2254,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496416</v>
+        <v>496029</v>
       </c>
       <c r="R16" t="n">
-        <v>7018877</v>
+        <v>7018962</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,11 +2318,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124365032</v>
+        <v>124372052</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,21 +2360,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2498,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496041</v>
+        <v>496397</v>
       </c>
       <c r="R17" t="n">
-        <v>7018962</v>
+        <v>7018931</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,9 +2417,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,22 +2444,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124372949</v>
+        <v>124364887</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,39 +2472,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496504</v>
+        <v>496078</v>
       </c>
       <c r="R18" t="n">
-        <v>7018879</v>
+        <v>7018964</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,11 +2532,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2672,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370557</v>
+        <v>124370553</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,40 +2570,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2726,13 +2617,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496338</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>7018951</v>
+        <v>7018896</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2759,11 +2650,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2772,6 +2678,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2788,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124366461</v>
+        <v>124366502</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>79795</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,47 +2715,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495944</v>
+        <v>495918</v>
       </c>
       <c r="R20" t="n">
-        <v>7018967</v>
+        <v>7018925</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2873,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,6 +2799,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2915,7 +2836,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124367848</v>
+        <v>124368930</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2955,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496067</v>
+        <v>496185</v>
       </c>
       <c r="R21" t="n">
-        <v>7018881</v>
+        <v>7018934</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3029,12 +2950,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3052,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124372203</v>
+        <v>124364937</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,21 +2989,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3092,10 +3013,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496503</v>
+        <v>496075</v>
       </c>
       <c r="R22" t="n">
-        <v>7018898</v>
+        <v>7018977</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,19 +3046,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,22 +3063,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369063</v>
+        <v>124372810</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3176,31 +3087,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3209,13 +3120,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496203</v>
+        <v>496460</v>
       </c>
       <c r="R23" t="n">
-        <v>7018907</v>
+        <v>7018885</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3242,19 +3153,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,31 +3171,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3306,7 +3187,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124374769</v>
+        <v>124374616</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3346,13 +3227,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496465</v>
+        <v>496506</v>
       </c>
       <c r="R24" t="n">
-        <v>7018933</v>
+        <v>7018942</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3381,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3391,7 +3272,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3443,7 +3324,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124373091</v>
+        <v>124372460</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3488,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496553</v>
+        <v>496311</v>
       </c>
       <c r="R25" t="n">
-        <v>7018888</v>
+        <v>7018869</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3555,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124368504</v>
+        <v>124372291</v>
       </c>
       <c r="B26" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3571,34 +3452,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496112</v>
+        <v>496371</v>
       </c>
       <c r="R26" t="n">
-        <v>7018885</v>
+        <v>7018862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3631,6 +3517,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3657,10 +3548,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124368130</v>
+        <v>124375105</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3673,21 +3564,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3697,13 +3588,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496089</v>
+        <v>496343</v>
       </c>
       <c r="R27" t="n">
-        <v>7018863</v>
+        <v>7018997</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3730,11 +3621,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3743,6 +3644,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3759,10 +3685,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124372986</v>
+        <v>124370431</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3775,39 +3701,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496526</v>
+        <v>496343</v>
       </c>
       <c r="R28" t="n">
-        <v>7018886</v>
+        <v>7018868</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3840,11 +3761,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3871,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375411</v>
+        <v>124365032</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>96354</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3883,60 +3799,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496320</v>
+        <v>496041</v>
       </c>
       <c r="R29" t="n">
-        <v>7018988</v>
+        <v>7018962</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3963,26 +3860,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3991,11 +3873,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4012,10 +3889,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124373102</v>
+        <v>124375665</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4024,43 +3901,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496574</v>
+        <v>496298</v>
       </c>
       <c r="R30" t="n">
-        <v>7018897</v>
+        <v>7018981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4090,14 +3962,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4112,22 +3994,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124365867</v>
+        <v>124367848</v>
       </c>
       <c r="B31" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4140,21 +4022,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4164,10 +4046,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496012</v>
+        <v>496067</v>
       </c>
       <c r="R31" t="n">
-        <v>7018928</v>
+        <v>7018881</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4197,11 +4079,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4210,6 +4102,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4226,10 +4143,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124372868</v>
+        <v>124365832</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4242,39 +4159,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496485</v>
+        <v>496020</v>
       </c>
       <c r="R32" t="n">
-        <v>7018881</v>
+        <v>7018936</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4307,11 +4219,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124369001</v>
+        <v>124374980</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4354,21 +4261,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4378,10 +4285,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496205</v>
+        <v>496356</v>
       </c>
       <c r="R33" t="n">
-        <v>7018858</v>
+        <v>7018988</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4411,9 +4318,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4428,22 +4345,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124367729</v>
+        <v>124368130</v>
       </c>
       <c r="B34" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4456,21 +4373,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4480,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496047</v>
+        <v>496089</v>
       </c>
       <c r="R34" t="n">
-        <v>7018892</v>
+        <v>7018863</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124371804</v>
+        <v>124366868</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4558,34 +4475,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496319</v>
+        <v>496023</v>
       </c>
       <c r="R35" t="n">
-        <v>7018893</v>
+        <v>7018919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4615,11 +4556,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4628,6 +4584,11 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4644,7 +4605,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124372343</v>
+        <v>124372826</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4689,10 +4650,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496345</v>
+        <v>496446</v>
       </c>
       <c r="R36" t="n">
-        <v>7018866</v>
+        <v>7018884</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4756,7 +4717,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124372906</v>
+        <v>124372986</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4801,10 +4762,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496496</v>
+        <v>496526</v>
       </c>
       <c r="R37" t="n">
-        <v>7018887</v>
+        <v>7018886</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4829,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124364937</v>
+        <v>124374892</v>
       </c>
       <c r="B38" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4845,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4869,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496075</v>
+        <v>496365</v>
       </c>
       <c r="R38" t="n">
-        <v>7018977</v>
+        <v>7018964</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4931,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124370553</v>
+        <v>124372169</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4982,45 +4943,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5029,13 +4976,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496283</v>
+        <v>496446</v>
       </c>
       <c r="R39" t="n">
-        <v>7018896</v>
+        <v>7018897</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5062,24 +5009,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5090,11 +5027,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5111,10 +5043,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124372406</v>
+        <v>124373203</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5127,42 +5059,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496324</v>
+        <v>496570</v>
       </c>
       <c r="R40" t="n">
-        <v>7018859</v>
+        <v>7018914</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,14 +5116,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5207,6 +5139,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5223,10 +5180,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124370135</v>
+        <v>124372203</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5239,21 +5196,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5263,10 +5220,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496395</v>
+        <v>496503</v>
       </c>
       <c r="R41" t="n">
-        <v>7018910</v>
+        <v>7018898</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5296,9 +5253,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5313,22 +5280,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124372382</v>
+        <v>124366031</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5341,39 +5308,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496322</v>
+        <v>495986</v>
       </c>
       <c r="R42" t="n">
-        <v>7018864</v>
+        <v>7018958</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5406,11 +5368,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5437,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375041</v>
+        <v>124370557</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5453,34 +5410,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496343</v>
+        <v>496338</v>
       </c>
       <c r="R43" t="n">
-        <v>7018997</v>
+        <v>7018951</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5539,10 +5510,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124368223</v>
+        <v>124375411</v>
       </c>
       <c r="B44" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5551,41 +5522,60 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496103</v>
+        <v>496320</v>
       </c>
       <c r="R44" t="n">
-        <v>7018878</v>
+        <v>7018988</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5612,11 +5602,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5625,6 +5630,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5641,7 +5651,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124372891</v>
+        <v>124372778</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5686,10 +5696,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496487</v>
+        <v>496426</v>
       </c>
       <c r="R45" t="n">
-        <v>7018890</v>
+        <v>7018876</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5753,7 +5763,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124372196</v>
+        <v>124372714</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5798,13 +5808,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496444</v>
+        <v>496416</v>
       </c>
       <c r="R46" t="n">
         <v>7018877</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5831,24 +5841,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5859,31 +5859,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5900,10 +5875,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124372460</v>
+        <v>124367729</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5916,39 +5891,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496311</v>
+        <v>496047</v>
       </c>
       <c r="R47" t="n">
-        <v>7018869</v>
+        <v>7018892</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5981,11 +5951,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6012,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124365253</v>
+        <v>124365867</v>
       </c>
       <c r="B48" t="n">
-        <v>100279</v>
+        <v>82597</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6024,43 +5989,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496029</v>
+        <v>496012</v>
       </c>
       <c r="R48" t="n">
-        <v>7018921</v>
+        <v>7018928</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6090,21 +6050,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6113,11 +6063,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6134,10 +6079,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124372778</v>
+        <v>124369222</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6150,39 +6095,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496426</v>
+        <v>496155</v>
       </c>
       <c r="R49" t="n">
-        <v>7018876</v>
+        <v>7018842</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6215,11 +6155,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6246,10 +6181,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124373142</v>
+        <v>124365917</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6262,32 +6197,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6296,10 +6226,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496560</v>
+        <v>496005</v>
       </c>
       <c r="R50" t="n">
-        <v>7018917</v>
+        <v>7018959</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6329,26 +6259,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6357,31 +6272,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6398,10 +6288,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124373649</v>
+        <v>124365439</v>
       </c>
       <c r="B51" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6410,46 +6300,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496649</v>
+        <v>496029</v>
       </c>
       <c r="R51" t="n">
-        <v>7018995</v>
+        <v>7018964</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6476,21 +6361,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6499,11 +6374,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6520,10 +6390,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124366502</v>
+        <v>124373030</v>
       </c>
       <c r="B52" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6532,41 +6402,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495918</v>
+        <v>496538</v>
       </c>
       <c r="R52" t="n">
-        <v>7018925</v>
+        <v>7018895</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6593,19 +6468,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:23</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6616,31 +6486,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6657,10 +6502,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124369981</v>
+        <v>124372196</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6673,34 +6518,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496293</v>
+        <v>496444</v>
       </c>
       <c r="R53" t="n">
-        <v>7018882</v>
+        <v>7018877</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6732,7 +6582,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6742,7 +6592,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6771,12 +6626,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6794,10 +6649,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374980</v>
+        <v>124372406</v>
       </c>
       <c r="B54" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6810,34 +6665,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496356</v>
+        <v>496324</v>
       </c>
       <c r="R54" t="n">
-        <v>7018988</v>
+        <v>7018859</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6867,19 +6727,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>20:22</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6894,22 +6749,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124372234</v>
+        <v>124366461</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6918,20 +6773,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6940,9 +6795,14 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6951,13 +6811,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496384</v>
+        <v>495944</v>
       </c>
       <c r="R55" t="n">
-        <v>7018864</v>
+        <v>7018967</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6984,14 +6844,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7002,6 +6867,11 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7018,10 +6888,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372291</v>
+        <v>124369001</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7034,39 +6904,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496371</v>
+        <v>496205</v>
       </c>
       <c r="R56" t="n">
-        <v>7018862</v>
+        <v>7018858</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7099,11 +6964,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7130,10 +6990,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124373902</v>
+        <v>124369063</v>
       </c>
       <c r="B57" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7146,37 +7006,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496634</v>
+        <v>496203</v>
       </c>
       <c r="R57" t="n">
-        <v>7019012</v>
+        <v>7018907</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7205,7 +7070,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7215,7 +7080,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7226,26 +7091,51 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372826</v>
+        <v>124366230</v>
       </c>
       <c r="B58" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7258,27 +7148,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7287,13 +7177,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496446</v>
+        <v>495918</v>
       </c>
       <c r="R58" t="n">
-        <v>7018884</v>
+        <v>7018928</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7320,14 +7210,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7338,6 +7238,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7354,10 +7279,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124367876</v>
+        <v>124372343</v>
       </c>
       <c r="B59" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7366,38 +7291,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496096</v>
+        <v>496345</v>
       </c>
       <c r="R59" t="n">
-        <v>7018871</v>
+        <v>7018866</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7430,6 +7360,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7456,10 +7391,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124365917</v>
+        <v>124372906</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7472,27 +7407,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7501,10 +7436,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496005</v>
+        <v>496496</v>
       </c>
       <c r="R60" t="n">
-        <v>7018959</v>
+        <v>7018887</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7537,6 +7472,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7563,7 +7503,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373030</v>
+        <v>124373091</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7608,10 +7548,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496538</v>
+        <v>496553</v>
       </c>
       <c r="R61" t="n">
-        <v>7018895</v>
+        <v>7018888</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7675,7 +7615,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372213</v>
+        <v>124372234</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7720,10 +7660,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496392</v>
+        <v>496384</v>
       </c>
       <c r="R62" t="n">
-        <v>7018866</v>
+        <v>7018864</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7787,10 +7727,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124369222</v>
+        <v>124368223</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7803,21 +7743,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7827,10 +7767,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496155</v>
+        <v>496103</v>
       </c>
       <c r="R63" t="n">
-        <v>7018842</v>
+        <v>7018878</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7889,10 +7829,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124365230</v>
+        <v>124372694</v>
       </c>
       <c r="B64" t="n">
-        <v>100279</v>
+        <v>74901</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7901,25 +7841,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7929,10 +7869,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496029</v>
+        <v>496555</v>
       </c>
       <c r="R64" t="n">
-        <v>7018962</v>
+        <v>7018901</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7962,9 +7902,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7979,22 +7929,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372052</v>
+        <v>124372184</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8007,34 +7957,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496397</v>
+        <v>496392</v>
       </c>
       <c r="R65" t="n">
-        <v>7018931</v>
+        <v>7018873</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8064,19 +8019,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>19:03</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8091,22 +8041,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124375602</v>
+        <v>124372891</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8119,37 +8069,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496297</v>
+        <v>496487</v>
       </c>
       <c r="R66" t="n">
-        <v>7018948</v>
+        <v>7018890</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8176,19 +8131,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>20:43</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8199,31 +8149,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8240,7 +8165,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124373122</v>
+        <v>124372245</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8285,10 +8210,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496571</v>
+        <v>496380</v>
       </c>
       <c r="R67" t="n">
-        <v>7018892</v>
+        <v>7018867</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8352,10 +8277,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124366031</v>
+        <v>124376085</v>
       </c>
       <c r="B68" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8368,34 +8293,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>495986</v>
+        <v>496204</v>
       </c>
       <c r="R68" t="n">
-        <v>7018958</v>
+        <v>7018992</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8428,6 +8358,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8454,10 +8389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124366246</v>
+        <v>124373122</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8470,34 +8405,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496045</v>
+        <v>496571</v>
       </c>
       <c r="R69" t="n">
-        <v>7018931</v>
+        <v>7018892</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8530,6 +8470,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8556,10 +8501,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372245</v>
+        <v>124369957</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8572,39 +8517,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496380</v>
+        <v>496287</v>
       </c>
       <c r="R70" t="n">
-        <v>7018867</v>
+        <v>7018882</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8637,11 +8577,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8668,7 +8603,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372169</v>
+        <v>124373047</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8713,10 +8648,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496446</v>
+        <v>496551</v>
       </c>
       <c r="R71" t="n">
-        <v>7018897</v>
+        <v>7018894</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8780,10 +8715,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372810</v>
+        <v>124373649</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8792,31 +8727,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8825,13 +8760,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496460</v>
+        <v>496649</v>
       </c>
       <c r="R72" t="n">
-        <v>7018885</v>
+        <v>7018995</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8858,14 +8793,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8876,6 +8816,11 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8892,10 +8837,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124369957</v>
+        <v>124373902</v>
       </c>
       <c r="B73" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8904,25 +8849,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8932,10 +8877,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496287</v>
+        <v>496634</v>
       </c>
       <c r="R73" t="n">
-        <v>7018882</v>
+        <v>7019012</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8965,9 +8910,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8982,22 +8937,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372184</v>
+        <v>124368893</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9010,39 +8965,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496392</v>
+        <v>496152</v>
       </c>
       <c r="R74" t="n">
-        <v>7018873</v>
+        <v>7018906</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9025,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372353</v>
+        <v>124369981</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9122,42 +9067,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496338</v>
+        <v>496293</v>
       </c>
       <c r="R75" t="n">
-        <v>7018864</v>
+        <v>7018882</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9184,14 +9124,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9202,6 +9147,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9218,10 +9188,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124375665</v>
+        <v>124365253</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9230,38 +9200,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496298</v>
+        <v>496029</v>
       </c>
       <c r="R76" t="n">
-        <v>7018981</v>
+        <v>7018921</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9293,7 +9268,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9303,12 +9278,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9319,26 +9289,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124365832</v>
+        <v>124370135</v>
       </c>
       <c r="B77" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9351,21 +9326,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9375,10 +9350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496020</v>
+        <v>496395</v>
       </c>
       <c r="R77" t="n">
-        <v>7018936</v>
+        <v>7018910</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9437,10 +9412,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372694</v>
+        <v>124371845</v>
       </c>
       <c r="B78" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9453,21 +9428,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9477,10 +9452,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496555</v>
+        <v>496327</v>
       </c>
       <c r="R78" t="n">
-        <v>7018901</v>
+        <v>7018893</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9510,19 +9485,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>19:23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9537,22 +9502,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124364887</v>
+        <v>124372353</v>
       </c>
       <c r="B79" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9565,34 +9530,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496078</v>
+        <v>496338</v>
       </c>
       <c r="R79" t="n">
-        <v>7018964</v>
+        <v>7018864</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9625,6 +9595,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9651,10 +9626,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124370431</v>
+        <v>124373102</v>
       </c>
       <c r="B80" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9667,34 +9642,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496343</v>
+        <v>496574</v>
       </c>
       <c r="R80" t="n">
-        <v>7018868</v>
+        <v>7018897</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9727,6 +9707,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9753,10 +9738,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124375105</v>
+        <v>124373142</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9769,37 +9754,47 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496343</v>
+        <v>496560</v>
       </c>
       <c r="R81" t="n">
-        <v>7018997</v>
+        <v>7018917</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9828,7 +9823,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9838,7 +9833,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9890,10 +9890,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124369822</v>
+        <v>124375041</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496245</v>
+        <v>496343</v>
       </c>
       <c r="R82" t="n">
-        <v>7018876</v>
+        <v>7018997</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124368930</v>
+        <v>124369822</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -10032,13 +10032,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496185</v>
+        <v>496245</v>
       </c>
       <c r="R83" t="n">
-        <v>7018934</v>
+        <v>7018876</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10065,21 +10065,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10088,31 +10078,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10129,10 +10094,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124365439</v>
+        <v>124375602</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10145,21 +10110,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10169,13 +10134,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496029</v>
+        <v>496297</v>
       </c>
       <c r="R84" t="n">
-        <v>7018964</v>
+        <v>7018948</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10202,11 +10167,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10215,6 +10190,31 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -3324,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124372460</v>
+        <v>124375105</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3340,42 +3340,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496311</v>
+        <v>496343</v>
       </c>
       <c r="R25" t="n">
-        <v>7018869</v>
+        <v>7018997</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3402,14 +3397,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,6 +3420,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3436,10 +3461,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124372291</v>
+        <v>124370431</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,39 +3477,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496371</v>
+        <v>496343</v>
       </c>
       <c r="R26" t="n">
-        <v>7018862</v>
+        <v>7018868</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,11 +3537,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3548,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375105</v>
+        <v>124372460</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,37 +3579,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496343</v>
+        <v>496311</v>
       </c>
       <c r="R27" t="n">
-        <v>7018997</v>
+        <v>7018869</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3621,19 +3641,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>20:25</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,31 +3659,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3685,10 +3675,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370431</v>
+        <v>124372291</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,34 +3691,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496343</v>
+        <v>496371</v>
       </c>
       <c r="R28" t="n">
-        <v>7018868</v>
+        <v>7018862</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,6 +3756,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -6888,10 +6888,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124369001</v>
+        <v>124372343</v>
       </c>
       <c r="B56" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6904,34 +6904,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496205</v>
+        <v>496345</v>
       </c>
       <c r="R56" t="n">
-        <v>7018858</v>
+        <v>7018866</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6964,6 +6969,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6990,10 +7000,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124369063</v>
+        <v>124366230</v>
       </c>
       <c r="B57" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7002,31 +7012,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7035,13 +7045,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496203</v>
+        <v>495918</v>
       </c>
       <c r="R57" t="n">
-        <v>7018907</v>
+        <v>7018928</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7070,7 +7080,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7080,7 +7090,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7109,12 +7124,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7132,10 +7147,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124366230</v>
+        <v>124369001</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7148,42 +7163,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495918</v>
+        <v>496205</v>
       </c>
       <c r="R58" t="n">
-        <v>7018928</v>
+        <v>7018858</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7210,26 +7220,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7238,31 +7233,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7279,10 +7249,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372343</v>
+        <v>124369063</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7291,31 +7261,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7324,13 +7294,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496345</v>
+        <v>496203</v>
       </c>
       <c r="R59" t="n">
-        <v>7018866</v>
+        <v>7018907</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7357,14 +7327,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7375,6 +7350,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7727,10 +7727,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124368223</v>
+        <v>124372184</v>
       </c>
       <c r="B63" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7743,34 +7743,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496103</v>
+        <v>496392</v>
       </c>
       <c r="R63" t="n">
-        <v>7018878</v>
+        <v>7018873</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,6 +7808,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7829,10 +7839,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372694</v>
+        <v>124372891</v>
       </c>
       <c r="B64" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7845,34 +7855,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496555</v>
+        <v>496487</v>
       </c>
       <c r="R64" t="n">
-        <v>7018901</v>
+        <v>7018890</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7902,19 +7917,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>19:23</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7929,19 +7939,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372184</v>
+        <v>124372245</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7986,10 +7996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496392</v>
+        <v>496380</v>
       </c>
       <c r="R65" t="n">
-        <v>7018873</v>
+        <v>7018867</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8053,7 +8063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372891</v>
+        <v>124376085</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8098,10 +8108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496487</v>
+        <v>496204</v>
       </c>
       <c r="R66" t="n">
-        <v>7018890</v>
+        <v>7018992</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8165,7 +8175,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372245</v>
+        <v>124373122</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8210,10 +8220,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496380</v>
+        <v>496571</v>
       </c>
       <c r="R67" t="n">
-        <v>7018867</v>
+        <v>7018892</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8277,10 +8287,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376085</v>
+        <v>124368223</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8293,39 +8303,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496204</v>
+        <v>496103</v>
       </c>
       <c r="R68" t="n">
-        <v>7018992</v>
+        <v>7018878</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8358,11 +8363,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8389,10 +8389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124373122</v>
+        <v>124372694</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8405,39 +8405,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496571</v>
+        <v>496555</v>
       </c>
       <c r="R69" t="n">
-        <v>7018892</v>
+        <v>7018901</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8467,14 +8462,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8489,12 +8489,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8837,10 +8837,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124373902</v>
+        <v>124369981</v>
       </c>
       <c r="B73" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8849,25 +8849,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8877,13 +8877,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496634</v>
+        <v>496293</v>
       </c>
       <c r="R73" t="n">
-        <v>7019012</v>
+        <v>7018882</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8933,16 +8933,41 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9051,10 +9076,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124369981</v>
+        <v>124373902</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9063,25 +9088,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9091,13 +9116,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496293</v>
+        <v>496634</v>
       </c>
       <c r="R75" t="n">
-        <v>7018882</v>
+        <v>7019012</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9126,7 +9151,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9136,7 +9161,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9147,41 +9172,16 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4006,14 +4006,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124367848</v>
+        <v>124366868</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4022,34 +4022,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496067</v>
+        <v>496023</v>
       </c>
       <c r="R31" t="n">
-        <v>7018881</v>
+        <v>7018919</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4106,26 +4135,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4143,14 +4152,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365832</v>
+        <v>124372826</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4159,34 +4168,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496020</v>
+        <v>496446</v>
       </c>
       <c r="R32" t="n">
-        <v>7018936</v>
+        <v>7018884</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4219,6 +4233,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4245,14 +4264,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374980</v>
+        <v>124372986</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4261,34 +4280,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496356</v>
+        <v>496526</v>
       </c>
       <c r="R33" t="n">
-        <v>7018988</v>
+        <v>7018886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4318,19 +4342,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>20:22</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4345,22 +4364,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124368130</v>
+        <v>124367848</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,21 +4392,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4416,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496089</v>
+        <v>496067</v>
       </c>
       <c r="R34" t="n">
-        <v>7018863</v>
+        <v>7018881</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4430,11 +4449,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4443,6 +4472,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4459,10 +4513,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124366868</v>
+        <v>124365832</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4475,58 +4529,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496023</v>
+        <v>496020</v>
       </c>
       <c r="R35" t="n">
-        <v>7018919</v>
+        <v>7018936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4556,26 +4586,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4584,11 +4599,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4605,10 +4615,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124372826</v>
+        <v>124374980</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4621,39 +4631,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496446</v>
+        <v>496356</v>
       </c>
       <c r="R36" t="n">
-        <v>7018884</v>
+        <v>7018988</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4683,14 +4688,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,22 +4715,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124372986</v>
+        <v>124368130</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4733,39 +4743,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496526</v>
+        <v>496089</v>
       </c>
       <c r="R37" t="n">
-        <v>7018886</v>
+        <v>7018863</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4798,11 +4803,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124370557</v>
+        <v>124375411</v>
       </c>
       <c r="B43" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,40 +5406,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5448,13 +5453,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496338</v>
+        <v>496320</v>
       </c>
       <c r="R43" t="n">
-        <v>7018951</v>
+        <v>7018988</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5481,11 +5486,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5494,6 +5514,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5510,10 +5535,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124375411</v>
+        <v>124370557</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5522,45 +5547,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5569,13 +5589,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496320</v>
+        <v>496338</v>
       </c>
       <c r="R44" t="n">
-        <v>7018988</v>
+        <v>7018951</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5602,26 +5622,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5630,11 +5635,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6181,14 +6181,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124365917</v>
+        <v>124373030</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6197,27 +6197,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496005</v>
+        <v>496538</v>
       </c>
       <c r="R50" t="n">
-        <v>7018959</v>
+        <v>7018895</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6262,6 +6262,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6288,14 +6293,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124365439</v>
+        <v>124372196</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6304,37 +6309,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496029</v>
+        <v>496444</v>
       </c>
       <c r="R51" t="n">
-        <v>7018964</v>
+        <v>7018877</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6361,11 +6371,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6374,6 +6399,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6390,14 +6440,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124373030</v>
+        <v>124372406</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6435,10 +6485,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496538</v>
+        <v>496324</v>
       </c>
       <c r="R52" t="n">
-        <v>7018895</v>
+        <v>7018859</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6502,10 +6552,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124372196</v>
+        <v>124365917</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6518,27 +6568,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6547,13 +6597,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496444</v>
+        <v>496005</v>
       </c>
       <c r="R53" t="n">
-        <v>7018877</v>
+        <v>7018959</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6580,26 +6630,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6608,31 +6643,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6649,10 +6659,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124372406</v>
+        <v>124365439</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6665,39 +6675,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496324</v>
+        <v>496029</v>
       </c>
       <c r="R54" t="n">
-        <v>7018859</v>
+        <v>7018964</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6730,11 +6735,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9890,10 +9890,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124375041</v>
+        <v>124369822</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496343</v>
+        <v>496245</v>
       </c>
       <c r="R82" t="n">
-        <v>7018997</v>
+        <v>7018876</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124369822</v>
+        <v>124375602</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -10032,13 +10032,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496245</v>
+        <v>496297</v>
       </c>
       <c r="R83" t="n">
-        <v>7018876</v>
+        <v>7018948</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10065,11 +10065,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10078,6 +10088,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10094,10 +10129,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124375602</v>
+        <v>124375041</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10110,21 +10145,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10134,13 +10169,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496297</v>
+        <v>496343</v>
       </c>
       <c r="R84" t="n">
-        <v>7018948</v>
+        <v>7018997</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10167,21 +10202,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10190,31 +10215,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374769</v>
+        <v>124366031</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496465</v>
+        <v>495986</v>
       </c>
       <c r="R2" t="n">
-        <v>7018933</v>
+        <v>7018958</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +748,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368788</v>
+        <v>124375665</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496168</v>
+        <v>496298</v>
       </c>
       <c r="R3" t="n">
-        <v>7018906</v>
+        <v>7018981</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,55 +878,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124372382</v>
+        <v>124364937</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91026</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -965,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496322</v>
+        <v>496075</v>
       </c>
       <c r="R4" t="n">
-        <v>7018864</v>
+        <v>7018977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124372949</v>
+        <v>124375158</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1094,10 +1029,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496504</v>
+        <v>496311</v>
       </c>
       <c r="R5" t="n">
-        <v>7018879</v>
+        <v>7018994</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,14 +1083,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1106,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124365804</v>
+        <v>124365867</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496020</v>
+        <v>496012</v>
       </c>
       <c r="R6" t="n">
-        <v>7018934</v>
+        <v>7018928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374413</v>
+        <v>124366246</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1315,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496449</v>
+        <v>496045</v>
       </c>
       <c r="R7" t="n">
-        <v>7018988</v>
+        <v>7018931</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124375158</v>
+        <v>124371845</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,55 +1343,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496311</v>
+        <v>496327</v>
       </c>
       <c r="R8" t="n">
-        <v>7018994</v>
+        <v>7018893</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1464,21 +1404,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1487,11 +1417,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124369665</v>
+        <v>124372203</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496219</v>
+        <v>496503</v>
       </c>
       <c r="R9" t="n">
-        <v>7018883</v>
+        <v>7018898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,9 +1506,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1533,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124366246</v>
+        <v>124368788</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,13 +1585,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496045</v>
+        <v>496168</v>
       </c>
       <c r="R10" t="n">
-        <v>7018931</v>
+        <v>7018906</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,11 +1618,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1696,6 +1641,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1712,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124371804</v>
+        <v>124374413</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1752,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496319</v>
+        <v>496449</v>
       </c>
       <c r="R11" t="n">
-        <v>7018893</v>
+        <v>7018988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,43 +1784,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124372213</v>
+        <v>124369063</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496392</v>
+        <v>496203</v>
       </c>
       <c r="R12" t="n">
-        <v>7018866</v>
+        <v>7018907</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,14 +1862,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,6 +1885,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124368504</v>
+        <v>124368893</v>
       </c>
       <c r="B13" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496112</v>
+        <v>496152</v>
       </c>
       <c r="R13" t="n">
-        <v>7018885</v>
+        <v>7018906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124367876</v>
+        <v>124368930</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496096</v>
+        <v>496185</v>
       </c>
       <c r="R14" t="n">
-        <v>7018871</v>
+        <v>7018934</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,11 +2101,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2114,6 +2124,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2130,14 +2165,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124372868</v>
+        <v>124374980</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2146,39 +2181,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496485</v>
+        <v>496356</v>
       </c>
       <c r="R15" t="n">
-        <v>7018881</v>
+        <v>7018988</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,14 +2238,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,22 +2265,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124365230</v>
+        <v>124372052</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,25 +2289,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496029</v>
+        <v>496397</v>
       </c>
       <c r="R16" t="n">
-        <v>7018962</v>
+        <v>7018931</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,9 +2350,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,19 +2377,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124372052</v>
+        <v>124369822</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2384,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496397</v>
+        <v>496245</v>
       </c>
       <c r="R17" t="n">
-        <v>7018931</v>
+        <v>7018876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,19 +2462,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,22 +2479,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124364887</v>
+        <v>124365032</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2472,21 +2507,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496078</v>
+        <v>496041</v>
       </c>
       <c r="R18" t="n">
-        <v>7018964</v>
+        <v>7018962</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370553</v>
+        <v>124370557</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,45 +2605,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2617,13 +2647,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496338</v>
       </c>
       <c r="R19" t="n">
-        <v>7018896</v>
+        <v>7018951</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2650,26 +2680,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2678,11 +2693,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2699,10 +2709,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124366502</v>
+        <v>124369665</v>
       </c>
       <c r="B20" t="n">
-        <v>79795</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,25 +2721,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2739,13 +2749,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495918</v>
+        <v>496219</v>
       </c>
       <c r="R20" t="n">
-        <v>7018925</v>
+        <v>7018883</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,21 +2782,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2795,31 +2795,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2836,10 +2811,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124368930</v>
+        <v>124370553</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,41 +2823,60 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496185</v>
+        <v>496283</v>
       </c>
       <c r="R21" t="n">
-        <v>7018934</v>
+        <v>7018896</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,7 +2905,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2915,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,26 +2935,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2973,10 +2952,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124364937</v>
+        <v>124367876</v>
       </c>
       <c r="B22" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,25 +2964,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3013,10 +2992,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496075</v>
+        <v>496096</v>
       </c>
       <c r="R22" t="n">
-        <v>7018977</v>
+        <v>7018871</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3075,55 +3054,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124372810</v>
+        <v>124373902</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496460</v>
+        <v>496634</v>
       </c>
       <c r="R23" t="n">
-        <v>7018885</v>
+        <v>7019012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3153,14 +3127,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,22 +3154,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124374616</v>
+        <v>124373649</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,41 +3178,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496506</v>
+        <v>496649</v>
       </c>
       <c r="R24" t="n">
-        <v>7018942</v>
+        <v>7018995</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3262,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3272,7 +3256,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,26 +3271,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3324,10 +3288,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375105</v>
+        <v>124366461</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,41 +3300,51 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496343</v>
+        <v>495944</v>
       </c>
       <c r="R25" t="n">
-        <v>7018997</v>
+        <v>7018967</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3399,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3409,7 +3383,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,26 +3398,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3461,7 +3415,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370431</v>
+        <v>124372694</v>
       </c>
       <c r="B26" t="n">
         <v>74901</v>
@@ -3501,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496343</v>
+        <v>496555</v>
       </c>
       <c r="R26" t="n">
-        <v>7018868</v>
+        <v>7018901</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3534,9 +3488,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,26 +3515,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124372460</v>
+        <v>124365917</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3579,27 +3543,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3608,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496311</v>
+        <v>496005</v>
       </c>
       <c r="R27" t="n">
-        <v>7018869</v>
+        <v>7018959</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,11 +3608,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,14 +3634,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124372291</v>
+        <v>124374616</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3691,42 +3650,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496371</v>
+        <v>496506</v>
       </c>
       <c r="R28" t="n">
-        <v>7018862</v>
+        <v>7018942</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3753,14 +3707,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,6 +3730,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3787,10 +3771,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365032</v>
+        <v>124365230</v>
       </c>
       <c r="B29" t="n">
-        <v>96354</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3799,25 +3783,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3827,7 +3811,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496041</v>
+        <v>496029</v>
       </c>
       <c r="R29" t="n">
         <v>7018962</v>
@@ -3889,10 +3873,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375665</v>
+        <v>124369957</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3901,25 +3885,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3929,10 +3913,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496298</v>
+        <v>496287</v>
       </c>
       <c r="R30" t="n">
-        <v>7018981</v>
+        <v>7018882</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3962,24 +3946,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,26 +3963,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124366868</v>
+        <v>124371804</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4022,58 +3991,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496023</v>
+        <v>496319</v>
       </c>
       <c r="R31" t="n">
-        <v>7018919</v>
+        <v>7018893</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4103,26 +4048,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4131,11 +4061,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4152,14 +4077,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124372826</v>
+        <v>124367848</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4168,39 +4093,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496446</v>
+        <v>496067</v>
       </c>
       <c r="R32" t="n">
-        <v>7018884</v>
+        <v>7018881</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4230,14 +4150,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4248,6 +4173,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4264,14 +4214,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124372986</v>
+        <v>124375602</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4280,42 +4230,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496526</v>
+        <v>496297</v>
       </c>
       <c r="R33" t="n">
-        <v>7018886</v>
+        <v>7018948</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4342,14 +4287,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,6 +4310,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4376,7 +4351,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124367848</v>
+        <v>124369981</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4416,13 +4391,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496067</v>
+        <v>496293</v>
       </c>
       <c r="R34" t="n">
-        <v>7018881</v>
+        <v>7018882</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4451,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4461,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4513,10 +4488,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124365832</v>
+        <v>124374892</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,21 +4504,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4553,10 +4528,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496020</v>
+        <v>496365</v>
       </c>
       <c r="R35" t="n">
-        <v>7018936</v>
+        <v>7018964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4615,10 +4590,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374980</v>
+        <v>124365439</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4631,21 +4606,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4655,10 +4630,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496356</v>
+        <v>496029</v>
       </c>
       <c r="R36" t="n">
-        <v>7018988</v>
+        <v>7018964</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4688,19 +4663,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,22 +4680,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124368130</v>
+        <v>124366502</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4739,25 +4704,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4767,13 +4732,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496089</v>
+        <v>495918</v>
       </c>
       <c r="R37" t="n">
-        <v>7018863</v>
+        <v>7018925</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4800,11 +4765,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4813,6 +4788,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4829,7 +4829,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124374892</v>
+        <v>124370135</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496365</v>
+        <v>496395</v>
       </c>
       <c r="R38" t="n">
-        <v>7018964</v>
+        <v>7018910</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4931,14 +4931,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124372169</v>
+        <v>124365832</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4947,39 +4947,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496446</v>
+        <v>496020</v>
       </c>
       <c r="R39" t="n">
-        <v>7018897</v>
+        <v>7018936</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5012,11 +5007,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5043,7 +5033,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124373203</v>
+        <v>124374769</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -5083,13 +5073,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496570</v>
+        <v>496465</v>
       </c>
       <c r="R40" t="n">
-        <v>7018914</v>
+        <v>7018933</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5118,7 +5108,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5128,7 +5118,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5180,7 +5170,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124372203</v>
+        <v>124365804</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5220,10 +5210,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496503</v>
+        <v>496020</v>
       </c>
       <c r="R41" t="n">
-        <v>7018898</v>
+        <v>7018934</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5253,19 +5243,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5280,22 +5260,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124366031</v>
+        <v>124375411</v>
       </c>
       <c r="B42" t="n">
-        <v>90962</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,41 +5284,60 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495986</v>
+        <v>496320</v>
       </c>
       <c r="R42" t="n">
-        <v>7018958</v>
+        <v>7018988</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5365,11 +5364,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5378,6 +5392,11 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5394,10 +5413,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375411</v>
+        <v>124368504</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,60 +5425,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496320</v>
+        <v>496112</v>
       </c>
       <c r="R43" t="n">
-        <v>7018988</v>
+        <v>7018885</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,26 +5486,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5514,11 +5499,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5535,10 +5515,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124370557</v>
+        <v>124368130</v>
       </c>
       <c r="B44" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5551,48 +5531,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496338</v>
+        <v>496089</v>
       </c>
       <c r="R44" t="n">
-        <v>7018951</v>
+        <v>7018863</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5651,14 +5617,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124372778</v>
+        <v>124369001</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5667,39 +5633,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496426</v>
+        <v>496205</v>
       </c>
       <c r="R45" t="n">
-        <v>7018876</v>
+        <v>7018858</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5732,11 +5693,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5763,14 +5719,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124372714</v>
+        <v>124368223</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5779,39 +5735,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496416</v>
+        <v>496103</v>
       </c>
       <c r="R46" t="n">
-        <v>7018877</v>
+        <v>7018878</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5844,11 +5795,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5875,10 +5821,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124367729</v>
+        <v>124364887</v>
       </c>
       <c r="B47" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5891,21 +5837,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5915,10 +5861,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496047</v>
+        <v>496078</v>
       </c>
       <c r="R47" t="n">
-        <v>7018892</v>
+        <v>7018964</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5977,10 +5923,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124365867</v>
+        <v>124367729</v>
       </c>
       <c r="B48" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5993,21 +5939,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6017,10 +5963,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496012</v>
+        <v>496047</v>
       </c>
       <c r="R48" t="n">
-        <v>7018928</v>
+        <v>7018892</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6181,14 +6127,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124373030</v>
+        <v>124373203</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6197,42 +6143,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496538</v>
+        <v>496570</v>
       </c>
       <c r="R50" t="n">
-        <v>7018895</v>
+        <v>7018914</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6259,14 +6200,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6277,6 +6223,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6293,43 +6264,43 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124372196</v>
+        <v>124365253</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>100279</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6338,13 +6309,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496444</v>
+        <v>496029</v>
       </c>
       <c r="R51" t="n">
-        <v>7018877</v>
+        <v>7018921</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6373,7 +6344,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6383,12 +6354,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6403,26 +6369,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6440,14 +6386,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124372406</v>
+        <v>124375041</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6456,39 +6402,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496324</v>
+        <v>496343</v>
       </c>
       <c r="R52" t="n">
-        <v>7018859</v>
+        <v>7018997</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6521,11 +6462,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6552,7 +6488,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124365917</v>
+        <v>124366230</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6597,13 +6533,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496005</v>
+        <v>495918</v>
       </c>
       <c r="R53" t="n">
-        <v>7018959</v>
+        <v>7018928</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6630,11 +6566,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6643,6 +6594,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6659,10 +6635,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124365439</v>
+        <v>124370431</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6675,21 +6651,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6699,10 +6675,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496029</v>
+        <v>496343</v>
       </c>
       <c r="R54" t="n">
-        <v>7018964</v>
+        <v>7018868</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6761,10 +6737,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124366461</v>
+        <v>124375105</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6773,51 +6749,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495944</v>
+        <v>496343</v>
       </c>
       <c r="R55" t="n">
-        <v>7018967</v>
+        <v>7018997</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6846,7 +6812,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6856,7 +6822,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6871,6 +6837,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6888,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372343</v>
+        <v>124372906</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6933,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496345</v>
+        <v>496496</v>
       </c>
       <c r="R56" t="n">
-        <v>7018866</v>
+        <v>7018887</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7000,14 +6986,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124366230</v>
+        <v>124366868</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7016,27 +7002,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7045,13 +7050,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495918</v>
+        <v>496023</v>
       </c>
       <c r="R57" t="n">
-        <v>7018928</v>
+        <v>7018919</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7080,7 +7085,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7090,12 +7095,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7110,26 +7115,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7147,14 +7132,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124369001</v>
+        <v>124372986</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7163,34 +7148,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496205</v>
+        <v>496526</v>
       </c>
       <c r="R58" t="n">
-        <v>7018858</v>
+        <v>7018886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7223,6 +7213,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7249,43 +7244,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124369063</v>
+        <v>124373091</v>
       </c>
       <c r="B59" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7294,13 +7289,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496203</v>
+        <v>496553</v>
       </c>
       <c r="R59" t="n">
-        <v>7018907</v>
+        <v>7018888</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7327,19 +7322,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7350,31 +7340,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7391,7 +7356,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372906</v>
+        <v>124372714</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7436,10 +7401,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496496</v>
+        <v>496416</v>
       </c>
       <c r="R60" t="n">
-        <v>7018887</v>
+        <v>7018877</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7503,7 +7468,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373091</v>
+        <v>124376085</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7548,10 +7513,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496553</v>
+        <v>496204</v>
       </c>
       <c r="R61" t="n">
-        <v>7018888</v>
+        <v>7018992</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7615,7 +7580,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372234</v>
+        <v>124373122</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7660,10 +7625,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496384</v>
+        <v>496571</v>
       </c>
       <c r="R62" t="n">
-        <v>7018864</v>
+        <v>7018892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7727,7 +7692,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372184</v>
+        <v>124372460</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7772,10 +7737,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496392</v>
+        <v>496311</v>
       </c>
       <c r="R63" t="n">
-        <v>7018873</v>
+        <v>7018869</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7839,7 +7804,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372891</v>
+        <v>124372184</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7884,10 +7849,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496487</v>
+        <v>496392</v>
       </c>
       <c r="R64" t="n">
-        <v>7018890</v>
+        <v>7018873</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7951,7 +7916,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372245</v>
+        <v>124372949</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7996,10 +7961,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496380</v>
+        <v>496504</v>
       </c>
       <c r="R65" t="n">
-        <v>7018867</v>
+        <v>7018879</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8063,7 +8028,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124376085</v>
+        <v>124372343</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8108,10 +8073,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496204</v>
+        <v>496345</v>
       </c>
       <c r="R66" t="n">
-        <v>7018992</v>
+        <v>7018866</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8175,7 +8140,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124373122</v>
+        <v>124372245</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8220,10 +8185,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496571</v>
+        <v>496380</v>
       </c>
       <c r="R67" t="n">
-        <v>7018892</v>
+        <v>7018867</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8287,14 +8252,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124368223</v>
+        <v>124372196</v>
       </c>
       <c r="B68" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8303,37 +8268,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496103</v>
+        <v>496444</v>
       </c>
       <c r="R68" t="n">
-        <v>7018878</v>
+        <v>7018877</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8360,11 +8330,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8373,6 +8358,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8389,14 +8399,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372694</v>
+        <v>124372234</v>
       </c>
       <c r="B69" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8405,34 +8415,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496555</v>
+        <v>496384</v>
       </c>
       <c r="R69" t="n">
-        <v>7018901</v>
+        <v>7018864</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8462,19 +8477,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>19:23</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8489,26 +8499,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124369957</v>
+        <v>124372891</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8517,34 +8527,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496287</v>
+        <v>496487</v>
       </c>
       <c r="R70" t="n">
-        <v>7018882</v>
+        <v>7018890</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8577,6 +8592,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8603,7 +8623,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124373047</v>
+        <v>124372382</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8648,10 +8668,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496551</v>
+        <v>496322</v>
       </c>
       <c r="R71" t="n">
-        <v>7018894</v>
+        <v>7018864</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8715,43 +8735,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373649</v>
+        <v>124373030</v>
       </c>
       <c r="B72" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8760,13 +8780,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496649</v>
+        <v>496538</v>
       </c>
       <c r="R72" t="n">
-        <v>7018995</v>
+        <v>7018895</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8793,19 +8813,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>19:52</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8816,11 +8831,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8837,14 +8847,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124369981</v>
+        <v>124372810</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8853,37 +8863,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496293</v>
+        <v>496460</v>
       </c>
       <c r="R73" t="n">
-        <v>7018882</v>
+        <v>7018885</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8910,19 +8925,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>18:10</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8933,31 +8943,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8974,14 +8959,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124368893</v>
+        <v>124372778</v>
       </c>
       <c r="B74" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8990,34 +8975,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496152</v>
+        <v>496426</v>
       </c>
       <c r="R74" t="n">
-        <v>7018906</v>
+        <v>7018876</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9050,6 +9040,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9076,50 +9071,55 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124373902</v>
+        <v>124372353</v>
       </c>
       <c r="B75" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496634</v>
+        <v>496338</v>
       </c>
       <c r="R75" t="n">
-        <v>7019012</v>
+        <v>7018864</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9149,19 +9149,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>19:55</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9176,55 +9171,55 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124365253</v>
+        <v>124372169</v>
       </c>
       <c r="B76" t="n">
-        <v>100279</v>
+        <v>57513</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9233,10 +9228,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496029</v>
+        <v>496446</v>
       </c>
       <c r="R76" t="n">
-        <v>7018921</v>
+        <v>7018897</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9266,19 +9261,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:46</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9289,11 +9279,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9310,14 +9295,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124370135</v>
+        <v>124372291</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9326,34 +9311,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496395</v>
+        <v>496371</v>
       </c>
       <c r="R77" t="n">
-        <v>7018910</v>
+        <v>7018862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9386,6 +9376,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9412,14 +9407,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124371845</v>
+        <v>124373047</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9428,34 +9423,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496327</v>
+        <v>496551</v>
       </c>
       <c r="R78" t="n">
-        <v>7018893</v>
+        <v>7018894</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9488,6 +9488,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9514,7 +9519,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372353</v>
+        <v>124372406</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9559,10 +9564,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496338</v>
+        <v>496324</v>
       </c>
       <c r="R79" t="n">
-        <v>7018864</v>
+        <v>7018859</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9626,7 +9631,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124373102</v>
+        <v>124372213</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9671,10 +9676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496574</v>
+        <v>496392</v>
       </c>
       <c r="R80" t="n">
-        <v>7018897</v>
+        <v>7018866</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9890,14 +9895,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124369822</v>
+        <v>124373102</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9906,34 +9911,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496245</v>
+        <v>496574</v>
       </c>
       <c r="R82" t="n">
-        <v>7018876</v>
+        <v>7018897</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9966,6 +9976,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9992,14 +10007,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124375602</v>
+        <v>124372868</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10008,37 +10023,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496297</v>
+        <v>496485</v>
       </c>
       <c r="R83" t="n">
-        <v>7018948</v>
+        <v>7018881</v>
       </c>
       <c r="S83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10065,19 +10085,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:43</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10088,31 +10103,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10129,14 +10119,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124375041</v>
+        <v>124372826</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10145,34 +10135,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496343</v>
+        <v>496446</v>
       </c>
       <c r="R84" t="n">
-        <v>7018997</v>
+        <v>7018884</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10205,6 +10200,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124366031</v>
+        <v>124374980</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495986</v>
+        <v>496356</v>
       </c>
       <c r="R2" t="n">
-        <v>7018958</v>
+        <v>7018988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +748,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375665</v>
+        <v>124368930</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496298</v>
+        <v>496185</v>
       </c>
       <c r="R3" t="n">
-        <v>7018981</v>
+        <v>7018934</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,26 +883,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124364937</v>
+        <v>124374892</v>
       </c>
       <c r="B4" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496075</v>
+        <v>496365</v>
       </c>
       <c r="R4" t="n">
-        <v>7018977</v>
+        <v>7018964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375158</v>
+        <v>124375105</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,52 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496311</v>
+        <v>496343</v>
       </c>
       <c r="R5" t="n">
-        <v>7018994</v>
+        <v>7018997</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1085,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,6 +1126,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1127,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124365867</v>
+        <v>124365032</v>
       </c>
       <c r="B6" t="n">
-        <v>82597</v>
+        <v>96354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1179,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496012</v>
+        <v>496041</v>
       </c>
       <c r="R6" t="n">
-        <v>7018928</v>
+        <v>7018962</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124366246</v>
+        <v>124364937</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496045</v>
+        <v>496075</v>
       </c>
       <c r="R7" t="n">
-        <v>7018931</v>
+        <v>7018977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124371845</v>
+        <v>124373902</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496327</v>
+        <v>496634</v>
       </c>
       <c r="R8" t="n">
-        <v>7018893</v>
+        <v>7019012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,9 +1440,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124372203</v>
+        <v>124368893</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496503</v>
+        <v>496152</v>
       </c>
       <c r="R9" t="n">
-        <v>7018898</v>
+        <v>7018906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,19 +1552,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124368788</v>
+        <v>124369063</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,41 +1593,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496168</v>
+        <v>496203</v>
       </c>
       <c r="R10" t="n">
-        <v>7018906</v>
+        <v>7018907</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,12 +1700,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1682,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374413</v>
+        <v>124365867</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,21 +1739,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496449</v>
+        <v>496012</v>
       </c>
       <c r="R11" t="n">
-        <v>7018988</v>
+        <v>7018928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124369063</v>
+        <v>124372203</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,46 +1837,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496203</v>
+        <v>496503</v>
       </c>
       <c r="R12" t="n">
-        <v>7018907</v>
+        <v>7018898</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,51 +1921,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124368893</v>
+        <v>124369981</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1953,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496152</v>
+        <v>496293</v>
       </c>
       <c r="R13" t="n">
-        <v>7018906</v>
+        <v>7018882</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,11 +2010,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2012,6 +2033,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2028,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124368930</v>
+        <v>124370557</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,37 +2090,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496185</v>
+        <v>496338</v>
       </c>
       <c r="R14" t="n">
-        <v>7018934</v>
+        <v>7018951</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,21 +2161,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2124,31 +2174,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2165,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374980</v>
+        <v>124367848</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,21 +2206,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2205,10 +2230,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496356</v>
+        <v>496067</v>
       </c>
       <c r="R15" t="n">
-        <v>7018988</v>
+        <v>7018881</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,23 +2286,48 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124372052</v>
+        <v>124374769</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2317,13 +2367,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496397</v>
+        <v>496465</v>
       </c>
       <c r="R16" t="n">
-        <v>7018931</v>
+        <v>7018933</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,7 +2402,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2362,7 +2412,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,26 +2423,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124369822</v>
+        <v>124366502</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,25 +2476,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2429,13 +2504,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496245</v>
+        <v>495918</v>
       </c>
       <c r="R17" t="n">
-        <v>7018876</v>
+        <v>7018925</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2462,11 +2537,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2475,6 +2560,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2491,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124365032</v>
+        <v>124366230</v>
       </c>
       <c r="B18" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,37 +2617,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496041</v>
+        <v>495918</v>
       </c>
       <c r="R18" t="n">
-        <v>7018962</v>
+        <v>7018928</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,11 +2679,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2577,6 +2707,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2593,10 +2748,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124370557</v>
+        <v>124368223</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,48 +2764,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496338</v>
+        <v>496103</v>
       </c>
       <c r="R19" t="n">
-        <v>7018951</v>
+        <v>7018878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,10 +2850,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124369665</v>
+        <v>124366031</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2725,21 +2866,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2749,10 +2890,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496219</v>
+        <v>495986</v>
       </c>
       <c r="R20" t="n">
-        <v>7018883</v>
+        <v>7018958</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,10 +2952,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124370553</v>
+        <v>124373203</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,60 +2964,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496283</v>
+        <v>496570</v>
       </c>
       <c r="R21" t="n">
-        <v>7018896</v>
+        <v>7018914</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2905,7 +3027,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,12 +3037,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,6 +3052,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2952,10 +3089,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124367876</v>
+        <v>124375158</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2968,37 +3105,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496096</v>
+        <v>496311</v>
       </c>
       <c r="R22" t="n">
-        <v>7018871</v>
+        <v>7018994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,11 +3176,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3038,6 +3199,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3054,10 +3220,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124373902</v>
+        <v>124375411</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3066,41 +3232,60 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496634</v>
+        <v>496320</v>
       </c>
       <c r="R23" t="n">
-        <v>7019012</v>
+        <v>7018988</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3129,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3139,7 +3324,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,26 +3340,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124373649</v>
+        <v>124364887</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3178,46 +3373,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496649</v>
+        <v>496078</v>
       </c>
       <c r="R24" t="n">
-        <v>7018995</v>
+        <v>7018964</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3244,21 +3434,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3267,11 +3447,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3288,10 +3463,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124366461</v>
+        <v>124368130</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3300,51 +3475,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495944</v>
+        <v>496089</v>
       </c>
       <c r="R25" t="n">
-        <v>7018967</v>
+        <v>7018863</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,21 +3536,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3394,11 +3549,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3415,10 +3565,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124372694</v>
+        <v>124365253</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3427,38 +3577,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496555</v>
+        <v>496029</v>
       </c>
       <c r="R26" t="n">
-        <v>7018901</v>
+        <v>7018921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3645,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3655,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3511,26 +3666,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365917</v>
+        <v>124366461</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,31 +3699,36 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3572,13 +3737,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496005</v>
+        <v>495944</v>
       </c>
       <c r="R27" t="n">
-        <v>7018959</v>
+        <v>7018967</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3605,11 +3770,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3618,6 +3793,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3634,10 +3814,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374616</v>
+        <v>124373649</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,41 +3826,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496506</v>
+        <v>496649</v>
       </c>
       <c r="R28" t="n">
-        <v>7018942</v>
+        <v>7018995</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3709,7 +3894,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3904,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,26 +3919,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3873,10 +4038,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369957</v>
+        <v>124369665</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3889,21 +4054,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3913,10 +4078,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496287</v>
+        <v>496219</v>
       </c>
       <c r="R30" t="n">
-        <v>7018882</v>
+        <v>7018883</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +4140,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124371804</v>
+        <v>124371845</v>
       </c>
       <c r="B31" t="n">
         <v>91012</v>
@@ -4015,7 +4180,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496319</v>
+        <v>496327</v>
       </c>
       <c r="R31" t="n">
         <v>7018893</v>
@@ -4077,10 +4242,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124367848</v>
+        <v>124367876</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4089,25 +4254,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4117,10 +4282,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496067</v>
+        <v>496096</v>
       </c>
       <c r="R32" t="n">
-        <v>7018881</v>
+        <v>7018871</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,21 +4315,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4173,31 +4328,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4214,10 +4344,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124375602</v>
+        <v>124365832</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4230,21 +4360,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4254,13 +4384,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496297</v>
+        <v>496020</v>
       </c>
       <c r="R33" t="n">
-        <v>7018948</v>
+        <v>7018936</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4287,21 +4417,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4310,31 +4430,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4351,10 +4446,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124369981</v>
+        <v>124375665</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4363,25 +4458,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4391,13 +4486,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496293</v>
+        <v>496298</v>
       </c>
       <c r="R34" t="n">
-        <v>7018882</v>
+        <v>7018981</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4426,7 +4521,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4531,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4447,51 +4547,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374892</v>
+        <v>124375602</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4504,21 +4579,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4528,13 +4603,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496365</v>
+        <v>496297</v>
       </c>
       <c r="R35" t="n">
-        <v>7018964</v>
+        <v>7018948</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4561,11 +4636,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4574,6 +4659,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4590,7 +4700,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124365439</v>
+        <v>124371804</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4630,10 +4740,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496029</v>
+        <v>496319</v>
       </c>
       <c r="R36" t="n">
-        <v>7018964</v>
+        <v>7018893</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4692,10 +4802,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124366502</v>
+        <v>124369222</v>
       </c>
       <c r="B37" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4704,25 +4814,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4732,13 +4842,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495918</v>
+        <v>496155</v>
       </c>
       <c r="R37" t="n">
-        <v>7018925</v>
+        <v>7018842</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4765,21 +4875,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4788,31 +4888,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4829,10 +4904,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124370135</v>
+        <v>124365804</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4845,21 +4920,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4869,10 +4944,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496395</v>
+        <v>496020</v>
       </c>
       <c r="R38" t="n">
-        <v>7018910</v>
+        <v>7018934</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4931,7 +5006,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124365832</v>
+        <v>124372694</v>
       </c>
       <c r="B39" t="n">
         <v>74901</v>
@@ -4971,10 +5046,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496020</v>
+        <v>496555</v>
       </c>
       <c r="R39" t="n">
-        <v>7018936</v>
+        <v>7018901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5004,9 +5079,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,22 +5106,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124374769</v>
+        <v>124367729</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5049,21 +5134,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5073,13 +5158,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496465</v>
+        <v>496047</v>
       </c>
       <c r="R40" t="n">
-        <v>7018933</v>
+        <v>7018892</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5106,21 +5191,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5129,31 +5204,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5170,7 +5220,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124365804</v>
+        <v>124369822</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5210,10 +5260,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496020</v>
+        <v>496245</v>
       </c>
       <c r="R41" t="n">
-        <v>7018934</v>
+        <v>7018876</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5272,10 +5322,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124375411</v>
+        <v>124370135</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5284,60 +5334,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496320</v>
+        <v>496395</v>
       </c>
       <c r="R42" t="n">
-        <v>7018988</v>
+        <v>7018910</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5364,26 +5395,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5392,11 +5408,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5413,10 +5424,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124368504</v>
+        <v>124365917</v>
       </c>
       <c r="B43" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5429,34 +5440,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496112</v>
+        <v>496005</v>
       </c>
       <c r="R43" t="n">
-        <v>7018885</v>
+        <v>7018959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5515,10 +5531,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124368130</v>
+        <v>124372052</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5531,21 +5547,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5555,10 +5571,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496089</v>
+        <v>496397</v>
       </c>
       <c r="R44" t="n">
-        <v>7018863</v>
+        <v>7018931</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5588,9 +5604,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5605,19 +5631,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124369001</v>
+        <v>124374413</v>
       </c>
       <c r="B45" t="n">
         <v>91012</v>
@@ -5657,10 +5683,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496205</v>
+        <v>496449</v>
       </c>
       <c r="R45" t="n">
-        <v>7018858</v>
+        <v>7018988</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5719,10 +5745,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124368223</v>
+        <v>124375041</v>
       </c>
       <c r="B46" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5735,21 +5761,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5759,10 +5785,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496103</v>
+        <v>496343</v>
       </c>
       <c r="R46" t="n">
-        <v>7018878</v>
+        <v>7018997</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5821,10 +5847,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124364887</v>
+        <v>124368504</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5837,21 +5863,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5861,10 +5887,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496078</v>
+        <v>496112</v>
       </c>
       <c r="R47" t="n">
-        <v>7018964</v>
+        <v>7018885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5923,10 +5949,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124367729</v>
+        <v>124369957</v>
       </c>
       <c r="B48" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5939,21 +5965,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5963,10 +5989,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496047</v>
+        <v>496287</v>
       </c>
       <c r="R48" t="n">
-        <v>7018892</v>
+        <v>7018882</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6025,10 +6051,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124369222</v>
+        <v>124368788</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6041,21 +6067,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6065,13 +6091,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496155</v>
+        <v>496168</v>
       </c>
       <c r="R49" t="n">
-        <v>7018842</v>
+        <v>7018906</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6098,11 +6124,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6111,6 +6147,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6127,10 +6188,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124373203</v>
+        <v>124365439</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6143,21 +6204,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6167,13 +6228,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496570</v>
+        <v>496029</v>
       </c>
       <c r="R50" t="n">
-        <v>7018914</v>
+        <v>7018964</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6200,21 +6261,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6223,31 +6274,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6264,10 +6290,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124365253</v>
+        <v>124366246</v>
       </c>
       <c r="B51" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6276,43 +6302,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496029</v>
+        <v>496045</v>
       </c>
       <c r="R51" t="n">
-        <v>7018921</v>
+        <v>7018931</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6342,21 +6363,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6365,11 +6376,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6386,10 +6392,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375041</v>
+        <v>124374616</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6402,21 +6408,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6426,13 +6432,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496343</v>
+        <v>496506</v>
       </c>
       <c r="R52" t="n">
-        <v>7018997</v>
+        <v>7018942</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6459,11 +6465,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6472,6 +6488,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6488,10 +6529,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124366230</v>
+        <v>124369001</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6504,42 +6545,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495918</v>
+        <v>496205</v>
       </c>
       <c r="R53" t="n">
-        <v>7018928</v>
+        <v>7018858</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6566,26 +6602,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6594,31 +6615,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6737,10 +6733,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124375105</v>
+        <v>124370553</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6749,41 +6745,60 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496343</v>
+        <v>496283</v>
       </c>
       <c r="R55" t="n">
-        <v>7018997</v>
+        <v>7018896</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6812,7 +6827,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6822,7 +6837,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6837,26 +6857,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372906</v>
+        <v>124372169</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496496</v>
+        <v>496446</v>
       </c>
       <c r="R56" t="n">
-        <v>7018887</v>
+        <v>7018897</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,14 +6986,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124366868</v>
+        <v>124372986</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7019,29 +7019,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7050,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496023</v>
+        <v>496526</v>
       </c>
       <c r="R57" t="n">
-        <v>7018919</v>
+        <v>7018886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7083,24 +7064,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7111,11 +7082,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7132,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372986</v>
+        <v>124372460</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7177,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496526</v>
+        <v>496311</v>
       </c>
       <c r="R58" t="n">
-        <v>7018886</v>
+        <v>7018869</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7244,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124373091</v>
+        <v>124372196</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7289,13 +7255,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496553</v>
+        <v>496444</v>
       </c>
       <c r="R59" t="n">
-        <v>7018888</v>
+        <v>7018877</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7322,14 +7288,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7340,6 +7316,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7356,7 +7357,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372714</v>
+        <v>124373047</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7401,10 +7402,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496416</v>
+        <v>496551</v>
       </c>
       <c r="R60" t="n">
-        <v>7018877</v>
+        <v>7018894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7468,7 +7469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376085</v>
+        <v>124372868</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7513,10 +7514,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496204</v>
+        <v>496485</v>
       </c>
       <c r="R61" t="n">
-        <v>7018992</v>
+        <v>7018881</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7580,7 +7581,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124373122</v>
+        <v>124372714</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7625,10 +7626,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496571</v>
+        <v>496416</v>
       </c>
       <c r="R62" t="n">
-        <v>7018892</v>
+        <v>7018877</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7692,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372460</v>
+        <v>124372213</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7737,10 +7738,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496311</v>
+        <v>496392</v>
       </c>
       <c r="R63" t="n">
-        <v>7018869</v>
+        <v>7018866</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7804,7 +7805,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372184</v>
+        <v>124372810</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7849,10 +7850,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496392</v>
+        <v>496460</v>
       </c>
       <c r="R64" t="n">
-        <v>7018873</v>
+        <v>7018885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7916,7 +7917,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372949</v>
+        <v>124372778</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7961,10 +7962,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496504</v>
+        <v>496426</v>
       </c>
       <c r="R65" t="n">
-        <v>7018879</v>
+        <v>7018876</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8028,7 +8029,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372343</v>
+        <v>124372184</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8073,10 +8074,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496345</v>
+        <v>496392</v>
       </c>
       <c r="R66" t="n">
-        <v>7018866</v>
+        <v>7018873</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8252,7 +8253,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372196</v>
+        <v>124372234</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8297,13 +8298,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496444</v>
+        <v>496384</v>
       </c>
       <c r="R68" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8330,24 +8331,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8358,31 +8349,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8399,7 +8365,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372234</v>
+        <v>124372343</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8444,10 +8410,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496384</v>
+        <v>496345</v>
       </c>
       <c r="R69" t="n">
-        <v>7018864</v>
+        <v>7018866</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8511,7 +8477,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372891</v>
+        <v>124372353</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8556,10 +8522,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496487</v>
+        <v>496338</v>
       </c>
       <c r="R70" t="n">
-        <v>7018890</v>
+        <v>7018864</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8735,7 +8701,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373030</v>
+        <v>124373102</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8780,10 +8746,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496538</v>
+        <v>496574</v>
       </c>
       <c r="R72" t="n">
-        <v>7018895</v>
+        <v>7018897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8847,7 +8813,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372810</v>
+        <v>124373091</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8892,10 +8858,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496460</v>
+        <v>496553</v>
       </c>
       <c r="R73" t="n">
-        <v>7018885</v>
+        <v>7018888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8959,7 +8925,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372778</v>
+        <v>124373122</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -9004,10 +8970,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496426</v>
+        <v>496571</v>
       </c>
       <c r="R74" t="n">
-        <v>7018876</v>
+        <v>7018892</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9071,7 +9037,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372353</v>
+        <v>124372826</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9116,10 +9082,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496338</v>
+        <v>496446</v>
       </c>
       <c r="R75" t="n">
-        <v>7018864</v>
+        <v>7018884</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9183,14 +9149,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372169</v>
+        <v>124366868</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9216,10 +9182,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9228,10 +9213,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496446</v>
+        <v>496023</v>
       </c>
       <c r="R76" t="n">
-        <v>7018897</v>
+        <v>7018919</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9261,14 +9246,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9279,6 +9274,11 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9295,7 +9295,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372291</v>
+        <v>124372406</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9331,7 +9331,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496371</v>
+        <v>496324</v>
       </c>
       <c r="R77" t="n">
-        <v>7018862</v>
+        <v>7018859</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9407,7 +9407,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124373047</v>
+        <v>124372949</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496551</v>
+        <v>496504</v>
       </c>
       <c r="R78" t="n">
-        <v>7018894</v>
+        <v>7018879</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372406</v>
+        <v>124376085</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9564,10 +9564,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496324</v>
+        <v>496204</v>
       </c>
       <c r="R79" t="n">
-        <v>7018859</v>
+        <v>7018992</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9631,7 +9631,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372213</v>
+        <v>124372906</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496392</v>
+        <v>496496</v>
       </c>
       <c r="R80" t="n">
-        <v>7018866</v>
+        <v>7018887</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124373102</v>
+        <v>124372891</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496574</v>
+        <v>496487</v>
       </c>
       <c r="R82" t="n">
-        <v>7018897</v>
+        <v>7018890</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372868</v>
+        <v>124373030</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496485</v>
+        <v>496538</v>
       </c>
       <c r="R83" t="n">
-        <v>7018881</v>
+        <v>7018895</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372826</v>
+        <v>124372291</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10155,7 +10155,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496446</v>
+        <v>496371</v>
       </c>
       <c r="R84" t="n">
-        <v>7018884</v>
+        <v>7018862</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -3814,10 +3814,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124373649</v>
+        <v>124369665</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>91008</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3826,46 +3826,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496649</v>
+        <v>496219</v>
       </c>
       <c r="R28" t="n">
-        <v>7018995</v>
+        <v>7018883</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3892,21 +3887,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3915,11 +3900,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3936,10 +3916,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365230</v>
+        <v>124367876</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3952,21 +3932,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3976,10 +3956,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496029</v>
+        <v>496096</v>
       </c>
       <c r="R29" t="n">
-        <v>7018962</v>
+        <v>7018871</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4038,10 +4018,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369665</v>
+        <v>124371845</v>
       </c>
       <c r="B30" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4054,21 +4034,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4078,10 +4058,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496219</v>
+        <v>496327</v>
       </c>
       <c r="R30" t="n">
-        <v>7018883</v>
+        <v>7018893</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4140,10 +4120,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124371845</v>
+        <v>124373649</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4152,41 +4132,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496327</v>
+        <v>496649</v>
       </c>
       <c r="R31" t="n">
-        <v>7018893</v>
+        <v>7018995</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4213,11 +4198,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4226,6 +4221,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4242,10 +4242,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124367876</v>
+        <v>124365230</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4258,21 +4258,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496096</v>
+        <v>496029</v>
       </c>
       <c r="R32" t="n">
-        <v>7018871</v>
+        <v>7018962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124371804</v>
+        <v>124369222</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496319</v>
+        <v>496155</v>
       </c>
       <c r="R36" t="n">
-        <v>7018893</v>
+        <v>7018842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124369222</v>
+        <v>124371804</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496155</v>
+        <v>496319</v>
       </c>
       <c r="R37" t="n">
-        <v>7018842</v>
+        <v>7018893</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372714</v>
+        <v>124372213</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496416</v>
+        <v>496392</v>
       </c>
       <c r="R62" t="n">
-        <v>7018877</v>
+        <v>7018866</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372213</v>
+        <v>124372714</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496392</v>
+        <v>496416</v>
       </c>
       <c r="R63" t="n">
-        <v>7018866</v>
+        <v>7018877</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374980</v>
+        <v>124370431</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>74901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496356</v>
+        <v>496343</v>
       </c>
       <c r="R2" t="n">
-        <v>7018988</v>
+        <v>7018868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368930</v>
+        <v>124368893</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496185</v>
+        <v>496152</v>
       </c>
       <c r="R3" t="n">
-        <v>7018934</v>
+        <v>7018906</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,21 +850,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,31 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374892</v>
+        <v>124370135</v>
       </c>
       <c r="B4" t="n">
         <v>91012</v>
@@ -964,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496365</v>
+        <v>496395</v>
       </c>
       <c r="R4" t="n">
-        <v>7018964</v>
+        <v>7018910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375105</v>
+        <v>124374413</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496343</v>
+        <v>496449</v>
       </c>
       <c r="R5" t="n">
-        <v>7018997</v>
+        <v>7018988</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,21 +1054,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1122,31 +1067,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124365032</v>
+        <v>124372052</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496041</v>
+        <v>496397</v>
       </c>
       <c r="R6" t="n">
-        <v>7018962</v>
+        <v>7018931</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,9 +1156,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124364937</v>
+        <v>124369981</v>
       </c>
       <c r="B7" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496075</v>
+        <v>496293</v>
       </c>
       <c r="R7" t="n">
-        <v>7018977</v>
+        <v>7018882</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,11 +1268,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,6 +1291,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124373902</v>
+        <v>124372203</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496634</v>
+        <v>496503</v>
       </c>
       <c r="R8" t="n">
-        <v>7019012</v>
+        <v>7018898</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124368893</v>
+        <v>124368788</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496152</v>
+        <v>496168</v>
       </c>
       <c r="R9" t="n">
         <v>7018906</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,11 +1517,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1565,6 +1540,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124369063</v>
+        <v>124365032</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>96354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,46 +1593,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496203</v>
+        <v>496041</v>
       </c>
       <c r="R10" t="n">
-        <v>7018907</v>
+        <v>7018962</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,21 +1654,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1682,31 +1667,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1723,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124365867</v>
+        <v>124374980</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1763,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496012</v>
+        <v>496356</v>
       </c>
       <c r="R11" t="n">
-        <v>7018928</v>
+        <v>7018988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,9 +1756,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124372203</v>
+        <v>124365230</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496503</v>
+        <v>496029</v>
       </c>
       <c r="R12" t="n">
-        <v>7018898</v>
+        <v>7018962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,19 +1868,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,19 +1885,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124369981</v>
+        <v>124366230</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1971,16 +1931,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496293</v>
+        <v>495918</v>
       </c>
       <c r="R13" t="n">
-        <v>7018882</v>
+        <v>7018928</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2012,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +1987,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124370557</v>
+        <v>124369957</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,48 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496338</v>
+        <v>496287</v>
       </c>
       <c r="R14" t="n">
-        <v>7018951</v>
+        <v>7018882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2190,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124367848</v>
+        <v>124371804</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2230,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496067</v>
+        <v>496319</v>
       </c>
       <c r="R15" t="n">
-        <v>7018881</v>
+        <v>7018893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,21 +2219,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2286,31 +2232,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2327,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374769</v>
+        <v>124367876</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2339,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,13 +2288,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496465</v>
+        <v>496096</v>
       </c>
       <c r="R16" t="n">
-        <v>7018933</v>
+        <v>7018871</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2400,21 +2321,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2423,31 +2334,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2464,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124366502</v>
+        <v>124364887</v>
       </c>
       <c r="B17" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2504,13 +2390,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495918</v>
+        <v>496078</v>
       </c>
       <c r="R17" t="n">
-        <v>7018925</v>
+        <v>7018964</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2537,21 +2423,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2560,31 +2436,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2601,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124366230</v>
+        <v>124372694</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,42 +2468,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495918</v>
+        <v>496555</v>
       </c>
       <c r="R18" t="n">
-        <v>7018928</v>
+        <v>7018901</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,12 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,51 +2548,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124368223</v>
+        <v>124366461</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2760,41 +2576,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496103</v>
+        <v>495944</v>
       </c>
       <c r="R19" t="n">
-        <v>7018878</v>
+        <v>7018967</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2821,11 +2647,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2834,6 +2670,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2850,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124366031</v>
+        <v>124366502</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>79795</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495986</v>
+        <v>495918</v>
       </c>
       <c r="R20" t="n">
-        <v>7018958</v>
+        <v>7018925</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2923,11 +2764,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2936,6 +2787,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2952,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124373203</v>
+        <v>124375041</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,21 +2844,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2992,13 +2868,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496570</v>
+        <v>496343</v>
       </c>
       <c r="R21" t="n">
-        <v>7018914</v>
+        <v>7018997</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3025,21 +2901,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3048,31 +2914,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3089,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124375158</v>
+        <v>124369222</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3101,55 +2942,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496311</v>
+        <v>496155</v>
       </c>
       <c r="R22" t="n">
-        <v>7018994</v>
+        <v>7018842</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3176,21 +3003,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3199,11 +3016,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3220,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124375411</v>
+        <v>124373902</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3232,60 +3044,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496320</v>
+        <v>496634</v>
       </c>
       <c r="R23" t="n">
-        <v>7018988</v>
+        <v>7019012</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3314,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3324,12 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3340,31 +3128,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124364887</v>
+        <v>124375158</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3373,41 +3156,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496078</v>
+        <v>496311</v>
       </c>
       <c r="R24" t="n">
-        <v>7018964</v>
+        <v>7018994</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3434,11 +3231,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3447,6 +3254,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3463,10 +3275,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124368130</v>
+        <v>124370553</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3475,41 +3287,60 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496089</v>
+        <v>496283</v>
       </c>
       <c r="R25" t="n">
-        <v>7018863</v>
+        <v>7018896</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3536,11 +3367,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3549,6 +3395,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3565,10 +3416,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365253</v>
+        <v>124369001</v>
       </c>
       <c r="B26" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3577,43 +3428,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496029</v>
+        <v>496205</v>
       </c>
       <c r="R26" t="n">
-        <v>7018921</v>
+        <v>7018858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3643,21 +3489,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3666,11 +3502,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3687,10 +3518,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124366461</v>
+        <v>124365832</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3699,51 +3530,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495944</v>
+        <v>496020</v>
       </c>
       <c r="R27" t="n">
-        <v>7018967</v>
+        <v>7018936</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3770,21 +3591,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3793,11 +3604,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3814,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369665</v>
+        <v>124368223</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3830,21 +3636,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3854,10 +3660,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496219</v>
+        <v>496103</v>
       </c>
       <c r="R28" t="n">
-        <v>7018883</v>
+        <v>7018878</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3916,10 +3722,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124367876</v>
+        <v>124365867</v>
       </c>
       <c r="B29" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3928,25 +3734,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3956,10 +3762,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496096</v>
+        <v>496012</v>
       </c>
       <c r="R29" t="n">
-        <v>7018871</v>
+        <v>7018928</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4018,10 +3824,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124371845</v>
+        <v>124369822</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4034,21 +3840,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4058,10 +3864,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496327</v>
+        <v>496245</v>
       </c>
       <c r="R30" t="n">
-        <v>7018893</v>
+        <v>7018876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4120,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124373649</v>
+        <v>124375602</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4132,46 +3938,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496649</v>
+        <v>496297</v>
       </c>
       <c r="R31" t="n">
-        <v>7018995</v>
+        <v>7018948</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4200,7 +4001,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4210,7 +4011,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4225,6 +4026,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4242,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365230</v>
+        <v>124365439</v>
       </c>
       <c r="B32" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4254,25 +4075,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4285,7 +4106,7 @@
         <v>496029</v>
       </c>
       <c r="R32" t="n">
-        <v>7018962</v>
+        <v>7018964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4344,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365832</v>
+        <v>124373203</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4360,21 +4181,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4384,13 +4205,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496020</v>
+        <v>496570</v>
       </c>
       <c r="R33" t="n">
-        <v>7018936</v>
+        <v>7018914</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4417,11 +4238,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4430,6 +4261,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4446,10 +4302,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124375665</v>
+        <v>124374892</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4458,25 +4314,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4486,10 +4342,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496298</v>
+        <v>496365</v>
       </c>
       <c r="R34" t="n">
-        <v>7018981</v>
+        <v>7018964</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4519,24 +4375,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4551,22 +4392,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124375602</v>
+        <v>124365253</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4575,41 +4416,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496297</v>
+        <v>496029</v>
       </c>
       <c r="R35" t="n">
-        <v>7018948</v>
+        <v>7018921</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4638,7 +4484,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4648,7 +4494,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4663,26 +4509,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4700,7 +4526,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124369222</v>
+        <v>124366246</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4740,10 +4566,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496155</v>
+        <v>496045</v>
       </c>
       <c r="R36" t="n">
-        <v>7018842</v>
+        <v>7018931</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4628,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124371804</v>
+        <v>124368130</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4842,10 +4668,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496319</v>
+        <v>496089</v>
       </c>
       <c r="R37" t="n">
-        <v>7018893</v>
+        <v>7018863</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4904,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124365804</v>
+        <v>124371845</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4920,21 +4746,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4944,10 +4770,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496020</v>
+        <v>496327</v>
       </c>
       <c r="R38" t="n">
-        <v>7018934</v>
+        <v>7018893</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5006,10 +4832,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124372694</v>
+        <v>124367848</v>
       </c>
       <c r="B39" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5022,21 +4848,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5046,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496555</v>
+        <v>496067</v>
       </c>
       <c r="R39" t="n">
-        <v>7018901</v>
+        <v>7018881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5081,7 +4907,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5091,7 +4917,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5102,26 +4928,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124367729</v>
+        <v>124368930</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5134,21 +4985,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5158,13 +5009,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496047</v>
+        <v>496185</v>
       </c>
       <c r="R40" t="n">
-        <v>7018892</v>
+        <v>7018934</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5191,11 +5042,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5204,6 +5065,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5220,7 +5106,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124369822</v>
+        <v>124365917</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5254,16 +5140,21 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496245</v>
+        <v>496005</v>
       </c>
       <c r="R41" t="n">
-        <v>7018876</v>
+        <v>7018959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5322,10 +5213,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124370135</v>
+        <v>124369063</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5334,41 +5225,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496395</v>
+        <v>496203</v>
       </c>
       <c r="R42" t="n">
-        <v>7018910</v>
+        <v>7018907</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5395,11 +5291,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5408,6 +5314,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5424,10 +5355,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124365917</v>
+        <v>124375665</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5436,43 +5367,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496005</v>
+        <v>496298</v>
       </c>
       <c r="R43" t="n">
-        <v>7018959</v>
+        <v>7018981</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5502,9 +5428,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5519,19 +5460,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124372052</v>
+        <v>124374769</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5571,13 +5512,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496397</v>
+        <v>496465</v>
       </c>
       <c r="R44" t="n">
-        <v>7018931</v>
+        <v>7018933</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5606,7 +5547,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5616,7 +5557,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5627,26 +5568,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374413</v>
+        <v>124364937</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5659,21 +5625,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5683,10 +5649,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496449</v>
+        <v>496075</v>
       </c>
       <c r="R45" t="n">
-        <v>7018988</v>
+        <v>7018977</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5745,10 +5711,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375041</v>
+        <v>124373649</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5757,41 +5723,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496343</v>
+        <v>496649</v>
       </c>
       <c r="R46" t="n">
-        <v>7018997</v>
+        <v>7018995</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5818,11 +5789,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5831,6 +5812,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5847,10 +5833,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124368504</v>
+        <v>124367729</v>
       </c>
       <c r="B47" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5863,21 +5849,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5887,10 +5873,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496112</v>
+        <v>496047</v>
       </c>
       <c r="R47" t="n">
-        <v>7018885</v>
+        <v>7018892</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5949,10 +5935,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124369957</v>
+        <v>124375105</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5965,21 +5951,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5989,13 +5975,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496287</v>
+        <v>496343</v>
       </c>
       <c r="R48" t="n">
-        <v>7018882</v>
+        <v>7018997</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6022,11 +6008,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6035,6 +6031,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6051,7 +6072,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124368788</v>
+        <v>124365804</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -6091,13 +6112,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496168</v>
+        <v>496020</v>
       </c>
       <c r="R49" t="n">
-        <v>7018906</v>
+        <v>7018934</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6124,21 +6145,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6147,31 +6158,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6188,10 +6174,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124365439</v>
+        <v>124368504</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6204,21 +6190,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6228,10 +6214,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496029</v>
+        <v>496112</v>
       </c>
       <c r="R50" t="n">
-        <v>7018964</v>
+        <v>7018885</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6290,10 +6276,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124366246</v>
+        <v>124370557</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6306,34 +6292,48 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496045</v>
+        <v>496338</v>
       </c>
       <c r="R51" t="n">
-        <v>7018931</v>
+        <v>7018951</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124374616</v>
+        <v>124375411</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6404,41 +6404,60 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496506</v>
+        <v>496320</v>
       </c>
       <c r="R52" t="n">
-        <v>7018942</v>
+        <v>7018988</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6467,7 +6486,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6477,7 +6496,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6492,26 +6516,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6529,10 +6533,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124369001</v>
+        <v>124374616</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6545,21 +6549,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6569,13 +6573,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496205</v>
+        <v>496506</v>
       </c>
       <c r="R53" t="n">
-        <v>7018858</v>
+        <v>7018942</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6602,11 +6606,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6615,6 +6629,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6631,10 +6670,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124370431</v>
+        <v>124369665</v>
       </c>
       <c r="B54" t="n">
-        <v>74901</v>
+        <v>91008</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6647,21 +6686,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6671,10 +6710,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496343</v>
+        <v>496219</v>
       </c>
       <c r="R54" t="n">
-        <v>7018868</v>
+        <v>7018883</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6733,10 +6772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124370553</v>
+        <v>124366031</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>90962</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6745,60 +6784,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496283</v>
+        <v>495986</v>
       </c>
       <c r="R55" t="n">
-        <v>7018896</v>
+        <v>7018958</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6825,26 +6845,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6853,11 +6858,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6874,14 +6874,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372169</v>
+        <v>124366868</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6907,10 +6907,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6919,10 +6938,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496446</v>
+        <v>496023</v>
       </c>
       <c r="R56" t="n">
-        <v>7018897</v>
+        <v>7018919</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6952,14 +6971,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6970,6 +6999,11 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6986,7 +7020,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372986</v>
+        <v>124373142</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7025,16 +7059,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496526</v>
+        <v>496560</v>
       </c>
       <c r="R57" t="n">
-        <v>7018886</v>
+        <v>7018917</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7064,14 +7103,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7082,6 +7131,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7098,7 +7172,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372460</v>
+        <v>124372986</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7143,10 +7217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496311</v>
+        <v>496526</v>
       </c>
       <c r="R58" t="n">
-        <v>7018869</v>
+        <v>7018886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,7 +7284,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372196</v>
+        <v>124372234</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,13 +7329,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496444</v>
+        <v>496384</v>
       </c>
       <c r="R59" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7288,24 +7362,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7316,31 +7380,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7357,7 +7396,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124373047</v>
+        <v>124372169</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7402,10 +7441,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496551</v>
+        <v>496446</v>
       </c>
       <c r="R60" t="n">
-        <v>7018894</v>
+        <v>7018897</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7469,7 +7508,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372868</v>
+        <v>124372778</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7514,10 +7553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496485</v>
+        <v>496426</v>
       </c>
       <c r="R61" t="n">
-        <v>7018881</v>
+        <v>7018876</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7581,7 +7620,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372213</v>
+        <v>124372906</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7626,10 +7665,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496392</v>
+        <v>496496</v>
       </c>
       <c r="R62" t="n">
-        <v>7018866</v>
+        <v>7018887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7693,7 +7732,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372714</v>
+        <v>124373122</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7738,10 +7777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496416</v>
+        <v>496571</v>
       </c>
       <c r="R63" t="n">
-        <v>7018877</v>
+        <v>7018892</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7805,7 +7844,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372810</v>
+        <v>124372382</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7850,10 +7889,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496460</v>
+        <v>496322</v>
       </c>
       <c r="R64" t="n">
-        <v>7018885</v>
+        <v>7018864</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7917,7 +7956,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372778</v>
+        <v>124373102</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7962,10 +8001,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496426</v>
+        <v>496574</v>
       </c>
       <c r="R65" t="n">
-        <v>7018876</v>
+        <v>7018897</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8029,7 +8068,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372184</v>
+        <v>124372196</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8074,13 +8113,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496392</v>
+        <v>496444</v>
       </c>
       <c r="R66" t="n">
-        <v>7018873</v>
+        <v>7018877</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8107,14 +8146,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8125,6 +8174,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8141,7 +8215,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372245</v>
+        <v>124372406</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8186,10 +8260,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496380</v>
+        <v>496324</v>
       </c>
       <c r="R67" t="n">
-        <v>7018867</v>
+        <v>7018859</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8253,7 +8327,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372234</v>
+        <v>124372868</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8298,10 +8372,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496384</v>
+        <v>496485</v>
       </c>
       <c r="R68" t="n">
-        <v>7018864</v>
+        <v>7018881</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8365,7 +8439,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372343</v>
+        <v>124372353</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8410,10 +8484,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496345</v>
+        <v>496338</v>
       </c>
       <c r="R69" t="n">
-        <v>7018866</v>
+        <v>7018864</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8477,7 +8551,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372353</v>
+        <v>124373030</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8522,10 +8596,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496338</v>
+        <v>496538</v>
       </c>
       <c r="R70" t="n">
-        <v>7018864</v>
+        <v>7018895</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8589,7 +8663,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372382</v>
+        <v>124373091</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8634,10 +8708,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496322</v>
+        <v>496553</v>
       </c>
       <c r="R71" t="n">
-        <v>7018864</v>
+        <v>7018888</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8701,7 +8775,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373102</v>
+        <v>124372184</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8746,10 +8820,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496574</v>
+        <v>496392</v>
       </c>
       <c r="R72" t="n">
-        <v>7018897</v>
+        <v>7018873</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8813,7 +8887,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124373091</v>
+        <v>124372245</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8858,10 +8932,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496553</v>
+        <v>496380</v>
       </c>
       <c r="R73" t="n">
-        <v>7018888</v>
+        <v>7018867</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8925,7 +8999,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124373122</v>
+        <v>124372213</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -8970,10 +9044,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496571</v>
+        <v>496392</v>
       </c>
       <c r="R74" t="n">
-        <v>7018892</v>
+        <v>7018866</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9149,14 +9223,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124366868</v>
+        <v>124372460</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9182,29 +9256,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9213,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496023</v>
+        <v>496311</v>
       </c>
       <c r="R76" t="n">
-        <v>7018919</v>
+        <v>7018869</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9246,24 +9301,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9274,11 +9319,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9295,7 +9335,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372406</v>
+        <v>124372949</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9340,10 +9380,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496324</v>
+        <v>496504</v>
       </c>
       <c r="R77" t="n">
-        <v>7018859</v>
+        <v>7018879</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9407,7 +9447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372949</v>
+        <v>124372810</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9452,10 +9492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496504</v>
+        <v>496460</v>
       </c>
       <c r="R78" t="n">
-        <v>7018879</v>
+        <v>7018885</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9519,7 +9559,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124376085</v>
+        <v>124372714</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9564,10 +9604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496204</v>
+        <v>496416</v>
       </c>
       <c r="R79" t="n">
-        <v>7018992</v>
+        <v>7018877</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9631,7 +9671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372906</v>
+        <v>124372291</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9667,7 +9707,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9676,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496496</v>
+        <v>496371</v>
       </c>
       <c r="R80" t="n">
-        <v>7018887</v>
+        <v>7018862</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9743,7 +9783,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124373142</v>
+        <v>124373047</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9782,21 +9822,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496560</v>
+        <v>496551</v>
       </c>
       <c r="R81" t="n">
-        <v>7018917</v>
+        <v>7018894</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9826,24 +9861,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9854,31 +9879,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372891</v>
+        <v>124376085</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496487</v>
+        <v>496204</v>
       </c>
       <c r="R82" t="n">
-        <v>7018890</v>
+        <v>7018992</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124373030</v>
+        <v>124372343</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496538</v>
+        <v>496345</v>
       </c>
       <c r="R83" t="n">
-        <v>7018895</v>
+        <v>7018866</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372291</v>
+        <v>124372891</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10155,7 +10155,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496371</v>
+        <v>496487</v>
       </c>
       <c r="R84" t="n">
-        <v>7018862</v>
+        <v>7018890</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124367876</v>
+        <v>124372694</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496096</v>
+        <v>496555</v>
       </c>
       <c r="R16" t="n">
-        <v>7018871</v>
+        <v>7018901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,9 +2321,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,22 +2348,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124364887</v>
+        <v>124367876</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,25 +2372,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496078</v>
+        <v>496096</v>
       </c>
       <c r="R17" t="n">
-        <v>7018964</v>
+        <v>7018871</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124372694</v>
+        <v>124364887</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2478,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496555</v>
+        <v>496078</v>
       </c>
       <c r="R18" t="n">
-        <v>7018901</v>
+        <v>7018964</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,19 +2535,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,12 +2552,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124365253</v>
+        <v>124366246</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4416,43 +4416,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496029</v>
+        <v>496045</v>
       </c>
       <c r="R35" t="n">
-        <v>7018921</v>
+        <v>7018931</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4482,21 +4477,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4505,11 +4490,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4526,7 +4506,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124366246</v>
+        <v>124368130</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4566,10 +4546,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496045</v>
+        <v>496089</v>
       </c>
       <c r="R36" t="n">
-        <v>7018931</v>
+        <v>7018863</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4628,7 +4608,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124368130</v>
+        <v>124371845</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4668,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496089</v>
+        <v>496327</v>
       </c>
       <c r="R37" t="n">
-        <v>7018863</v>
+        <v>7018893</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4730,10 +4710,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124371845</v>
+        <v>124365253</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4742,38 +4722,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496327</v>
+        <v>496029</v>
       </c>
       <c r="R38" t="n">
-        <v>7018893</v>
+        <v>7018921</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4803,11 +4788,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4816,6 +4811,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124370431</v>
+        <v>124373649</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496343</v>
+        <v>496649</v>
       </c>
       <c r="R2" t="n">
-        <v>7018868</v>
+        <v>7018995</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +753,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +776,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124368893</v>
+        <v>124374769</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496152</v>
+        <v>496465</v>
       </c>
       <c r="R3" t="n">
-        <v>7018906</v>
+        <v>7018933</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,11 +870,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124370135</v>
+        <v>124365917</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +950,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496395</v>
+        <v>496005</v>
       </c>
       <c r="R4" t="n">
-        <v>7018910</v>
+        <v>7018959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374413</v>
+        <v>124373902</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1053,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496449</v>
+        <v>496634</v>
       </c>
       <c r="R5" t="n">
-        <v>7018988</v>
+        <v>7019012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1114,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124372052</v>
+        <v>124371845</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496397</v>
+        <v>496327</v>
       </c>
       <c r="R6" t="n">
-        <v>7018931</v>
+        <v>7018893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,19 +1226,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,19 +1243,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124369981</v>
+        <v>124375602</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1235,13 +1295,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496293</v>
+        <v>496297</v>
       </c>
       <c r="R7" t="n">
-        <v>7018882</v>
+        <v>7018948</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124372203</v>
+        <v>124369063</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,41 +1404,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496503</v>
+        <v>496203</v>
       </c>
       <c r="R8" t="n">
-        <v>7018898</v>
+        <v>7018907</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,26 +1493,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124368788</v>
+        <v>124366502</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,25 +1546,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1574,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496168</v>
+        <v>495918</v>
       </c>
       <c r="R9" t="n">
-        <v>7018906</v>
+        <v>7018925</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1638,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1581,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124365032</v>
+        <v>124368930</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1687,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,13 +1711,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496041</v>
+        <v>496185</v>
       </c>
       <c r="R10" t="n">
-        <v>7018962</v>
+        <v>7018934</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,11 +1744,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1667,6 +1767,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1683,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374980</v>
+        <v>124374616</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1824,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1848,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496356</v>
+        <v>496506</v>
       </c>
       <c r="R11" t="n">
-        <v>7018988</v>
+        <v>7018942</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1883,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1893,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,26 +1904,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124365230</v>
+        <v>124367876</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1961,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496029</v>
+        <v>496096</v>
       </c>
       <c r="R12" t="n">
-        <v>7018962</v>
+        <v>7018871</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124366230</v>
+        <v>124374892</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,42 +2063,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495918</v>
+        <v>496365</v>
       </c>
       <c r="R13" t="n">
-        <v>7018928</v>
+        <v>7018964</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,26 +2120,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2003,31 +2133,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2044,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124369957</v>
+        <v>124374413</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -2084,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496287</v>
+        <v>496449</v>
       </c>
       <c r="R14" t="n">
-        <v>7018882</v>
+        <v>7018988</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,10 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124371804</v>
+        <v>124365804</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2267,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2291,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496319</v>
+        <v>496020</v>
       </c>
       <c r="R15" t="n">
-        <v>7018893</v>
+        <v>7018934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124372694</v>
+        <v>124364937</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2369,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2393,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496555</v>
+        <v>496075</v>
       </c>
       <c r="R16" t="n">
-        <v>7018901</v>
+        <v>7018977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,19 +2426,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>19:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,22 +2443,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124367876</v>
+        <v>124365867</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,25 +2467,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2495,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496096</v>
+        <v>496012</v>
       </c>
       <c r="R17" t="n">
-        <v>7018871</v>
+        <v>7018928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,7 +2557,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124364887</v>
+        <v>124368130</v>
       </c>
       <c r="B18" t="n">
         <v>91012</v>
@@ -2502,10 +2597,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496078</v>
+        <v>496089</v>
       </c>
       <c r="R18" t="n">
-        <v>7018964</v>
+        <v>7018863</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124366461</v>
+        <v>124369001</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,51 +2671,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495944</v>
+        <v>496205</v>
       </c>
       <c r="R19" t="n">
-        <v>7018967</v>
+        <v>7018858</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2647,21 +2732,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2670,11 +2745,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2691,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124366502</v>
+        <v>124367729</v>
       </c>
       <c r="B20" t="n">
-        <v>79795</v>
+        <v>74901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2773,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,13 +2801,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495918</v>
+        <v>496047</v>
       </c>
       <c r="R20" t="n">
-        <v>7018925</v>
+        <v>7018892</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2764,21 +2834,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2787,31 +2847,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2828,10 +2863,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375041</v>
+        <v>124373203</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,21 +2879,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,13 +2903,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496343</v>
+        <v>496570</v>
       </c>
       <c r="R21" t="n">
-        <v>7018997</v>
+        <v>7018914</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2901,11 +2936,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2914,6 +2959,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2930,10 +3000,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124369222</v>
+        <v>124372052</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,21 +3016,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,10 +3040,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496155</v>
+        <v>496397</v>
       </c>
       <c r="R22" t="n">
-        <v>7018842</v>
+        <v>7018931</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,9 +3073,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,22 +3100,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124373902</v>
+        <v>124370557</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>56714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,38 +3124,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496634</v>
+        <v>496338</v>
       </c>
       <c r="R23" t="n">
-        <v>7019012</v>
+        <v>7018951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3105,19 +3199,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,22 +3216,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375158</v>
+        <v>124369222</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,55 +3240,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496311</v>
+        <v>496155</v>
       </c>
       <c r="R24" t="n">
-        <v>7018994</v>
+        <v>7018842</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,21 +3301,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3254,11 +3314,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3275,10 +3330,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370553</v>
+        <v>124365439</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,60 +3342,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496283</v>
+        <v>496029</v>
       </c>
       <c r="R25" t="n">
-        <v>7018896</v>
+        <v>7018964</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3367,26 +3403,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3395,11 +3416,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3416,7 +3432,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369001</v>
+        <v>124375041</v>
       </c>
       <c r="B26" t="n">
         <v>91012</v>
@@ -3456,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496205</v>
+        <v>496343</v>
       </c>
       <c r="R26" t="n">
-        <v>7018858</v>
+        <v>7018997</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3518,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124365832</v>
+        <v>124369957</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,21 +3550,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3558,10 +3574,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496020</v>
+        <v>496287</v>
       </c>
       <c r="R27" t="n">
-        <v>7018936</v>
+        <v>7018882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3620,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124368223</v>
+        <v>124371804</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3636,21 +3652,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3660,10 +3676,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496103</v>
+        <v>496319</v>
       </c>
       <c r="R28" t="n">
-        <v>7018878</v>
+        <v>7018893</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3722,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124365867</v>
+        <v>124368788</v>
       </c>
       <c r="B29" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,21 +3754,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3762,13 +3778,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496012</v>
+        <v>496168</v>
       </c>
       <c r="R29" t="n">
-        <v>7018928</v>
+        <v>7018906</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3795,11 +3811,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3808,6 +3834,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3824,10 +3875,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369822</v>
+        <v>124374980</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3840,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3864,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496245</v>
+        <v>496356</v>
       </c>
       <c r="R30" t="n">
-        <v>7018876</v>
+        <v>7018988</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,9 +3948,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3914,19 +3975,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124375602</v>
+        <v>124366230</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3960,19 +4021,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496297</v>
+        <v>495918</v>
       </c>
       <c r="R31" t="n">
-        <v>7018948</v>
+        <v>7018928</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4001,7 +4067,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4011,7 +4077,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4063,10 +4134,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124365439</v>
+        <v>124372694</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,21 +4150,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4103,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496029</v>
+        <v>496555</v>
       </c>
       <c r="R32" t="n">
-        <v>7018964</v>
+        <v>7018901</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,9 +4207,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4153,22 +4234,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124373203</v>
+        <v>124365832</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,21 +4262,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4205,13 +4286,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496570</v>
+        <v>496020</v>
       </c>
       <c r="R33" t="n">
-        <v>7018914</v>
+        <v>7018936</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4238,21 +4319,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4261,31 +4332,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4302,10 +4348,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374892</v>
+        <v>124366461</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4314,41 +4360,51 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496365</v>
+        <v>495944</v>
       </c>
       <c r="R34" t="n">
-        <v>7018964</v>
+        <v>7018967</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4375,11 +4431,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4388,6 +4454,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4404,10 +4475,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124366246</v>
+        <v>124365032</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4420,21 +4491,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4444,10 +4515,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496045</v>
+        <v>496041</v>
       </c>
       <c r="R35" t="n">
-        <v>7018931</v>
+        <v>7018962</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4506,10 +4577,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124368130</v>
+        <v>124375411</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4518,41 +4589,60 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496089</v>
+        <v>496320</v>
       </c>
       <c r="R36" t="n">
-        <v>7018863</v>
+        <v>7018988</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4579,11 +4669,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4592,6 +4697,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4608,10 +4718,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124371845</v>
+        <v>124367848</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4624,21 +4734,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4758,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496327</v>
+        <v>496067</v>
       </c>
       <c r="R37" t="n">
-        <v>7018893</v>
+        <v>7018881</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,11 +4791,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4694,6 +4814,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4710,10 +4855,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124365253</v>
+        <v>124368504</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4722,43 +4867,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496029</v>
+        <v>496112</v>
       </c>
       <c r="R38" t="n">
-        <v>7018921</v>
+        <v>7018885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4788,21 +4928,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4811,11 +4941,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4832,10 +4957,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124367848</v>
+        <v>124368893</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4848,21 +4973,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4872,10 +4997,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496067</v>
+        <v>496152</v>
       </c>
       <c r="R39" t="n">
-        <v>7018881</v>
+        <v>7018906</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4905,21 +5030,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4928,31 +5043,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4969,10 +5059,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124368930</v>
+        <v>124369665</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4985,21 +5075,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5009,13 +5099,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496185</v>
+        <v>496219</v>
       </c>
       <c r="R40" t="n">
-        <v>7018934</v>
+        <v>7018883</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5042,21 +5132,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5065,31 +5145,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5106,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124365917</v>
+        <v>124375665</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5118,43 +5173,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496005</v>
+        <v>496298</v>
       </c>
       <c r="R41" t="n">
-        <v>7018959</v>
+        <v>7018981</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5184,9 +5234,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5201,22 +5266,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124369063</v>
+        <v>124365230</v>
       </c>
       <c r="B42" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5229,42 +5294,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496203</v>
+        <v>496029</v>
       </c>
       <c r="R42" t="n">
-        <v>7018907</v>
+        <v>7018962</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5291,21 +5351,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5314,31 +5364,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5355,10 +5380,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375665</v>
+        <v>124370135</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5367,25 +5392,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5395,10 +5420,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496298</v>
+        <v>496395</v>
       </c>
       <c r="R43" t="n">
-        <v>7018981</v>
+        <v>7018910</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5428,24 +5453,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5460,22 +5470,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124374769</v>
+        <v>124364887</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5488,21 +5498,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5512,13 +5522,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496465</v>
+        <v>496078</v>
       </c>
       <c r="R44" t="n">
-        <v>7018933</v>
+        <v>7018964</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5545,21 +5555,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5568,31 +5568,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5609,10 +5584,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124364937</v>
+        <v>124375105</v>
       </c>
       <c r="B45" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5625,21 +5600,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5649,13 +5624,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496075</v>
+        <v>496343</v>
       </c>
       <c r="R45" t="n">
-        <v>7018977</v>
+        <v>7018997</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5682,11 +5657,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5695,6 +5680,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5711,10 +5721,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124373649</v>
+        <v>124369981</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,43 +5733,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496649</v>
+        <v>496293</v>
       </c>
       <c r="R46" t="n">
-        <v>7018995</v>
+        <v>7018882</v>
       </c>
       <c r="S46" t="n">
         <v>8</v>
@@ -5791,7 +5796,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5801,7 +5806,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,6 +5821,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5833,7 +5858,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124367729</v>
+        <v>124368223</v>
       </c>
       <c r="B47" t="n">
         <v>74901</v>
@@ -5873,10 +5898,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496047</v>
+        <v>496103</v>
       </c>
       <c r="R47" t="n">
-        <v>7018892</v>
+        <v>7018878</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,10 +5960,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124375105</v>
+        <v>124375158</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5947,38 +5972,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496343</v>
+        <v>496311</v>
       </c>
       <c r="R48" t="n">
-        <v>7018997</v>
+        <v>7018994</v>
       </c>
       <c r="S48" t="n">
         <v>7</v>
@@ -6010,7 +6049,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6020,7 +6059,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6035,26 +6074,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6072,10 +6091,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124365804</v>
+        <v>124366246</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6088,21 +6107,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6112,10 +6131,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496020</v>
+        <v>496045</v>
       </c>
       <c r="R49" t="n">
-        <v>7018934</v>
+        <v>7018931</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6174,10 +6193,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124368504</v>
+        <v>124370431</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6190,21 +6209,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6214,10 +6233,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496112</v>
+        <v>496343</v>
       </c>
       <c r="R50" t="n">
-        <v>7018885</v>
+        <v>7018868</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6276,10 +6295,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124370557</v>
+        <v>124369822</v>
       </c>
       <c r="B51" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6292,48 +6311,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496338</v>
+        <v>496245</v>
       </c>
       <c r="R51" t="n">
-        <v>7018951</v>
+        <v>7018876</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6392,10 +6397,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375411</v>
+        <v>124372203</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6404,60 +6409,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496320</v>
+        <v>496503</v>
       </c>
       <c r="R52" t="n">
-        <v>7018988</v>
+        <v>7018898</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6486,7 +6472,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6496,12 +6482,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6512,31 +6493,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124374616</v>
+        <v>124365253</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6545,41 +6521,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496506</v>
+        <v>496029</v>
       </c>
       <c r="R53" t="n">
-        <v>7018942</v>
+        <v>7018921</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6608,7 +6589,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6618,7 +6599,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6633,26 +6614,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6670,10 +6631,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124369665</v>
+        <v>124370553</v>
       </c>
       <c r="B54" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6682,41 +6643,60 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496219</v>
+        <v>496283</v>
       </c>
       <c r="R54" t="n">
-        <v>7018883</v>
+        <v>7018896</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6743,11 +6723,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6756,6 +6751,11 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6874,14 +6874,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124366868</v>
+        <v>124372382</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6907,29 +6907,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6938,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496023</v>
+        <v>496322</v>
       </c>
       <c r="R56" t="n">
-        <v>7018919</v>
+        <v>7018864</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6971,24 +6952,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6999,11 +6970,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7020,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124373142</v>
+        <v>124372826</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7059,21 +7025,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496560</v>
+        <v>496446</v>
       </c>
       <c r="R57" t="n">
-        <v>7018917</v>
+        <v>7018884</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7103,24 +7064,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7131,31 +7082,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7172,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372986</v>
+        <v>124372406</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7217,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496526</v>
+        <v>496324</v>
       </c>
       <c r="R58" t="n">
-        <v>7018886</v>
+        <v>7018859</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7284,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372234</v>
+        <v>124372986</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7329,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496384</v>
+        <v>496526</v>
       </c>
       <c r="R59" t="n">
-        <v>7018864</v>
+        <v>7018886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7508,7 +7434,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372778</v>
+        <v>124372868</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7553,10 +7479,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496426</v>
+        <v>496485</v>
       </c>
       <c r="R61" t="n">
-        <v>7018876</v>
+        <v>7018881</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7620,7 +7546,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372906</v>
+        <v>124373122</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7665,10 +7591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496496</v>
+        <v>496571</v>
       </c>
       <c r="R62" t="n">
-        <v>7018887</v>
+        <v>7018892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7732,7 +7658,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124373122</v>
+        <v>124372949</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7777,10 +7703,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496571</v>
+        <v>496504</v>
       </c>
       <c r="R63" t="n">
-        <v>7018892</v>
+        <v>7018879</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7844,7 +7770,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372382</v>
+        <v>124372213</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7889,10 +7815,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496322</v>
+        <v>496392</v>
       </c>
       <c r="R64" t="n">
-        <v>7018864</v>
+        <v>7018866</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7956,7 +7882,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124373102</v>
+        <v>124373030</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -8001,10 +7927,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496574</v>
+        <v>496538</v>
       </c>
       <c r="R65" t="n">
-        <v>7018897</v>
+        <v>7018895</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8068,7 +7994,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372196</v>
+        <v>124372234</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8113,13 +8039,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496444</v>
+        <v>496384</v>
       </c>
       <c r="R66" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8146,24 +8072,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8174,31 +8090,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8215,7 +8106,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372406</v>
+        <v>124372810</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8260,10 +8151,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496324</v>
+        <v>496460</v>
       </c>
       <c r="R67" t="n">
-        <v>7018859</v>
+        <v>7018885</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8327,7 +8218,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372868</v>
+        <v>124372245</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8372,10 +8263,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496485</v>
+        <v>496380</v>
       </c>
       <c r="R68" t="n">
-        <v>7018881</v>
+        <v>7018867</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8551,7 +8442,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124373030</v>
+        <v>124373091</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8596,10 +8487,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496538</v>
+        <v>496553</v>
       </c>
       <c r="R70" t="n">
-        <v>7018895</v>
+        <v>7018888</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8663,7 +8554,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124373091</v>
+        <v>124376085</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8708,10 +8599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496553</v>
+        <v>496204</v>
       </c>
       <c r="R71" t="n">
-        <v>7018888</v>
+        <v>7018992</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8775,7 +8666,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372184</v>
+        <v>124373142</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8814,16 +8705,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496392</v>
+        <v>496560</v>
       </c>
       <c r="R72" t="n">
-        <v>7018873</v>
+        <v>7018917</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8853,14 +8749,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8871,6 +8777,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8887,7 +8818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372245</v>
+        <v>124372891</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8932,10 +8863,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496380</v>
+        <v>496487</v>
       </c>
       <c r="R73" t="n">
-        <v>7018867</v>
+        <v>7018890</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8999,14 +8930,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372213</v>
+        <v>124366868</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9032,10 +8963,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9044,10 +8994,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496392</v>
+        <v>496023</v>
       </c>
       <c r="R74" t="n">
-        <v>7018866</v>
+        <v>7018919</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9077,14 +9027,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9095,6 +9055,11 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9111,7 +9076,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372826</v>
+        <v>124372196</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9156,13 +9121,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496446</v>
+        <v>496444</v>
       </c>
       <c r="R75" t="n">
-        <v>7018884</v>
+        <v>7018877</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9189,14 +9154,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9207,6 +9182,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9223,7 +9223,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372460</v>
+        <v>124372778</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9268,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496311</v>
+        <v>496426</v>
       </c>
       <c r="R76" t="n">
-        <v>7018869</v>
+        <v>7018876</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372949</v>
+        <v>124372291</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9371,7 +9371,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496504</v>
+        <v>496371</v>
       </c>
       <c r="R77" t="n">
-        <v>7018879</v>
+        <v>7018862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9447,7 +9447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372810</v>
+        <v>124373102</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496460</v>
+        <v>496574</v>
       </c>
       <c r="R78" t="n">
-        <v>7018885</v>
+        <v>7018897</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372714</v>
+        <v>124372460</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496416</v>
+        <v>496311</v>
       </c>
       <c r="R79" t="n">
-        <v>7018877</v>
+        <v>7018869</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372291</v>
+        <v>124372714</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9707,7 +9707,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496371</v>
+        <v>496416</v>
       </c>
       <c r="R80" t="n">
-        <v>7018862</v>
+        <v>7018877</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124373047</v>
+        <v>124372184</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496551</v>
+        <v>496392</v>
       </c>
       <c r="R81" t="n">
-        <v>7018894</v>
+        <v>7018873</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124376085</v>
+        <v>124372343</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496204</v>
+        <v>496345</v>
       </c>
       <c r="R82" t="n">
-        <v>7018992</v>
+        <v>7018866</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372343</v>
+        <v>124372906</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496345</v>
+        <v>496496</v>
       </c>
       <c r="R83" t="n">
-        <v>7018866</v>
+        <v>7018887</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372891</v>
+        <v>124373047</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496487</v>
+        <v>496551</v>
       </c>
       <c r="R84" t="n">
-        <v>7018890</v>
+        <v>7018894</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124373649</v>
+        <v>124370135</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496649</v>
+        <v>496395</v>
       </c>
       <c r="R2" t="n">
-        <v>7018995</v>
+        <v>7018910</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,21 +748,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374769</v>
+        <v>124366230</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -831,19 +811,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496465</v>
+        <v>495918</v>
       </c>
       <c r="R3" t="n">
-        <v>7018933</v>
+        <v>7018928</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124365917</v>
+        <v>124369665</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496005</v>
+        <v>496219</v>
       </c>
       <c r="R4" t="n">
-        <v>7018959</v>
+        <v>7018883</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124373902</v>
+        <v>124373203</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496634</v>
+        <v>496570</v>
       </c>
       <c r="R5" t="n">
-        <v>7019012</v>
+        <v>7018914</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,26 +1122,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124371845</v>
+        <v>124375158</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,41 +1175,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496327</v>
+        <v>496311</v>
       </c>
       <c r="R6" t="n">
-        <v>7018893</v>
+        <v>7018994</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,11 +1250,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,6 +1273,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124375602</v>
+        <v>124373902</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1306,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496297</v>
+        <v>496634</v>
       </c>
       <c r="R7" t="n">
-        <v>7018948</v>
+        <v>7019012</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,51 +1390,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124369063</v>
+        <v>124365253</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,27 +1422,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496203</v>
+        <v>496029</v>
       </c>
       <c r="R8" t="n">
-        <v>7018907</v>
+        <v>7018921</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,26 +1511,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1534,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124366502</v>
+        <v>124370553</v>
       </c>
       <c r="B9" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,41 +1540,60 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495918</v>
+        <v>496283</v>
       </c>
       <c r="R9" t="n">
-        <v>7018925</v>
+        <v>7018896</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,7 +1622,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,7 +1632,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,26 +1652,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,7 +1669,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124368930</v>
+        <v>124375602</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1711,13 +1709,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496185</v>
+        <v>496297</v>
       </c>
       <c r="R10" t="n">
-        <v>7018934</v>
+        <v>7018948</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1744,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,7 +1754,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,12 +1783,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1808,7 +1806,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374616</v>
+        <v>124365804</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1848,13 +1846,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496506</v>
+        <v>496020</v>
       </c>
       <c r="R11" t="n">
-        <v>7018942</v>
+        <v>7018934</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1881,21 +1879,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1904,31 +1892,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1945,10 +1908,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124367876</v>
+        <v>124365230</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1961,21 +1924,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1985,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496096</v>
+        <v>496029</v>
       </c>
       <c r="R12" t="n">
-        <v>7018871</v>
+        <v>7018962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2047,10 +2010,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124374892</v>
+        <v>124365832</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2063,21 +2026,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2087,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496365</v>
+        <v>496020</v>
       </c>
       <c r="R13" t="n">
-        <v>7018964</v>
+        <v>7018936</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2149,10 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374413</v>
+        <v>124375411</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2161,41 +2124,60 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496449</v>
+        <v>496320</v>
       </c>
       <c r="R14" t="n">
         <v>7018988</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2222,11 +2204,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2235,6 +2232,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2251,10 +2253,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124365804</v>
+        <v>124364887</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,21 +2269,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2291,10 +2293,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496020</v>
+        <v>496078</v>
       </c>
       <c r="R15" t="n">
-        <v>7018934</v>
+        <v>7018964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2353,10 +2355,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124364937</v>
+        <v>124366031</v>
       </c>
       <c r="B16" t="n">
-        <v>91026</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,21 +2371,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2393,10 +2395,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496075</v>
+        <v>495986</v>
       </c>
       <c r="R16" t="n">
-        <v>7018977</v>
+        <v>7018958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2455,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124365867</v>
+        <v>124374892</v>
       </c>
       <c r="B17" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2471,21 +2473,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2495,10 +2497,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496012</v>
+        <v>496365</v>
       </c>
       <c r="R17" t="n">
-        <v>7018928</v>
+        <v>7018964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2557,7 +2559,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124368130</v>
+        <v>124371804</v>
       </c>
       <c r="B18" t="n">
         <v>91012</v>
@@ -2597,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496089</v>
+        <v>496319</v>
       </c>
       <c r="R18" t="n">
-        <v>7018863</v>
+        <v>7018893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,10 +2661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124369001</v>
+        <v>124364937</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,21 +2677,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2699,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496205</v>
+        <v>496075</v>
       </c>
       <c r="R19" t="n">
-        <v>7018858</v>
+        <v>7018977</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124367729</v>
+        <v>124365032</v>
       </c>
       <c r="B20" t="n">
-        <v>74901</v>
+        <v>96354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,21 +2779,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496047</v>
+        <v>496041</v>
       </c>
       <c r="R20" t="n">
-        <v>7018892</v>
+        <v>7018962</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2863,7 +2865,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124373203</v>
+        <v>124367848</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2903,13 +2905,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496570</v>
+        <v>496067</v>
       </c>
       <c r="R21" t="n">
-        <v>7018914</v>
+        <v>7018881</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,10 +3002,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124372052</v>
+        <v>124369063</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3012,41 +3014,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496397</v>
+        <v>496203</v>
       </c>
       <c r="R22" t="n">
-        <v>7018931</v>
+        <v>7018907</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3075,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3085,7 +3092,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,26 +3103,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124370557</v>
+        <v>124368130</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3128,48 +3160,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496338</v>
+        <v>496089</v>
       </c>
       <c r="R23" t="n">
-        <v>7018951</v>
+        <v>7018863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3228,10 +3246,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124369222</v>
+        <v>124372052</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3244,21 +3262,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3268,10 +3286,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496155</v>
+        <v>496397</v>
       </c>
       <c r="R24" t="n">
-        <v>7018842</v>
+        <v>7018931</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3301,9 +3319,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,22 +3346,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124365439</v>
+        <v>124370431</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3346,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3370,10 +3398,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496029</v>
+        <v>496343</v>
       </c>
       <c r="R25" t="n">
-        <v>7018964</v>
+        <v>7018868</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3432,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124375041</v>
+        <v>124372203</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3472,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496343</v>
+        <v>496503</v>
       </c>
       <c r="R26" t="n">
-        <v>7018997</v>
+        <v>7018898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3505,9 +3533,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,22 +3560,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124369957</v>
+        <v>124368788</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,21 +3588,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3574,13 +3612,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496287</v>
+        <v>496168</v>
       </c>
       <c r="R27" t="n">
-        <v>7018882</v>
+        <v>7018906</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3607,11 +3645,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3620,6 +3668,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3636,7 +3709,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124371804</v>
+        <v>124369001</v>
       </c>
       <c r="B28" t="n">
         <v>91012</v>
@@ -3676,10 +3749,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496319</v>
+        <v>496205</v>
       </c>
       <c r="R28" t="n">
-        <v>7018893</v>
+        <v>7018858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3738,10 +3811,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124368788</v>
+        <v>124374980</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3754,21 +3827,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3778,13 +3851,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496168</v>
+        <v>496356</v>
       </c>
       <c r="R29" t="n">
-        <v>7018906</v>
+        <v>7018988</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3813,7 +3886,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3896,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,51 +3907,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124374980</v>
+        <v>124369822</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3891,21 +3939,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3963,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496356</v>
+        <v>496245</v>
       </c>
       <c r="R30" t="n">
-        <v>7018988</v>
+        <v>7018876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,19 +3996,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3975,19 +4013,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124366230</v>
+        <v>124369981</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -4021,21 +4059,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495918</v>
+        <v>496293</v>
       </c>
       <c r="R31" t="n">
-        <v>7018928</v>
+        <v>7018882</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4067,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4077,12 +4110,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4134,10 +4162,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124372694</v>
+        <v>124370557</v>
       </c>
       <c r="B32" t="n">
-        <v>74901</v>
+        <v>56714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4150,34 +4178,48 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496555</v>
+        <v>496338</v>
       </c>
       <c r="R32" t="n">
-        <v>7018901</v>
+        <v>7018951</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,19 +4249,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>19:23</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>19:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4234,22 +4266,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124365832</v>
+        <v>124374413</v>
       </c>
       <c r="B33" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4262,21 +4294,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4286,10 +4318,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496020</v>
+        <v>496449</v>
       </c>
       <c r="R33" t="n">
-        <v>7018936</v>
+        <v>7018988</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4348,10 +4380,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124366461</v>
+        <v>124375105</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4360,51 +4392,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495944</v>
+        <v>496343</v>
       </c>
       <c r="R34" t="n">
-        <v>7018967</v>
+        <v>7018997</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4433,7 +4455,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4465,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4458,6 +4480,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4475,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124365032</v>
+        <v>124367729</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4491,21 +4533,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4515,10 +4557,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496041</v>
+        <v>496047</v>
       </c>
       <c r="R35" t="n">
-        <v>7018962</v>
+        <v>7018892</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4577,10 +4619,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375411</v>
+        <v>124368930</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4589,57 +4631,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496320</v>
+        <v>496185</v>
       </c>
       <c r="R36" t="n">
-        <v>7018988</v>
+        <v>7018934</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4671,7 +4694,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4681,12 +4704,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4701,6 +4719,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4718,7 +4756,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124367848</v>
+        <v>124374769</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4758,13 +4796,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496067</v>
+        <v>496465</v>
       </c>
       <c r="R37" t="n">
-        <v>7018881</v>
+        <v>7018933</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4793,7 +4831,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4803,7 +4841,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,7 +4893,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124368504</v>
+        <v>124365867</v>
       </c>
       <c r="B38" t="n">
         <v>82597</v>
@@ -4895,10 +4933,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496112</v>
+        <v>496012</v>
       </c>
       <c r="R38" t="n">
-        <v>7018885</v>
+        <v>7018928</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4957,7 +4995,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124368893</v>
+        <v>124369957</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4997,10 +5035,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496152</v>
+        <v>496287</v>
       </c>
       <c r="R39" t="n">
-        <v>7018906</v>
+        <v>7018882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5059,10 +5097,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124369665</v>
+        <v>124372694</v>
       </c>
       <c r="B40" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5075,21 +5113,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5099,10 +5137,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496219</v>
+        <v>496555</v>
       </c>
       <c r="R40" t="n">
-        <v>7018883</v>
+        <v>7018901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5132,9 +5170,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5149,22 +5197,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375665</v>
+        <v>124375041</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5173,25 +5221,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5201,10 +5249,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496298</v>
+        <v>496343</v>
       </c>
       <c r="R41" t="n">
-        <v>7018981</v>
+        <v>7018997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5234,24 +5282,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5266,22 +5299,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124365230</v>
+        <v>124368504</v>
       </c>
       <c r="B42" t="n">
-        <v>100279</v>
+        <v>82597</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5290,25 +5323,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5318,10 +5351,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496029</v>
+        <v>496112</v>
       </c>
       <c r="R42" t="n">
-        <v>7018962</v>
+        <v>7018885</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5380,7 +5413,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124370135</v>
+        <v>124366246</v>
       </c>
       <c r="B43" t="n">
         <v>91012</v>
@@ -5420,10 +5453,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496395</v>
+        <v>496045</v>
       </c>
       <c r="R43" t="n">
-        <v>7018910</v>
+        <v>7018931</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5482,7 +5515,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124364887</v>
+        <v>124369222</v>
       </c>
       <c r="B44" t="n">
         <v>91012</v>
@@ -5522,10 +5555,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496078</v>
+        <v>496155</v>
       </c>
       <c r="R44" t="n">
-        <v>7018964</v>
+        <v>7018842</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5584,10 +5617,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375105</v>
+        <v>124366502</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5596,25 +5629,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5624,13 +5657,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496343</v>
+        <v>495918</v>
       </c>
       <c r="R45" t="n">
-        <v>7018997</v>
+        <v>7018925</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5659,7 +5692,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5669,7 +5702,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5688,22 +5721,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5721,10 +5754,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124369981</v>
+        <v>124368223</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5737,21 +5770,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5761,13 +5794,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496293</v>
+        <v>496103</v>
       </c>
       <c r="R46" t="n">
-        <v>7018882</v>
+        <v>7018878</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5794,21 +5827,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5817,31 +5840,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5858,10 +5856,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124368223</v>
+        <v>124366461</v>
       </c>
       <c r="B47" t="n">
-        <v>74901</v>
+        <v>57883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5870,41 +5868,51 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496103</v>
+        <v>495944</v>
       </c>
       <c r="R47" t="n">
-        <v>7018878</v>
+        <v>7018967</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5931,11 +5939,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5944,6 +5962,11 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5960,10 +5983,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124375158</v>
+        <v>124373649</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>100279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5976,36 +5999,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6014,13 +6028,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496311</v>
+        <v>496649</v>
       </c>
       <c r="R48" t="n">
-        <v>7018994</v>
+        <v>7018995</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6049,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6059,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6091,10 +6105,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124366246</v>
+        <v>124375665</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6103,25 +6117,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6131,10 +6145,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496045</v>
+        <v>496298</v>
       </c>
       <c r="R49" t="n">
-        <v>7018931</v>
+        <v>7018981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6164,9 +6178,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6181,22 +6210,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124370431</v>
+        <v>124365439</v>
       </c>
       <c r="B50" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6209,21 +6238,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6233,10 +6262,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496343</v>
+        <v>496029</v>
       </c>
       <c r="R50" t="n">
-        <v>7018868</v>
+        <v>7018964</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6295,10 +6324,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124369822</v>
+        <v>124367876</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6307,25 +6336,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6335,10 +6364,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496245</v>
+        <v>496096</v>
       </c>
       <c r="R51" t="n">
-        <v>7018876</v>
+        <v>7018871</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6397,7 +6426,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124372203</v>
+        <v>124365917</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6431,16 +6460,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496503</v>
+        <v>496005</v>
       </c>
       <c r="R52" t="n">
-        <v>7018898</v>
+        <v>7018959</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6470,19 +6504,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6497,22 +6521,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124365253</v>
+        <v>124374616</v>
       </c>
       <c r="B53" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6521,46 +6545,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496029</v>
+        <v>496506</v>
       </c>
       <c r="R53" t="n">
-        <v>7018921</v>
+        <v>7018942</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6589,7 +6608,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6599,7 +6618,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6614,6 +6633,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6631,10 +6670,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124370553</v>
+        <v>124368893</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6643,60 +6682,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496283</v>
+        <v>496152</v>
       </c>
       <c r="R54" t="n">
-        <v>7018896</v>
+        <v>7018906</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6723,26 +6743,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6751,11 +6756,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6772,10 +6772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124366031</v>
+        <v>124371845</v>
       </c>
       <c r="B55" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6788,21 +6788,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495986</v>
+        <v>496327</v>
       </c>
       <c r="R55" t="n">
-        <v>7018958</v>
+        <v>7018893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372382</v>
+        <v>124372406</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496322</v>
+        <v>496324</v>
       </c>
       <c r="R56" t="n">
-        <v>7018864</v>
+        <v>7018859</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372826</v>
+        <v>124372382</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496446</v>
+        <v>496322</v>
       </c>
       <c r="R57" t="n">
-        <v>7018884</v>
+        <v>7018864</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372406</v>
+        <v>124372343</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496324</v>
+        <v>496345</v>
       </c>
       <c r="R58" t="n">
-        <v>7018859</v>
+        <v>7018866</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372986</v>
+        <v>124372891</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496526</v>
+        <v>496487</v>
       </c>
       <c r="R59" t="n">
-        <v>7018886</v>
+        <v>7018890</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372169</v>
+        <v>124372196</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496446</v>
+        <v>496444</v>
       </c>
       <c r="R60" t="n">
-        <v>7018897</v>
+        <v>7018877</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7400,14 +7400,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,6 +7428,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7434,7 +7469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372868</v>
+        <v>124373102</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7479,10 +7514,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496485</v>
+        <v>496574</v>
       </c>
       <c r="R61" t="n">
-        <v>7018881</v>
+        <v>7018897</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,7 +7581,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124373122</v>
+        <v>124372778</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7591,10 +7626,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496571</v>
+        <v>496426</v>
       </c>
       <c r="R62" t="n">
-        <v>7018892</v>
+        <v>7018876</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7658,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372949</v>
+        <v>124372460</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7703,10 +7738,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496504</v>
+        <v>496311</v>
       </c>
       <c r="R63" t="n">
-        <v>7018879</v>
+        <v>7018869</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7770,7 +7805,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372213</v>
+        <v>124373142</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7809,16 +7844,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496392</v>
+        <v>496560</v>
       </c>
       <c r="R64" t="n">
-        <v>7018866</v>
+        <v>7018917</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7848,14 +7888,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7866,6 +7916,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7882,7 +7957,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124373030</v>
+        <v>124372868</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7927,10 +8002,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496538</v>
+        <v>496485</v>
       </c>
       <c r="R65" t="n">
-        <v>7018895</v>
+        <v>7018881</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7994,7 +8069,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372234</v>
+        <v>124372291</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8030,7 +8105,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8039,10 +8114,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496384</v>
+        <v>496371</v>
       </c>
       <c r="R66" t="n">
-        <v>7018864</v>
+        <v>7018862</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8106,7 +8181,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372810</v>
+        <v>124373047</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8151,10 +8226,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496460</v>
+        <v>496551</v>
       </c>
       <c r="R67" t="n">
-        <v>7018885</v>
+        <v>7018894</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8218,7 +8293,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372245</v>
+        <v>124373122</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8263,10 +8338,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496380</v>
+        <v>496571</v>
       </c>
       <c r="R68" t="n">
-        <v>7018867</v>
+        <v>7018892</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8330,7 +8405,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372353</v>
+        <v>124376085</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8375,10 +8450,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496338</v>
+        <v>496204</v>
       </c>
       <c r="R69" t="n">
-        <v>7018864</v>
+        <v>7018992</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8442,14 +8517,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124373091</v>
+        <v>124366868</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8475,10 +8550,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8487,10 +8581,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496553</v>
+        <v>496023</v>
       </c>
       <c r="R70" t="n">
-        <v>7018888</v>
+        <v>7018919</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8520,14 +8614,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8538,6 +8642,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8554,7 +8663,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124376085</v>
+        <v>124372826</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8599,10 +8708,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496204</v>
+        <v>496446</v>
       </c>
       <c r="R71" t="n">
-        <v>7018992</v>
+        <v>7018884</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8666,7 +8775,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373142</v>
+        <v>124372213</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8705,21 +8814,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496560</v>
+        <v>496392</v>
       </c>
       <c r="R72" t="n">
-        <v>7018917</v>
+        <v>7018866</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8749,24 +8853,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8777,31 +8871,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8818,7 +8887,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372891</v>
+        <v>124372810</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8863,10 +8932,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496487</v>
+        <v>496460</v>
       </c>
       <c r="R73" t="n">
-        <v>7018890</v>
+        <v>7018885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8930,14 +8999,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124366868</v>
+        <v>124372986</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8963,29 +9032,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8994,10 +9044,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496023</v>
+        <v>496526</v>
       </c>
       <c r="R74" t="n">
-        <v>7018919</v>
+        <v>7018886</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9027,24 +9077,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9055,11 +9095,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9076,7 +9111,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372196</v>
+        <v>124372169</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9121,13 +9156,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496444</v>
+        <v>496446</v>
       </c>
       <c r="R75" t="n">
-        <v>7018877</v>
+        <v>7018897</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9154,24 +9189,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9182,31 +9207,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9223,7 +9223,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372778</v>
+        <v>124372353</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9268,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496426</v>
+        <v>496338</v>
       </c>
       <c r="R76" t="n">
-        <v>7018876</v>
+        <v>7018864</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372291</v>
+        <v>124372714</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9371,7 +9371,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496371</v>
+        <v>496416</v>
       </c>
       <c r="R77" t="n">
-        <v>7018862</v>
+        <v>7018877</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9447,7 +9447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124373102</v>
+        <v>124373030</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496574</v>
+        <v>496538</v>
       </c>
       <c r="R78" t="n">
-        <v>7018897</v>
+        <v>7018895</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372460</v>
+        <v>124372234</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496311</v>
+        <v>496384</v>
       </c>
       <c r="R79" t="n">
-        <v>7018869</v>
+        <v>7018864</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372714</v>
+        <v>124372184</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496416</v>
+        <v>496392</v>
       </c>
       <c r="R80" t="n">
-        <v>7018877</v>
+        <v>7018873</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372184</v>
+        <v>124372245</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496392</v>
+        <v>496380</v>
       </c>
       <c r="R81" t="n">
-        <v>7018873</v>
+        <v>7018867</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372343</v>
+        <v>124372906</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496345</v>
+        <v>496496</v>
       </c>
       <c r="R82" t="n">
-        <v>7018866</v>
+        <v>7018887</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372906</v>
+        <v>124373091</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496496</v>
+        <v>496553</v>
       </c>
       <c r="R83" t="n">
-        <v>7018887</v>
+        <v>7018888</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124373047</v>
+        <v>124372949</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496551</v>
+        <v>496504</v>
       </c>
       <c r="R84" t="n">
-        <v>7018894</v>
+        <v>7018879</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124370135</v>
+        <v>124374413</v>
       </c>
       <c r="B2" t="n">
         <v>91012</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496395</v>
+        <v>496449</v>
       </c>
       <c r="R2" t="n">
-        <v>7018910</v>
+        <v>7018988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124369665</v>
+        <v>124370431</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496219</v>
+        <v>496343</v>
       </c>
       <c r="R4" t="n">
-        <v>7018883</v>
+        <v>7018868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124373203</v>
+        <v>124365832</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496570</v>
+        <v>496020</v>
       </c>
       <c r="R5" t="n">
-        <v>7018914</v>
+        <v>7018936</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,21 +1099,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1122,31 +1112,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124375158</v>
+        <v>124368788</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,55 +1140,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496311</v>
+        <v>496168</v>
       </c>
       <c r="R6" t="n">
-        <v>7018994</v>
+        <v>7018906</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,6 +1228,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1294,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124373902</v>
+        <v>124372052</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,25 +1277,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496634</v>
+        <v>496397</v>
       </c>
       <c r="R7" t="n">
-        <v>7019012</v>
+        <v>7018931</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124365253</v>
+        <v>124369981</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,46 +1389,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496029</v>
+        <v>496293</v>
       </c>
       <c r="R8" t="n">
-        <v>7018921</v>
+        <v>7018882</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,6 +1477,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124370553</v>
+        <v>124365804</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,60 +1526,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496283</v>
+        <v>496020</v>
       </c>
       <c r="R9" t="n">
-        <v>7018896</v>
+        <v>7018934</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,26 +1587,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1648,11 +1600,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1669,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375602</v>
+        <v>124365230</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,13 +1656,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496297</v>
+        <v>496029</v>
       </c>
       <c r="R10" t="n">
-        <v>7018948</v>
+        <v>7018962</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1742,21 +1689,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1765,31 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1806,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124365804</v>
+        <v>124365253</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,38 +1730,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496020</v>
+        <v>496029</v>
       </c>
       <c r="R11" t="n">
-        <v>7018934</v>
+        <v>7018921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,11 +1796,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1892,6 +1819,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1908,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124365230</v>
+        <v>124371804</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,25 +1852,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1948,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496029</v>
+        <v>496319</v>
       </c>
       <c r="R12" t="n">
-        <v>7018962</v>
+        <v>7018893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2010,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124365832</v>
+        <v>124372694</v>
       </c>
       <c r="B13" t="n">
         <v>74901</v>
@@ -2050,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496020</v>
+        <v>496555</v>
       </c>
       <c r="R13" t="n">
-        <v>7018936</v>
+        <v>7018901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,9 +2015,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2100,22 +2042,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375411</v>
+        <v>124366246</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,60 +2066,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496320</v>
+        <v>496045</v>
       </c>
       <c r="R14" t="n">
-        <v>7018988</v>
+        <v>7018931</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2204,26 +2127,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2232,11 +2140,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2253,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124364887</v>
+        <v>124374980</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2269,21 +2172,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2293,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496078</v>
+        <v>496356</v>
       </c>
       <c r="R15" t="n">
-        <v>7018964</v>
+        <v>7018988</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,9 +2229,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,22 +2256,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124366031</v>
+        <v>124374616</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2395,13 +2308,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495986</v>
+        <v>496506</v>
       </c>
       <c r="R16" t="n">
-        <v>7018958</v>
+        <v>7018942</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2428,11 +2341,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2441,6 +2364,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2457,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124374892</v>
+        <v>124366502</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,25 +2417,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2497,13 +2445,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496365</v>
+        <v>495918</v>
       </c>
       <c r="R17" t="n">
-        <v>7018964</v>
+        <v>7018925</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2530,11 +2478,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2543,6 +2501,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2559,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124371804</v>
+        <v>124375602</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2575,21 +2558,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,13 +2582,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496319</v>
+        <v>496297</v>
       </c>
       <c r="R18" t="n">
-        <v>7018893</v>
+        <v>7018948</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2632,11 +2615,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2645,6 +2638,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2661,10 +2679,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124364937</v>
+        <v>124375041</v>
       </c>
       <c r="B19" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2677,21 +2695,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2701,10 +2719,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496075</v>
+        <v>496343</v>
       </c>
       <c r="R19" t="n">
-        <v>7018977</v>
+        <v>7018997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2763,10 +2781,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124365032</v>
+        <v>124368504</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>82597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2779,21 +2797,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2803,10 +2821,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496041</v>
+        <v>496112</v>
       </c>
       <c r="R20" t="n">
-        <v>7018962</v>
+        <v>7018885</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2865,10 +2883,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124367848</v>
+        <v>124368130</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,21 +2899,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2905,10 +2923,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496067</v>
+        <v>496089</v>
       </c>
       <c r="R21" t="n">
-        <v>7018881</v>
+        <v>7018863</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,21 +2956,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2961,31 +2969,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3002,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124369063</v>
+        <v>124370557</v>
       </c>
       <c r="B22" t="n">
-        <v>90977</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,31 +2997,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3047,13 +3039,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496203</v>
+        <v>496338</v>
       </c>
       <c r="R22" t="n">
-        <v>7018907</v>
+        <v>7018951</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3080,21 +3072,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3103,31 +3085,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3144,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124368130</v>
+        <v>124365032</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>96354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,21 +3117,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496089</v>
+        <v>496041</v>
       </c>
       <c r="R23" t="n">
-        <v>7018863</v>
+        <v>7018962</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3246,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124372052</v>
+        <v>124369001</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3262,21 +3219,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3286,10 +3243,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496397</v>
+        <v>496205</v>
       </c>
       <c r="R24" t="n">
-        <v>7018931</v>
+        <v>7018858</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3319,19 +3276,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,22 +3293,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370431</v>
+        <v>124367848</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,21 +3321,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3398,10 +3345,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496343</v>
+        <v>496067</v>
       </c>
       <c r="R25" t="n">
-        <v>7018868</v>
+        <v>7018881</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,11 +3378,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3444,6 +3401,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3460,7 +3442,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124372203</v>
+        <v>124369822</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3500,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496503</v>
+        <v>496245</v>
       </c>
       <c r="R26" t="n">
-        <v>7018898</v>
+        <v>7018876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3533,19 +3515,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>19:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3560,22 +3532,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124368788</v>
+        <v>124368223</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3588,21 +3560,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3612,13 +3584,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496168</v>
+        <v>496103</v>
       </c>
       <c r="R27" t="n">
-        <v>7018906</v>
+        <v>7018878</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,21 +3617,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3668,31 +3630,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3709,10 +3646,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369001</v>
+        <v>124375105</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3725,21 +3662,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3749,13 +3686,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496205</v>
+        <v>496343</v>
       </c>
       <c r="R28" t="n">
-        <v>7018858</v>
+        <v>7018997</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3782,11 +3719,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3795,6 +3742,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3811,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374980</v>
+        <v>124370135</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3827,21 +3799,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3851,10 +3823,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496356</v>
+        <v>496395</v>
       </c>
       <c r="R29" t="n">
-        <v>7018988</v>
+        <v>7018910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3884,19 +3856,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3911,19 +3873,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369822</v>
+        <v>124373203</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3963,13 +3925,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496245</v>
+        <v>496570</v>
       </c>
       <c r="R30" t="n">
-        <v>7018876</v>
+        <v>7018914</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3996,11 +3958,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4009,6 +3981,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4025,10 +4022,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124369981</v>
+        <v>124375665</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,25 +4034,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4065,13 +4062,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496293</v>
+        <v>496298</v>
       </c>
       <c r="R31" t="n">
-        <v>7018882</v>
+        <v>7018981</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4097,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4107,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4121,51 +4123,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124370557</v>
+        <v>124375411</v>
       </c>
       <c r="B32" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4174,40 +4151,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4216,13 +4198,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496338</v>
+        <v>496320</v>
       </c>
       <c r="R32" t="n">
-        <v>7018951</v>
+        <v>7018988</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4249,11 +4231,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4262,6 +4259,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4278,10 +4280,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374413</v>
+        <v>124364937</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4294,21 +4296,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4318,10 +4320,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496449</v>
+        <v>496075</v>
       </c>
       <c r="R33" t="n">
-        <v>7018988</v>
+        <v>7018977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4380,10 +4382,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124375105</v>
+        <v>124364887</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4396,21 +4398,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4420,13 +4422,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496343</v>
+        <v>496078</v>
       </c>
       <c r="R34" t="n">
-        <v>7018997</v>
+        <v>7018964</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4453,21 +4455,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4476,31 +4468,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4517,10 +4484,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124367729</v>
+        <v>124372203</v>
       </c>
       <c r="B35" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4533,21 +4500,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4557,10 +4524,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496047</v>
+        <v>496503</v>
       </c>
       <c r="R35" t="n">
-        <v>7018892</v>
+        <v>7018898</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4590,9 +4557,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4607,22 +4584,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124368930</v>
+        <v>124369063</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4631,38 +4608,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496185</v>
+        <v>496203</v>
       </c>
       <c r="R36" t="n">
-        <v>7018934</v>
+        <v>7018907</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4694,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4704,7 +4686,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4733,12 +4715,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4756,10 +4738,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374769</v>
+        <v>124374892</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4772,21 +4754,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4796,13 +4778,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496465</v>
+        <v>496365</v>
       </c>
       <c r="R37" t="n">
-        <v>7018933</v>
+        <v>7018964</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4829,21 +4811,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4852,31 +4824,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4893,10 +4840,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124365867</v>
+        <v>124365917</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4909,34 +4856,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496012</v>
+        <v>496005</v>
       </c>
       <c r="R38" t="n">
-        <v>7018928</v>
+        <v>7018959</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4995,10 +4947,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124369957</v>
+        <v>124369665</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5011,21 +4963,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5035,10 +4987,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496287</v>
+        <v>496219</v>
       </c>
       <c r="R39" t="n">
-        <v>7018882</v>
+        <v>7018883</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5097,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124372694</v>
+        <v>124373649</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5109,41 +5061,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496555</v>
+        <v>496649</v>
       </c>
       <c r="R40" t="n">
-        <v>7018901</v>
+        <v>7018995</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5172,7 +5129,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5182,7 +5139,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5193,26 +5150,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375041</v>
+        <v>124365867</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5225,21 +5187,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5249,10 +5211,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496343</v>
+        <v>496012</v>
       </c>
       <c r="R41" t="n">
-        <v>7018997</v>
+        <v>7018928</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5311,10 +5273,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124368504</v>
+        <v>124367876</v>
       </c>
       <c r="B42" t="n">
-        <v>82597</v>
+        <v>90977</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5323,25 +5285,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5351,10 +5313,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496112</v>
+        <v>496096</v>
       </c>
       <c r="R42" t="n">
-        <v>7018885</v>
+        <v>7018871</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5413,7 +5375,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124366246</v>
+        <v>124368893</v>
       </c>
       <c r="B43" t="n">
         <v>91012</v>
@@ -5453,10 +5415,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496045</v>
+        <v>496152</v>
       </c>
       <c r="R43" t="n">
-        <v>7018931</v>
+        <v>7018906</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5617,10 +5579,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124366502</v>
+        <v>124371845</v>
       </c>
       <c r="B45" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5629,25 +5591,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5657,13 +5619,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495918</v>
+        <v>496327</v>
       </c>
       <c r="R45" t="n">
-        <v>7018925</v>
+        <v>7018893</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5690,21 +5652,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5713,31 +5665,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5754,7 +5681,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124368223</v>
+        <v>124367729</v>
       </c>
       <c r="B46" t="n">
         <v>74901</v>
@@ -5794,10 +5721,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496103</v>
+        <v>496047</v>
       </c>
       <c r="R46" t="n">
-        <v>7018878</v>
+        <v>7018892</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5856,10 +5783,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124366461</v>
+        <v>124374769</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5868,51 +5795,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495944</v>
+        <v>496465</v>
       </c>
       <c r="R47" t="n">
-        <v>7018967</v>
+        <v>7018933</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5941,7 +5858,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5951,7 +5868,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5966,6 +5883,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5983,7 +5920,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124373649</v>
+        <v>124373902</v>
       </c>
       <c r="B48" t="n">
         <v>100279</v>
@@ -6017,24 +5954,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496649</v>
+        <v>496634</v>
       </c>
       <c r="R48" t="n">
-        <v>7018995</v>
+        <v>7019012</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6063,7 +5995,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6005,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6084,31 +6016,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124375665</v>
+        <v>124365439</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6117,25 +6044,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6145,10 +6072,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496298</v>
+        <v>496029</v>
       </c>
       <c r="R49" t="n">
-        <v>7018981</v>
+        <v>7018964</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6178,24 +6105,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6210,19 +6122,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124365439</v>
+        <v>124369957</v>
       </c>
       <c r="B50" t="n">
         <v>91012</v>
@@ -6262,10 +6174,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496029</v>
+        <v>496287</v>
       </c>
       <c r="R50" t="n">
-        <v>7018964</v>
+        <v>7018882</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6324,10 +6236,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124367876</v>
+        <v>124368930</v>
       </c>
       <c r="B51" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6336,25 +6248,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6364,13 +6276,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496096</v>
+        <v>496185</v>
       </c>
       <c r="R51" t="n">
-        <v>7018871</v>
+        <v>7018934</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6397,11 +6309,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6410,6 +6332,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6426,10 +6373,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124365917</v>
+        <v>124366461</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6438,31 +6385,36 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6471,13 +6423,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496005</v>
+        <v>495944</v>
       </c>
       <c r="R52" t="n">
-        <v>7018959</v>
+        <v>7018967</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6504,11 +6456,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6517,6 +6479,11 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6533,10 +6500,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124374616</v>
+        <v>124366031</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6549,21 +6516,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6573,13 +6540,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496506</v>
+        <v>495986</v>
       </c>
       <c r="R53" t="n">
-        <v>7018942</v>
+        <v>7018958</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6606,21 +6573,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6629,31 +6586,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6670,10 +6602,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124368893</v>
+        <v>124375158</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6682,41 +6614,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496152</v>
+        <v>496311</v>
       </c>
       <c r="R54" t="n">
-        <v>7018906</v>
+        <v>7018994</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6743,11 +6689,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6756,6 +6712,11 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6772,10 +6733,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124371845</v>
+        <v>124370553</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6784,41 +6745,60 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496327</v>
+        <v>496283</v>
       </c>
       <c r="R55" t="n">
-        <v>7018893</v>
+        <v>7018896</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6845,11 +6825,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6858,6 +6853,11 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124372052</v>
+        <v>124365230</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,25 +1277,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496397</v>
+        <v>496029</v>
       </c>
       <c r="R7" t="n">
-        <v>7018931</v>
+        <v>7018962</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,19 +1338,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,19 +1355,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124369981</v>
+        <v>124372052</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1417,13 +1407,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496293</v>
+        <v>496397</v>
       </c>
       <c r="R8" t="n">
-        <v>7018882</v>
+        <v>7018931</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,48 +1463,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124365804</v>
+        <v>124369981</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1554,13 +1519,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496020</v>
+        <v>496293</v>
       </c>
       <c r="R9" t="n">
-        <v>7018934</v>
+        <v>7018882</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,11 +1552,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1600,6 +1575,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124365230</v>
+        <v>124365804</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496029</v>
+        <v>496020</v>
       </c>
       <c r="R10" t="n">
-        <v>7018962</v>
+        <v>7018934</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124365032</v>
+        <v>124367848</v>
       </c>
       <c r="B23" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496041</v>
+        <v>496067</v>
       </c>
       <c r="R23" t="n">
-        <v>7018962</v>
+        <v>7018881</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,11 +3174,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3187,6 +3197,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3203,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124369001</v>
+        <v>124369822</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3219,21 +3254,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3243,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496205</v>
+        <v>496245</v>
       </c>
       <c r="R24" t="n">
-        <v>7018858</v>
+        <v>7018876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,10 +3340,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124367848</v>
+        <v>124368223</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,21 +3356,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3345,10 +3380,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496067</v>
+        <v>496103</v>
       </c>
       <c r="R25" t="n">
-        <v>7018881</v>
+        <v>7018878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3378,21 +3413,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3401,31 +3426,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369822</v>
+        <v>124365032</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496245</v>
+        <v>496041</v>
       </c>
       <c r="R26" t="n">
-        <v>7018876</v>
+        <v>7018962</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124368223</v>
+        <v>124369001</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496103</v>
+        <v>496205</v>
       </c>
       <c r="R27" t="n">
-        <v>7018878</v>
+        <v>7018858</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124367876</v>
+        <v>124368893</v>
       </c>
       <c r="B42" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5285,25 +5285,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496096</v>
+        <v>496152</v>
       </c>
       <c r="R42" t="n">
-        <v>7018871</v>
+        <v>7018906</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124368893</v>
+        <v>124369222</v>
       </c>
       <c r="B43" t="n">
         <v>91012</v>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496152</v>
+        <v>496155</v>
       </c>
       <c r="R43" t="n">
-        <v>7018906</v>
+        <v>7018842</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124369222</v>
+        <v>124367876</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5489,25 +5489,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496155</v>
+        <v>496096</v>
       </c>
       <c r="R44" t="n">
-        <v>7018842</v>
+        <v>7018871</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374413</v>
+        <v>124364887</v>
       </c>
       <c r="B2" t="n">
         <v>91012</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496449</v>
+        <v>496078</v>
       </c>
       <c r="R2" t="n">
-        <v>7018988</v>
+        <v>7018964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124366230</v>
+        <v>124374892</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495918</v>
+        <v>496365</v>
       </c>
       <c r="R3" t="n">
-        <v>7018928</v>
+        <v>7018964</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,26 +850,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,31 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124370431</v>
+        <v>124372052</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496343</v>
+        <v>496397</v>
       </c>
       <c r="R4" t="n">
-        <v>7018868</v>
+        <v>7018931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,9 +952,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124365832</v>
+        <v>124365804</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,7 +1034,7 @@
         <v>496020</v>
       </c>
       <c r="R5" t="n">
-        <v>7018936</v>
+        <v>7018934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124368788</v>
+        <v>124369665</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496168</v>
+        <v>496219</v>
       </c>
       <c r="R6" t="n">
-        <v>7018906</v>
+        <v>7018883</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,21 +1166,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1224,31 +1179,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1265,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124365230</v>
+        <v>124368504</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>82597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496029</v>
+        <v>496112</v>
       </c>
       <c r="R7" t="n">
-        <v>7018962</v>
+        <v>7018885</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124372052</v>
+        <v>124365917</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1401,16 +1331,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496397</v>
+        <v>496005</v>
       </c>
       <c r="R8" t="n">
-        <v>7018931</v>
+        <v>7018959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,19 +1375,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1392,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124369981</v>
+        <v>124368893</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,13 +1444,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496293</v>
+        <v>496152</v>
       </c>
       <c r="R9" t="n">
-        <v>7018882</v>
+        <v>7018906</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,21 +1477,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,31 +1490,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124365804</v>
+        <v>124366502</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496020</v>
+        <v>495918</v>
       </c>
       <c r="R10" t="n">
-        <v>7018934</v>
+        <v>7018925</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,11 +1579,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1702,6 +1602,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124365253</v>
+        <v>124375041</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,43 +1655,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496029</v>
+        <v>496343</v>
       </c>
       <c r="R11" t="n">
-        <v>7018921</v>
+        <v>7018997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,21 +1716,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1819,11 +1729,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1840,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124371804</v>
+        <v>124368930</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496319</v>
+        <v>496185</v>
       </c>
       <c r="R12" t="n">
-        <v>7018893</v>
+        <v>7018934</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,11 +1818,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1926,6 +1841,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124372694</v>
+        <v>124375411</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,41 +1894,60 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496555</v>
+        <v>496320</v>
       </c>
       <c r="R13" t="n">
-        <v>7018901</v>
+        <v>7018988</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +1986,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,26 +2002,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124366246</v>
+        <v>124367848</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496045</v>
+        <v>496067</v>
       </c>
       <c r="R14" t="n">
-        <v>7018931</v>
+        <v>7018881</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,11 +2096,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2140,6 +2119,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2156,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374980</v>
+        <v>124365832</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2176,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496356</v>
+        <v>496020</v>
       </c>
       <c r="R15" t="n">
-        <v>7018988</v>
+        <v>7018936</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,19 +2233,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,22 +2250,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374616</v>
+        <v>124369063</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,41 +2274,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496506</v>
+        <v>496203</v>
       </c>
       <c r="R16" t="n">
-        <v>7018942</v>
+        <v>7018907</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,12 +2381,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124366502</v>
+        <v>124374413</v>
       </c>
       <c r="B17" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,25 +2416,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2445,13 +2444,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495918</v>
+        <v>496449</v>
       </c>
       <c r="R17" t="n">
-        <v>7018925</v>
+        <v>7018988</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,21 +2477,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2501,31 +2490,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2542,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124375602</v>
+        <v>124365439</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2582,13 +2546,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496297</v>
+        <v>496029</v>
       </c>
       <c r="R18" t="n">
-        <v>7018948</v>
+        <v>7018964</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2615,21 +2579,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2638,31 +2592,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2679,10 +2608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375041</v>
+        <v>124367729</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2695,21 +2624,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2719,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496343</v>
+        <v>496047</v>
       </c>
       <c r="R19" t="n">
-        <v>7018997</v>
+        <v>7018892</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124368504</v>
+        <v>124365230</v>
       </c>
       <c r="B20" t="n">
-        <v>82597</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2793,25 +2722,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2821,10 +2750,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496112</v>
+        <v>496029</v>
       </c>
       <c r="R20" t="n">
-        <v>7018885</v>
+        <v>7018962</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2883,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124368130</v>
+        <v>124369981</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,21 +2828,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2923,13 +2852,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496089</v>
+        <v>496293</v>
       </c>
       <c r="R21" t="n">
-        <v>7018863</v>
+        <v>7018882</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2956,11 +2885,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2969,6 +2908,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2985,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124370557</v>
+        <v>124372694</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,48 +2965,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496338</v>
+        <v>496555</v>
       </c>
       <c r="R22" t="n">
-        <v>7018951</v>
+        <v>7018901</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3072,9 +3022,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,19 +3049,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124367848</v>
+        <v>124369822</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3141,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496067</v>
+        <v>496245</v>
       </c>
       <c r="R23" t="n">
-        <v>7018881</v>
+        <v>7018876</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,21 +3134,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3197,31 +3147,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3238,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124369822</v>
+        <v>124369001</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,21 +3179,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,10 +3203,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496245</v>
+        <v>496205</v>
       </c>
       <c r="R24" t="n">
-        <v>7018876</v>
+        <v>7018858</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3340,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124368223</v>
+        <v>124375665</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3352,25 +3277,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3380,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496103</v>
+        <v>496298</v>
       </c>
       <c r="R25" t="n">
-        <v>7018878</v>
+        <v>7018981</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,9 +3338,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,22 +3370,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124365032</v>
+        <v>124366461</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>57883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,41 +3394,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496041</v>
+        <v>495944</v>
       </c>
       <c r="R26" t="n">
-        <v>7018962</v>
+        <v>7018967</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3515,11 +3465,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3528,6 +3488,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3544,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124369001</v>
+        <v>124370431</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3560,21 +3525,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3584,10 +3549,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496205</v>
+        <v>496343</v>
       </c>
       <c r="R27" t="n">
-        <v>7018858</v>
+        <v>7018868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3646,7 +3611,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375105</v>
+        <v>124372203</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3686,13 +3651,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496343</v>
+        <v>496503</v>
       </c>
       <c r="R28" t="n">
-        <v>7018997</v>
+        <v>7018898</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3721,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3742,51 +3707,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370135</v>
+        <v>124373902</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,25 +3735,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3823,10 +3763,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496395</v>
+        <v>496634</v>
       </c>
       <c r="R29" t="n">
-        <v>7018910</v>
+        <v>7019012</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,9 +3796,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,12 +3823,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4022,10 +3972,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124375665</v>
+        <v>124364937</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4034,25 +3984,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4062,10 +4012,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496298</v>
+        <v>496075</v>
       </c>
       <c r="R31" t="n">
-        <v>7018981</v>
+        <v>7018977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4095,24 +4045,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4127,22 +4062,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375411</v>
+        <v>124369957</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4151,60 +4086,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496320</v>
+        <v>496287</v>
       </c>
       <c r="R32" t="n">
-        <v>7018988</v>
+        <v>7018882</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4231,26 +4147,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4259,11 +4160,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4280,10 +4176,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124364937</v>
+        <v>124370553</v>
       </c>
       <c r="B33" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4292,41 +4188,60 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496075</v>
+        <v>496283</v>
       </c>
       <c r="R33" t="n">
-        <v>7018977</v>
+        <v>7018896</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4353,11 +4268,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4366,6 +4296,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4382,10 +4317,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124364887</v>
+        <v>124373649</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4394,41 +4329,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496078</v>
+        <v>496649</v>
       </c>
       <c r="R34" t="n">
-        <v>7018964</v>
+        <v>7018995</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4455,11 +4395,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4468,6 +4418,11 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4484,7 +4439,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124372203</v>
+        <v>124366230</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4518,19 +4473,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496503</v>
+        <v>495918</v>
       </c>
       <c r="R35" t="n">
-        <v>7018898</v>
+        <v>7018928</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4559,7 +4519,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4569,7 +4529,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4580,26 +4545,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124369063</v>
+        <v>124375105</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4608,43 +4598,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496203</v>
+        <v>496343</v>
       </c>
       <c r="R36" t="n">
-        <v>7018907</v>
+        <v>7018997</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -4676,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4671,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4700,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4738,10 +4723,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374892</v>
+        <v>124375602</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4754,21 +4739,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4778,13 +4763,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496365</v>
+        <v>496297</v>
       </c>
       <c r="R37" t="n">
-        <v>7018964</v>
+        <v>7018948</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4811,11 +4796,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4824,6 +4819,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4840,10 +4860,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124365917</v>
+        <v>124365032</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4856,39 +4876,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496005</v>
+        <v>496041</v>
       </c>
       <c r="R38" t="n">
-        <v>7018959</v>
+        <v>7018962</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4947,10 +4962,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124369665</v>
+        <v>124366246</v>
       </c>
       <c r="B39" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4963,21 +4978,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4987,10 +5002,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496219</v>
+        <v>496045</v>
       </c>
       <c r="R39" t="n">
-        <v>7018883</v>
+        <v>7018931</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5049,10 +5064,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124373649</v>
+        <v>124368130</v>
       </c>
       <c r="B40" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5061,46 +5076,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496649</v>
+        <v>496089</v>
       </c>
       <c r="R40" t="n">
-        <v>7018995</v>
+        <v>7018863</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5127,21 +5137,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>19:52</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5150,11 +5150,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5171,10 +5166,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124365867</v>
+        <v>124371845</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5187,21 +5182,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5211,10 +5206,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496012</v>
+        <v>496327</v>
       </c>
       <c r="R41" t="n">
-        <v>7018928</v>
+        <v>7018893</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5273,7 +5268,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124368893</v>
+        <v>124370135</v>
       </c>
       <c r="B42" t="n">
         <v>91012</v>
@@ -5313,10 +5308,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496152</v>
+        <v>496395</v>
       </c>
       <c r="R42" t="n">
-        <v>7018906</v>
+        <v>7018910</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5375,10 +5370,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124369222</v>
+        <v>124370557</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5391,34 +5386,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496155</v>
+        <v>496338</v>
       </c>
       <c r="R43" t="n">
-        <v>7018842</v>
+        <v>7018951</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5579,10 +5588,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124371845</v>
+        <v>124374769</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5595,21 +5604,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5619,13 +5628,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496327</v>
+        <v>496465</v>
       </c>
       <c r="R45" t="n">
-        <v>7018893</v>
+        <v>7018933</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5652,11 +5661,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5665,6 +5684,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5681,10 +5725,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124367729</v>
+        <v>124365867</v>
       </c>
       <c r="B46" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5697,21 +5741,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5721,10 +5765,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496047</v>
+        <v>496012</v>
       </c>
       <c r="R46" t="n">
-        <v>7018892</v>
+        <v>7018928</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5783,10 +5827,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374769</v>
+        <v>124374980</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5799,21 +5843,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5823,13 +5867,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496465</v>
+        <v>496356</v>
       </c>
       <c r="R47" t="n">
-        <v>7018933</v>
+        <v>7018988</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5858,7 +5902,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5868,7 +5912,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5879,51 +5923,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124373902</v>
+        <v>124369222</v>
       </c>
       <c r="B48" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5932,25 +5951,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5960,10 +5979,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496634</v>
+        <v>496155</v>
       </c>
       <c r="R48" t="n">
-        <v>7019012</v>
+        <v>7018842</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5993,19 +6012,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>19:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6020,22 +6029,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124365439</v>
+        <v>124375158</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6044,41 +6053,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496029</v>
+        <v>496311</v>
       </c>
       <c r="R49" t="n">
-        <v>7018964</v>
+        <v>7018994</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6105,11 +6128,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6118,6 +6151,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6134,10 +6172,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124369957</v>
+        <v>124374616</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6150,21 +6188,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6174,13 +6212,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496287</v>
+        <v>496506</v>
       </c>
       <c r="R50" t="n">
-        <v>7018882</v>
+        <v>7018942</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6207,11 +6245,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6220,6 +6268,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6236,7 +6309,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124368930</v>
+        <v>124368788</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6276,13 +6349,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496185</v>
+        <v>496168</v>
       </c>
       <c r="R51" t="n">
-        <v>7018934</v>
+        <v>7018906</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6311,7 +6384,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6321,7 +6394,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6350,12 +6423,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6373,10 +6446,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124366461</v>
+        <v>124368223</v>
       </c>
       <c r="B52" t="n">
-        <v>57883</v>
+        <v>74901</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6385,51 +6458,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495944</v>
+        <v>496103</v>
       </c>
       <c r="R52" t="n">
-        <v>7018967</v>
+        <v>7018878</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6456,21 +6519,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:21</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6479,11 +6532,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6602,10 +6650,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124375158</v>
+        <v>124371804</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6614,55 +6662,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496311</v>
+        <v>496319</v>
       </c>
       <c r="R54" t="n">
-        <v>7018994</v>
+        <v>7018893</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6689,21 +6723,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6712,11 +6736,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6733,10 +6752,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124370553</v>
+        <v>124365253</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>100279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6745,45 +6764,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6792,13 +6797,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496283</v>
+        <v>496029</v>
       </c>
       <c r="R55" t="n">
-        <v>7018896</v>
+        <v>7018921</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6827,7 +6832,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6837,12 +6842,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372406</v>
+        <v>124372213</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496324</v>
+        <v>496392</v>
       </c>
       <c r="R56" t="n">
-        <v>7018859</v>
+        <v>7018866</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372382</v>
+        <v>124372810</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496322</v>
+        <v>496460</v>
       </c>
       <c r="R57" t="n">
-        <v>7018864</v>
+        <v>7018885</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372891</v>
+        <v>124372986</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496487</v>
+        <v>496526</v>
       </c>
       <c r="R59" t="n">
-        <v>7018890</v>
+        <v>7018886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372196</v>
+        <v>124372184</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496444</v>
+        <v>496392</v>
       </c>
       <c r="R60" t="n">
-        <v>7018877</v>
+        <v>7018873</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7400,24 +7400,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7428,31 +7418,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7469,7 +7434,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373102</v>
+        <v>124372196</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7514,13 +7479,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496574</v>
+        <v>496444</v>
       </c>
       <c r="R61" t="n">
-        <v>7018897</v>
+        <v>7018877</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7547,14 +7512,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7565,6 +7540,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7581,7 +7581,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372778</v>
+        <v>124373122</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496426</v>
+        <v>496571</v>
       </c>
       <c r="R62" t="n">
-        <v>7018876</v>
+        <v>7018892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372460</v>
+        <v>124372382</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496311</v>
+        <v>496322</v>
       </c>
       <c r="R63" t="n">
-        <v>7018869</v>
+        <v>7018864</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124373142</v>
+        <v>124373030</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7844,21 +7844,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496560</v>
+        <v>496538</v>
       </c>
       <c r="R64" t="n">
-        <v>7018917</v>
+        <v>7018895</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7888,24 +7883,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7916,31 +7901,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7957,7 +7917,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372868</v>
+        <v>124372291</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7993,7 +7953,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8002,10 +7962,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496485</v>
+        <v>496371</v>
       </c>
       <c r="R65" t="n">
-        <v>7018881</v>
+        <v>7018862</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8069,7 +8029,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372291</v>
+        <v>124372868</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8105,7 +8065,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8114,10 +8074,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496371</v>
+        <v>496485</v>
       </c>
       <c r="R66" t="n">
-        <v>7018862</v>
+        <v>7018881</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8181,7 +8141,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124373047</v>
+        <v>124372460</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8226,10 +8186,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496551</v>
+        <v>496311</v>
       </c>
       <c r="R67" t="n">
-        <v>7018894</v>
+        <v>7018869</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8293,7 +8253,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124373122</v>
+        <v>124373142</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8332,16 +8292,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496571</v>
+        <v>496560</v>
       </c>
       <c r="R68" t="n">
-        <v>7018892</v>
+        <v>7018917</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8371,14 +8336,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8389,6 +8364,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8405,7 +8405,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124376085</v>
+        <v>124373091</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8450,10 +8450,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496204</v>
+        <v>496553</v>
       </c>
       <c r="R69" t="n">
-        <v>7018992</v>
+        <v>7018888</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8517,14 +8517,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124366868</v>
+        <v>124372949</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8550,29 +8550,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8581,10 +8562,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496023</v>
+        <v>496504</v>
       </c>
       <c r="R70" t="n">
-        <v>7018919</v>
+        <v>7018879</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8614,24 +8595,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8642,11 +8613,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8663,7 +8629,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372826</v>
+        <v>124372714</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8708,10 +8674,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496446</v>
+        <v>496416</v>
       </c>
       <c r="R71" t="n">
-        <v>7018884</v>
+        <v>7018877</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8775,7 +8741,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372213</v>
+        <v>124372906</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8820,10 +8786,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496392</v>
+        <v>496496</v>
       </c>
       <c r="R72" t="n">
-        <v>7018866</v>
+        <v>7018887</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8887,7 +8853,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372810</v>
+        <v>124372353</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8932,10 +8898,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496460</v>
+        <v>496338</v>
       </c>
       <c r="R73" t="n">
-        <v>7018885</v>
+        <v>7018864</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8999,7 +8965,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372986</v>
+        <v>124372245</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -9044,10 +9010,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496526</v>
+        <v>496380</v>
       </c>
       <c r="R74" t="n">
-        <v>7018886</v>
+        <v>7018867</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9111,14 +9077,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372169</v>
+        <v>124366868</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9144,10 +9110,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9156,10 +9141,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496446</v>
+        <v>496023</v>
       </c>
       <c r="R75" t="n">
-        <v>7018897</v>
+        <v>7018919</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9189,14 +9174,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9207,6 +9202,11 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9223,7 +9223,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372353</v>
+        <v>124372891</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9268,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496338</v>
+        <v>496487</v>
       </c>
       <c r="R76" t="n">
-        <v>7018864</v>
+        <v>7018890</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372714</v>
+        <v>124372169</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496416</v>
+        <v>496446</v>
       </c>
       <c r="R77" t="n">
-        <v>7018877</v>
+        <v>7018897</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9447,7 +9447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124373030</v>
+        <v>124373047</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496538</v>
+        <v>496551</v>
       </c>
       <c r="R78" t="n">
-        <v>7018895</v>
+        <v>7018894</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372234</v>
+        <v>124376085</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496384</v>
+        <v>496204</v>
       </c>
       <c r="R79" t="n">
-        <v>7018864</v>
+        <v>7018992</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372184</v>
+        <v>124372234</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496392</v>
+        <v>496384</v>
       </c>
       <c r="R80" t="n">
-        <v>7018873</v>
+        <v>7018864</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372245</v>
+        <v>124372778</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496380</v>
+        <v>496426</v>
       </c>
       <c r="R81" t="n">
-        <v>7018867</v>
+        <v>7018876</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372906</v>
+        <v>124372406</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496496</v>
+        <v>496324</v>
       </c>
       <c r="R82" t="n">
-        <v>7018887</v>
+        <v>7018859</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124373091</v>
+        <v>124373102</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496553</v>
+        <v>496574</v>
       </c>
       <c r="R83" t="n">
-        <v>7018888</v>
+        <v>7018897</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372949</v>
+        <v>124372826</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496504</v>
+        <v>496446</v>
       </c>
       <c r="R84" t="n">
-        <v>7018879</v>
+        <v>7018884</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124364887</v>
+        <v>124366230</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496078</v>
+        <v>495918</v>
       </c>
       <c r="R2" t="n">
-        <v>7018964</v>
+        <v>7018928</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +753,26 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +781,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374892</v>
+        <v>124372694</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +838,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +862,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496365</v>
+        <v>496555</v>
       </c>
       <c r="R3" t="n">
-        <v>7018964</v>
+        <v>7018901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +895,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +922,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124372052</v>
+        <v>124364937</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +950,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496397</v>
+        <v>496075</v>
       </c>
       <c r="R4" t="n">
-        <v>7018931</v>
+        <v>7018977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +1007,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +1024,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124365804</v>
+        <v>124366246</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496020</v>
+        <v>496045</v>
       </c>
       <c r="R5" t="n">
-        <v>7018934</v>
+        <v>7018931</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124369665</v>
+        <v>124368130</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496219</v>
+        <v>496089</v>
       </c>
       <c r="R6" t="n">
-        <v>7018883</v>
+        <v>7018863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124368504</v>
+        <v>124365832</v>
       </c>
       <c r="B7" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496112</v>
+        <v>496020</v>
       </c>
       <c r="R7" t="n">
-        <v>7018885</v>
+        <v>7018936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124365917</v>
+        <v>124373902</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,43 +1354,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496005</v>
+        <v>496634</v>
       </c>
       <c r="R8" t="n">
-        <v>7018959</v>
+        <v>7019012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,9 +1415,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,22 +1442,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124368893</v>
+        <v>124375665</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496152</v>
+        <v>496298</v>
       </c>
       <c r="R9" t="n">
-        <v>7018906</v>
+        <v>7018981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,9 +1527,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124366502</v>
+        <v>124371804</v>
       </c>
       <c r="B10" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495918</v>
+        <v>496319</v>
       </c>
       <c r="R10" t="n">
-        <v>7018925</v>
+        <v>7018893</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,21 +1644,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1602,31 +1657,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1643,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124375041</v>
+        <v>124365253</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,38 +1685,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496343</v>
+        <v>496029</v>
       </c>
       <c r="R11" t="n">
-        <v>7018997</v>
+        <v>7018921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,11 +1751,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1729,6 +1774,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1745,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124368930</v>
+        <v>124367848</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1785,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496185</v>
+        <v>496067</v>
       </c>
       <c r="R12" t="n">
-        <v>7018934</v>
+        <v>7018881</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,12 +1909,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1882,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375411</v>
+        <v>124370557</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,45 +1944,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1941,13 +1986,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496320</v>
+        <v>496338</v>
       </c>
       <c r="R13" t="n">
-        <v>7018988</v>
+        <v>7018951</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,26 +2019,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2002,11 +2032,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2023,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124367848</v>
+        <v>124375411</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,41 +2060,60 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496067</v>
+        <v>496320</v>
       </c>
       <c r="R14" t="n">
-        <v>7018881</v>
+        <v>7018988</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2152,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 46 plantor och 4 vinterståndare inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,26 +2172,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2160,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124365832</v>
+        <v>124374892</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,21 +2205,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2200,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496020</v>
+        <v>496365</v>
       </c>
       <c r="R15" t="n">
-        <v>7018936</v>
+        <v>7018964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2404,7 +2433,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124374413</v>
+        <v>124364887</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2444,10 +2473,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496449</v>
+        <v>496078</v>
       </c>
       <c r="R17" t="n">
-        <v>7018988</v>
+        <v>7018964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124365439</v>
+        <v>124375602</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,21 +2551,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,13 +2575,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496029</v>
+        <v>496297</v>
       </c>
       <c r="R18" t="n">
-        <v>7018964</v>
+        <v>7018948</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2579,11 +2608,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2592,6 +2631,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2608,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124367729</v>
+        <v>124365230</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,25 +2684,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496047</v>
+        <v>496029</v>
       </c>
       <c r="R19" t="n">
-        <v>7018892</v>
+        <v>7018962</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,10 +2774,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124365230</v>
+        <v>124368930</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,25 +2786,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2750,13 +2814,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496029</v>
+        <v>496185</v>
       </c>
       <c r="R20" t="n">
-        <v>7018962</v>
+        <v>7018934</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,11 +2847,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2796,6 +2870,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2812,7 +2911,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124369981</v>
+        <v>124374769</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2852,13 +2951,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496293</v>
+        <v>496465</v>
       </c>
       <c r="R21" t="n">
-        <v>7018882</v>
+        <v>7018933</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124372694</v>
+        <v>124372203</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2965,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2989,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496555</v>
+        <v>496503</v>
       </c>
       <c r="R22" t="n">
-        <v>7018901</v>
+        <v>7018898</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3133,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,10 +3160,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124369822</v>
+        <v>124365439</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,21 +3176,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3200,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496245</v>
+        <v>496029</v>
       </c>
       <c r="R23" t="n">
-        <v>7018876</v>
+        <v>7018964</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,10 +3262,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124369001</v>
+        <v>124375105</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,21 +3278,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3203,13 +3302,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496205</v>
+        <v>496343</v>
       </c>
       <c r="R24" t="n">
-        <v>7018858</v>
+        <v>7018997</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3236,11 +3335,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3249,6 +3358,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3265,10 +3399,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375665</v>
+        <v>124369822</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,25 +3411,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3439,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496298</v>
+        <v>496245</v>
       </c>
       <c r="R25" t="n">
-        <v>7018981</v>
+        <v>7018876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,24 +3472,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 50 ex på en halv kvm2</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,22 +3489,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124366461</v>
+        <v>124370553</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,36 +3513,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3432,13 +3560,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495944</v>
+        <v>496283</v>
       </c>
       <c r="R26" t="n">
-        <v>7018967</v>
+        <v>7018896</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3467,7 +3595,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3477,7 +3605,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3509,10 +3642,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370431</v>
+        <v>124366031</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>90962</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,21 +3658,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3549,10 +3682,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496343</v>
+        <v>495986</v>
       </c>
       <c r="R27" t="n">
-        <v>7018868</v>
+        <v>7018958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3611,7 +3744,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124372203</v>
+        <v>124373203</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3651,13 +3784,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496503</v>
+        <v>496570</v>
       </c>
       <c r="R28" t="n">
-        <v>7018898</v>
+        <v>7018914</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3686,7 +3819,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3829,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,26 +3840,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124373902</v>
+        <v>124370135</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,25 +3893,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3921,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496634</v>
+        <v>496395</v>
       </c>
       <c r="R29" t="n">
-        <v>7019012</v>
+        <v>7018910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,19 +3954,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>19:55</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>19:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,22 +3971,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124373203</v>
+        <v>124370431</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3851,21 +3999,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3875,13 +4023,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496570</v>
+        <v>496343</v>
       </c>
       <c r="R30" t="n">
-        <v>7018914</v>
+        <v>7018868</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3908,21 +4056,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3931,31 +4069,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3972,10 +4085,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124364937</v>
+        <v>124374616</v>
       </c>
       <c r="B31" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3988,21 +4101,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4012,13 +4125,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496075</v>
+        <v>496506</v>
       </c>
       <c r="R31" t="n">
-        <v>7018977</v>
+        <v>7018942</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4045,11 +4158,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4058,6 +4181,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4074,10 +4222,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124369957</v>
+        <v>124365804</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4090,21 +4238,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4262,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496287</v>
+        <v>496020</v>
       </c>
       <c r="R32" t="n">
-        <v>7018882</v>
+        <v>7018934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,10 +4324,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124370553</v>
+        <v>124368893</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,60 +4336,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496283</v>
+        <v>496152</v>
       </c>
       <c r="R33" t="n">
-        <v>7018896</v>
+        <v>7018906</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4268,26 +4397,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor och 1 vinterståndare inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4296,11 +4410,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4317,10 +4426,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124373649</v>
+        <v>124374980</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4329,46 +4438,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496649</v>
+        <v>496356</v>
       </c>
       <c r="R34" t="n">
-        <v>7018995</v>
+        <v>7018988</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4397,7 +4501,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4407,7 +4511,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,31 +4522,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124366230</v>
+        <v>124367729</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4455,42 +4554,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495918</v>
+        <v>496047</v>
       </c>
       <c r="R35" t="n">
-        <v>7018928</v>
+        <v>7018892</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4517,26 +4611,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4545,31 +4624,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4586,10 +4640,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375105</v>
+        <v>124368223</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4602,21 +4656,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4626,13 +4680,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496343</v>
+        <v>496103</v>
       </c>
       <c r="R36" t="n">
-        <v>7018997</v>
+        <v>7018878</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4659,21 +4713,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4682,31 +4726,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4723,10 +4742,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124375602</v>
+        <v>124369665</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4739,21 +4758,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4763,13 +4782,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496297</v>
+        <v>496219</v>
       </c>
       <c r="R37" t="n">
-        <v>7018948</v>
+        <v>7018883</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4796,21 +4815,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>20:43</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4819,31 +4828,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4860,10 +4844,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124365032</v>
+        <v>124373649</v>
       </c>
       <c r="B38" t="n">
-        <v>96354</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4872,41 +4856,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496041</v>
+        <v>496649</v>
       </c>
       <c r="R38" t="n">
-        <v>7018962</v>
+        <v>7018995</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4933,11 +4922,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4946,6 +4945,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4962,10 +4966,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124366246</v>
+        <v>124366461</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4974,41 +4978,51 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496045</v>
+        <v>495944</v>
       </c>
       <c r="R39" t="n">
-        <v>7018931</v>
+        <v>7018967</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5035,11 +5049,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5048,6 +5072,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5064,10 +5093,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124368130</v>
+        <v>124365867</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5080,21 +5109,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5104,10 +5133,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496089</v>
+        <v>496012</v>
       </c>
       <c r="R40" t="n">
-        <v>7018863</v>
+        <v>7018928</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5166,7 +5195,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124371845</v>
+        <v>124375041</v>
       </c>
       <c r="B41" t="n">
         <v>91012</v>
@@ -5206,10 +5235,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496327</v>
+        <v>496343</v>
       </c>
       <c r="R41" t="n">
-        <v>7018893</v>
+        <v>7018997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5268,7 +5297,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124370135</v>
+        <v>124369001</v>
       </c>
       <c r="B42" t="n">
         <v>91012</v>
@@ -5308,10 +5337,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496395</v>
+        <v>496205</v>
       </c>
       <c r="R42" t="n">
-        <v>7018910</v>
+        <v>7018858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5370,10 +5399,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124370557</v>
+        <v>124371845</v>
       </c>
       <c r="B43" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5386,48 +5415,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496338</v>
+        <v>496327</v>
       </c>
       <c r="R43" t="n">
-        <v>7018951</v>
+        <v>7018893</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5486,10 +5501,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124367876</v>
+        <v>124374413</v>
       </c>
       <c r="B44" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5498,25 +5513,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5526,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496096</v>
+        <v>496449</v>
       </c>
       <c r="R44" t="n">
-        <v>7018871</v>
+        <v>7018988</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5588,10 +5603,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374769</v>
+        <v>124375158</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5600,38 +5615,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496465</v>
+        <v>496311</v>
       </c>
       <c r="R45" t="n">
-        <v>7018933</v>
+        <v>7018994</v>
       </c>
       <c r="S45" t="n">
         <v>7</v>
@@ -5663,7 +5692,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5673,7 +5702,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5688,26 +5717,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5725,10 +5734,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124365867</v>
+        <v>124369957</v>
       </c>
       <c r="B46" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5741,21 +5750,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5765,10 +5774,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496012</v>
+        <v>496287</v>
       </c>
       <c r="R46" t="n">
-        <v>7018928</v>
+        <v>7018882</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5827,10 +5836,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374980</v>
+        <v>124368504</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>82597</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5843,21 +5852,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5867,10 +5876,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496356</v>
+        <v>496112</v>
       </c>
       <c r="R47" t="n">
-        <v>7018988</v>
+        <v>7018885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5900,19 +5909,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>20:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,22 +5926,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124369222</v>
+        <v>124366502</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5951,25 +5950,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5979,13 +5978,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496155</v>
+        <v>495918</v>
       </c>
       <c r="R48" t="n">
-        <v>7018842</v>
+        <v>7018925</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6012,11 +6011,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6025,6 +6034,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6041,10 +6075,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124375158</v>
+        <v>124365917</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6053,40 +6087,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6095,13 +6120,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496311</v>
+        <v>496005</v>
       </c>
       <c r="R49" t="n">
-        <v>7018994</v>
+        <v>7018959</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6128,21 +6153,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>20:28</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6151,11 +6166,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6172,10 +6182,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124374616</v>
+        <v>124369222</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6188,21 +6198,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6212,13 +6222,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496506</v>
+        <v>496155</v>
       </c>
       <c r="R50" t="n">
-        <v>7018942</v>
+        <v>7018842</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6245,21 +6255,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>20:11</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6268,31 +6268,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6309,7 +6284,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124368788</v>
+        <v>124372052</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6349,13 +6324,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496168</v>
+        <v>496397</v>
       </c>
       <c r="R51" t="n">
-        <v>7018906</v>
+        <v>7018931</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6384,7 +6359,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6394,7 +6369,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,51 +6380,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124368223</v>
+        <v>124368788</v>
       </c>
       <c r="B52" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6462,21 +6412,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6486,13 +6436,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496103</v>
+        <v>496168</v>
       </c>
       <c r="R52" t="n">
-        <v>7018878</v>
+        <v>7018906</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6519,11 +6469,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6532,6 +6492,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6548,10 +6533,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124366031</v>
+        <v>124365032</v>
       </c>
       <c r="B53" t="n">
-        <v>90962</v>
+        <v>96354</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6564,21 +6549,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6588,10 +6573,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495986</v>
+        <v>496041</v>
       </c>
       <c r="R53" t="n">
-        <v>7018958</v>
+        <v>7018962</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6650,10 +6635,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124371804</v>
+        <v>124369981</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6666,21 +6651,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6690,13 +6675,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496319</v>
+        <v>496293</v>
       </c>
       <c r="R54" t="n">
-        <v>7018893</v>
+        <v>7018882</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6723,11 +6708,21 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6736,6 +6731,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6752,10 +6772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124365253</v>
+        <v>124367876</v>
       </c>
       <c r="B55" t="n">
-        <v>100279</v>
+        <v>90977</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6768,39 +6788,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496029</v>
+        <v>496096</v>
       </c>
       <c r="R55" t="n">
-        <v>7018921</v>
+        <v>7018871</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6830,21 +6845,11 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6853,11 +6858,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372213</v>
+        <v>124372714</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496392</v>
+        <v>496416</v>
       </c>
       <c r="R56" t="n">
-        <v>7018866</v>
+        <v>7018877</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372810</v>
+        <v>124372291</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7022,7 +7022,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496460</v>
+        <v>496371</v>
       </c>
       <c r="R57" t="n">
-        <v>7018885</v>
+        <v>7018862</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372343</v>
+        <v>124372891</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496345</v>
+        <v>496487</v>
       </c>
       <c r="R58" t="n">
-        <v>7018866</v>
+        <v>7018890</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372986</v>
+        <v>124373047</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496526</v>
+        <v>496551</v>
       </c>
       <c r="R59" t="n">
-        <v>7018886</v>
+        <v>7018894</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372184</v>
+        <v>124372986</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496392</v>
+        <v>496526</v>
       </c>
       <c r="R60" t="n">
-        <v>7018873</v>
+        <v>7018886</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7434,7 +7434,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372196</v>
+        <v>124373030</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7479,13 +7479,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496444</v>
+        <v>496538</v>
       </c>
       <c r="R61" t="n">
-        <v>7018877</v>
+        <v>7018895</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7512,24 +7512,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7540,31 +7530,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7693,7 +7658,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372382</v>
+        <v>124376085</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7738,10 +7703,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496322</v>
+        <v>496204</v>
       </c>
       <c r="R63" t="n">
-        <v>7018864</v>
+        <v>7018992</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7805,7 +7770,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124373030</v>
+        <v>124373102</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7850,10 +7815,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496538</v>
+        <v>496574</v>
       </c>
       <c r="R64" t="n">
-        <v>7018895</v>
+        <v>7018897</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7917,7 +7882,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372291</v>
+        <v>124372382</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7953,7 +7918,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7962,10 +7927,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496371</v>
+        <v>496322</v>
       </c>
       <c r="R65" t="n">
-        <v>7018862</v>
+        <v>7018864</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8029,7 +7994,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372868</v>
+        <v>124372460</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8074,10 +8039,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496485</v>
+        <v>496311</v>
       </c>
       <c r="R66" t="n">
-        <v>7018881</v>
+        <v>7018869</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8141,7 +8106,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372460</v>
+        <v>124372826</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8186,10 +8151,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496311</v>
+        <v>496446</v>
       </c>
       <c r="R67" t="n">
-        <v>7018869</v>
+        <v>7018884</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8253,7 +8218,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124373142</v>
+        <v>124372245</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8292,21 +8257,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496560</v>
+        <v>496380</v>
       </c>
       <c r="R68" t="n">
-        <v>7018917</v>
+        <v>7018867</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8336,24 +8296,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8364,31 +8314,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8517,7 +8442,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372949</v>
+        <v>124372213</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8562,10 +8487,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496504</v>
+        <v>496392</v>
       </c>
       <c r="R70" t="n">
-        <v>7018879</v>
+        <v>7018866</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8629,7 +8554,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372714</v>
+        <v>124372906</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8674,10 +8599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496416</v>
+        <v>496496</v>
       </c>
       <c r="R71" t="n">
-        <v>7018877</v>
+        <v>7018887</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8741,7 +8666,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372906</v>
+        <v>124373142</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8780,16 +8705,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496496</v>
+        <v>496560</v>
       </c>
       <c r="R72" t="n">
-        <v>7018887</v>
+        <v>7018917</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8819,14 +8749,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8837,6 +8777,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8853,7 +8818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372353</v>
+        <v>124372810</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8898,10 +8863,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496338</v>
+        <v>496460</v>
       </c>
       <c r="R73" t="n">
-        <v>7018864</v>
+        <v>7018885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8965,7 +8930,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372245</v>
+        <v>124372343</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -9010,10 +8975,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496380</v>
+        <v>496345</v>
       </c>
       <c r="R74" t="n">
-        <v>7018867</v>
+        <v>7018866</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9077,14 +9042,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124366868</v>
+        <v>124372868</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9110,29 +9075,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9141,10 +9087,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496023</v>
+        <v>496485</v>
       </c>
       <c r="R75" t="n">
-        <v>7018919</v>
+        <v>7018881</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9174,24 +9120,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9202,11 +9138,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9223,7 +9154,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372891</v>
+        <v>124372778</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9268,10 +9199,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496487</v>
+        <v>496426</v>
       </c>
       <c r="R76" t="n">
-        <v>7018890</v>
+        <v>7018876</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9335,7 +9266,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372169</v>
+        <v>124372949</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9380,10 +9311,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496446</v>
+        <v>496504</v>
       </c>
       <c r="R77" t="n">
-        <v>7018897</v>
+        <v>7018879</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9447,7 +9378,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124373047</v>
+        <v>124372184</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9492,10 +9423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496551</v>
+        <v>496392</v>
       </c>
       <c r="R78" t="n">
-        <v>7018894</v>
+        <v>7018873</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9559,7 +9490,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124376085</v>
+        <v>124372169</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9604,10 +9535,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496204</v>
+        <v>496446</v>
       </c>
       <c r="R79" t="n">
-        <v>7018992</v>
+        <v>7018897</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9671,14 +9602,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372234</v>
+        <v>124366868</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9704,10 +9635,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9716,10 +9666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496384</v>
+        <v>496023</v>
       </c>
       <c r="R80" t="n">
-        <v>7018864</v>
+        <v>7018919</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9749,14 +9699,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9767,6 +9727,11 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9783,7 +9748,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372778</v>
+        <v>124372196</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9828,13 +9793,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496426</v>
+        <v>496444</v>
       </c>
       <c r="R81" t="n">
-        <v>7018876</v>
+        <v>7018877</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9861,14 +9826,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9879,6 +9854,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372406</v>
+        <v>124372353</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496324</v>
+        <v>496338</v>
       </c>
       <c r="R82" t="n">
-        <v>7018859</v>
+        <v>7018864</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124373102</v>
+        <v>124372406</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496574</v>
+        <v>496324</v>
       </c>
       <c r="R83" t="n">
-        <v>7018897</v>
+        <v>7018859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372826</v>
+        <v>124372234</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496446</v>
+        <v>496384</v>
       </c>
       <c r="R84" t="n">
-        <v>7018884</v>
+        <v>7018864</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372714</v>
+        <v>124372406</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496416</v>
+        <v>496324</v>
       </c>
       <c r="R56" t="n">
-        <v>7018877</v>
+        <v>7018859</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372291</v>
+        <v>124372213</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7022,7 +7022,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496371</v>
+        <v>496392</v>
       </c>
       <c r="R57" t="n">
-        <v>7018862</v>
+        <v>7018866</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372891</v>
+        <v>124373122</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496487</v>
+        <v>496571</v>
       </c>
       <c r="R58" t="n">
-        <v>7018890</v>
+        <v>7018892</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124373047</v>
+        <v>124372382</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496551</v>
+        <v>496322</v>
       </c>
       <c r="R59" t="n">
-        <v>7018894</v>
+        <v>7018864</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372986</v>
+        <v>124373142</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7361,16 +7361,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496526</v>
+        <v>496560</v>
       </c>
       <c r="R60" t="n">
-        <v>7018886</v>
+        <v>7018917</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7400,14 +7405,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,6 +7433,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7434,7 +7474,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373030</v>
+        <v>124372184</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7479,10 +7519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496538</v>
+        <v>496392</v>
       </c>
       <c r="R61" t="n">
-        <v>7018895</v>
+        <v>7018873</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,7 +7586,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124373122</v>
+        <v>124372291</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7582,7 +7622,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7591,10 +7631,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496571</v>
+        <v>496371</v>
       </c>
       <c r="R62" t="n">
-        <v>7018892</v>
+        <v>7018862</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7658,7 +7698,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124376085</v>
+        <v>124372868</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7703,10 +7743,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496204</v>
+        <v>496485</v>
       </c>
       <c r="R63" t="n">
-        <v>7018992</v>
+        <v>7018881</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7770,7 +7810,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124373102</v>
+        <v>124372778</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7815,10 +7855,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496574</v>
+        <v>496426</v>
       </c>
       <c r="R64" t="n">
-        <v>7018897</v>
+        <v>7018876</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7882,7 +7922,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372382</v>
+        <v>124372949</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7927,10 +7967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496322</v>
+        <v>496504</v>
       </c>
       <c r="R65" t="n">
-        <v>7018864</v>
+        <v>7018879</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7994,7 +8034,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372460</v>
+        <v>124372353</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8039,10 +8079,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496311</v>
+        <v>496338</v>
       </c>
       <c r="R66" t="n">
-        <v>7018869</v>
+        <v>7018864</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8106,14 +8146,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372826</v>
+        <v>124366868</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8139,10 +8179,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8151,10 +8210,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496446</v>
+        <v>496023</v>
       </c>
       <c r="R67" t="n">
-        <v>7018884</v>
+        <v>7018919</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8184,14 +8243,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8202,6 +8271,11 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8218,7 +8292,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372245</v>
+        <v>124373091</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8263,10 +8337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496380</v>
+        <v>496553</v>
       </c>
       <c r="R68" t="n">
-        <v>7018867</v>
+        <v>7018888</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8330,7 +8404,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124373091</v>
+        <v>124372169</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8375,10 +8449,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496553</v>
+        <v>496446</v>
       </c>
       <c r="R69" t="n">
-        <v>7018888</v>
+        <v>7018897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8442,7 +8516,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372213</v>
+        <v>124372196</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8487,13 +8561,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496392</v>
+        <v>496444</v>
       </c>
       <c r="R70" t="n">
-        <v>7018866</v>
+        <v>7018877</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8520,14 +8594,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8538,6 +8622,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8554,7 +8663,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372906</v>
+        <v>124372891</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8599,10 +8708,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496496</v>
+        <v>496487</v>
       </c>
       <c r="R71" t="n">
-        <v>7018887</v>
+        <v>7018890</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8666,7 +8775,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373142</v>
+        <v>124373102</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
@@ -8705,21 +8814,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496560</v>
+        <v>496574</v>
       </c>
       <c r="R72" t="n">
-        <v>7018917</v>
+        <v>7018897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8749,24 +8853,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8777,31 +8871,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8818,7 +8887,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372810</v>
+        <v>124372906</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8863,10 +8932,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496460</v>
+        <v>496496</v>
       </c>
       <c r="R73" t="n">
-        <v>7018885</v>
+        <v>7018887</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8930,7 +8999,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372343</v>
+        <v>124372810</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -8975,10 +9044,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496345</v>
+        <v>496460</v>
       </c>
       <c r="R74" t="n">
-        <v>7018866</v>
+        <v>7018885</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9042,7 +9111,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372868</v>
+        <v>124372343</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9087,10 +9156,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496485</v>
+        <v>496345</v>
       </c>
       <c r="R75" t="n">
-        <v>7018881</v>
+        <v>7018866</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9154,7 +9223,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372778</v>
+        <v>124376085</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9199,10 +9268,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496426</v>
+        <v>496204</v>
       </c>
       <c r="R76" t="n">
-        <v>7018876</v>
+        <v>7018992</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9266,7 +9335,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372949</v>
+        <v>124372714</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9311,10 +9380,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496504</v>
+        <v>496416</v>
       </c>
       <c r="R77" t="n">
-        <v>7018879</v>
+        <v>7018877</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9378,7 +9447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372184</v>
+        <v>124372826</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9423,10 +9492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496392</v>
+        <v>496446</v>
       </c>
       <c r="R78" t="n">
-        <v>7018873</v>
+        <v>7018884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9490,7 +9559,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372169</v>
+        <v>124373047</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9535,10 +9604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496446</v>
+        <v>496551</v>
       </c>
       <c r="R79" t="n">
-        <v>7018897</v>
+        <v>7018894</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9602,14 +9671,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124366868</v>
+        <v>124372245</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9635,29 +9704,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9666,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496023</v>
+        <v>496380</v>
       </c>
       <c r="R80" t="n">
-        <v>7018919</v>
+        <v>7018867</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9699,24 +9749,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9727,11 +9767,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9748,7 +9783,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372196</v>
+        <v>124372460</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9793,13 +9828,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496444</v>
+        <v>496311</v>
       </c>
       <c r="R81" t="n">
-        <v>7018877</v>
+        <v>7018869</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9826,24 +9861,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9854,31 +9879,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372353</v>
+        <v>124373030</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496338</v>
+        <v>496538</v>
       </c>
       <c r="R82" t="n">
-        <v>7018864</v>
+        <v>7018895</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372406</v>
+        <v>124372234</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496324</v>
+        <v>496384</v>
       </c>
       <c r="R83" t="n">
-        <v>7018859</v>
+        <v>7018864</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372234</v>
+        <v>124372986</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496384</v>
+        <v>496526</v>
       </c>
       <c r="R84" t="n">
-        <v>7018864</v>
+        <v>7018886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372406</v>
+        <v>124372234</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496324</v>
+        <v>496384</v>
       </c>
       <c r="R56" t="n">
-        <v>7018859</v>
+        <v>7018864</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372213</v>
+        <v>124373122</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496392</v>
+        <v>496571</v>
       </c>
       <c r="R57" t="n">
-        <v>7018866</v>
+        <v>7018892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124373122</v>
+        <v>124372213</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496571</v>
+        <v>496392</v>
       </c>
       <c r="R58" t="n">
-        <v>7018892</v>
+        <v>7018866</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372382</v>
+        <v>124372891</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496322</v>
+        <v>496487</v>
       </c>
       <c r="R59" t="n">
-        <v>7018864</v>
+        <v>7018890</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124373142</v>
+        <v>124372245</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7361,21 +7361,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496560</v>
+        <v>496380</v>
       </c>
       <c r="R60" t="n">
-        <v>7018917</v>
+        <v>7018867</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7405,24 +7400,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7433,31 +7418,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7474,7 +7434,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372184</v>
+        <v>124373047</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7519,10 +7479,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496392</v>
+        <v>496551</v>
       </c>
       <c r="R61" t="n">
-        <v>7018873</v>
+        <v>7018894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7586,7 +7546,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372291</v>
+        <v>124372810</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7622,7 +7582,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7631,10 +7591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496371</v>
+        <v>496460</v>
       </c>
       <c r="R62" t="n">
-        <v>7018862</v>
+        <v>7018885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7698,7 +7658,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372868</v>
+        <v>124372826</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7743,10 +7703,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496485</v>
+        <v>496446</v>
       </c>
       <c r="R63" t="n">
-        <v>7018881</v>
+        <v>7018884</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8034,7 +7994,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372353</v>
+        <v>124372169</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8079,10 +8039,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496338</v>
+        <v>496446</v>
       </c>
       <c r="R66" t="n">
-        <v>7018864</v>
+        <v>7018897</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8146,14 +8106,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124366868</v>
+        <v>124372184</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8179,29 +8139,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8210,10 +8151,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496023</v>
+        <v>496392</v>
       </c>
       <c r="R67" t="n">
-        <v>7018919</v>
+        <v>7018873</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8243,24 +8184,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8271,11 +8202,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8292,7 +8218,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124373091</v>
+        <v>124376085</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8337,10 +8263,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496553</v>
+        <v>496204</v>
       </c>
       <c r="R68" t="n">
-        <v>7018888</v>
+        <v>7018992</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8404,7 +8330,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372169</v>
+        <v>124372406</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8449,10 +8375,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496446</v>
+        <v>496324</v>
       </c>
       <c r="R69" t="n">
-        <v>7018897</v>
+        <v>7018859</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8516,7 +8442,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372196</v>
+        <v>124372382</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8561,13 +8487,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496444</v>
+        <v>496322</v>
       </c>
       <c r="R70" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8594,24 +8520,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8622,31 +8538,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8663,7 +8554,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372891</v>
+        <v>124373142</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8702,16 +8593,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496487</v>
+        <v>496560</v>
       </c>
       <c r="R71" t="n">
-        <v>7018890</v>
+        <v>7018917</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8741,14 +8637,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8759,6 +8665,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8775,14 +8706,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373102</v>
+        <v>124366868</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8808,10 +8739,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8820,10 +8770,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496574</v>
+        <v>496023</v>
       </c>
       <c r="R72" t="n">
-        <v>7018897</v>
+        <v>7018919</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8853,14 +8803,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8871,6 +8831,11 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8887,7 +8852,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372906</v>
+        <v>124372343</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8932,10 +8897,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496496</v>
+        <v>496345</v>
       </c>
       <c r="R73" t="n">
-        <v>7018887</v>
+        <v>7018866</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8999,7 +8964,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372810</v>
+        <v>124373102</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -9044,10 +9009,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496460</v>
+        <v>496574</v>
       </c>
       <c r="R74" t="n">
-        <v>7018885</v>
+        <v>7018897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9111,7 +9076,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372343</v>
+        <v>124372353</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9156,10 +9121,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496345</v>
+        <v>496338</v>
       </c>
       <c r="R75" t="n">
-        <v>7018866</v>
+        <v>7018864</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9223,7 +9188,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124376085</v>
+        <v>124372714</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9268,10 +9233,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496204</v>
+        <v>496416</v>
       </c>
       <c r="R76" t="n">
-        <v>7018992</v>
+        <v>7018877</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9335,7 +9300,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372714</v>
+        <v>124372196</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9380,13 +9345,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496416</v>
+        <v>496444</v>
       </c>
       <c r="R77" t="n">
         <v>7018877</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9413,14 +9378,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9431,6 +9406,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9447,7 +9447,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372826</v>
+        <v>124372906</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496446</v>
+        <v>496496</v>
       </c>
       <c r="R78" t="n">
-        <v>7018884</v>
+        <v>7018887</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124373047</v>
+        <v>124372868</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496551</v>
+        <v>496485</v>
       </c>
       <c r="R79" t="n">
-        <v>7018894</v>
+        <v>7018881</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372245</v>
+        <v>124373030</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496380</v>
+        <v>496538</v>
       </c>
       <c r="R80" t="n">
-        <v>7018867</v>
+        <v>7018895</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372460</v>
+        <v>124373091</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496311</v>
+        <v>496553</v>
       </c>
       <c r="R81" t="n">
-        <v>7018869</v>
+        <v>7018888</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124373030</v>
+        <v>124372291</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9931,7 +9931,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496538</v>
+        <v>496371</v>
       </c>
       <c r="R82" t="n">
-        <v>7018895</v>
+        <v>7018862</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372234</v>
+        <v>124372460</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496384</v>
+        <v>496311</v>
       </c>
       <c r="R83" t="n">
-        <v>7018864</v>
+        <v>7018869</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372234</v>
+        <v>124372906</v>
       </c>
       <c r="B56" t="n">
         <v>57513</v>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496384</v>
+        <v>496496</v>
       </c>
       <c r="R56" t="n">
-        <v>7018864</v>
+        <v>7018887</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124373122</v>
+        <v>124372343</v>
       </c>
       <c r="B57" t="n">
         <v>57513</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496571</v>
+        <v>496345</v>
       </c>
       <c r="R57" t="n">
-        <v>7018892</v>
+        <v>7018866</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372213</v>
+        <v>124373102</v>
       </c>
       <c r="B58" t="n">
         <v>57513</v>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496392</v>
+        <v>496574</v>
       </c>
       <c r="R58" t="n">
-        <v>7018866</v>
+        <v>7018897</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372891</v>
+        <v>124372868</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496487</v>
+        <v>496485</v>
       </c>
       <c r="R59" t="n">
-        <v>7018890</v>
+        <v>7018881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372245</v>
+        <v>124372196</v>
       </c>
       <c r="B60" t="n">
         <v>57513</v>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496380</v>
+        <v>496444</v>
       </c>
       <c r="R60" t="n">
-        <v>7018867</v>
+        <v>7018877</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7400,14 +7400,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7418,6 +7428,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7434,7 +7469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373047</v>
+        <v>124372714</v>
       </c>
       <c r="B61" t="n">
         <v>57513</v>
@@ -7479,10 +7514,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496551</v>
+        <v>496416</v>
       </c>
       <c r="R61" t="n">
-        <v>7018894</v>
+        <v>7018877</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,7 +7581,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372810</v>
+        <v>124372949</v>
       </c>
       <c r="B62" t="n">
         <v>57513</v>
@@ -7591,10 +7626,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496460</v>
+        <v>496504</v>
       </c>
       <c r="R62" t="n">
-        <v>7018885</v>
+        <v>7018879</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7658,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372826</v>
+        <v>124372213</v>
       </c>
       <c r="B63" t="n">
         <v>57513</v>
@@ -7703,10 +7738,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496446</v>
+        <v>496392</v>
       </c>
       <c r="R63" t="n">
-        <v>7018884</v>
+        <v>7018866</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7770,7 +7805,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372778</v>
+        <v>124372291</v>
       </c>
       <c r="B64" t="n">
         <v>57513</v>
@@ -7806,7 +7841,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7815,10 +7850,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496426</v>
+        <v>496371</v>
       </c>
       <c r="R64" t="n">
-        <v>7018876</v>
+        <v>7018862</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7882,7 +7917,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372949</v>
+        <v>124372891</v>
       </c>
       <c r="B65" t="n">
         <v>57513</v>
@@ -7927,10 +7962,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496504</v>
+        <v>496487</v>
       </c>
       <c r="R65" t="n">
-        <v>7018879</v>
+        <v>7018890</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7994,7 +8029,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372169</v>
+        <v>124372986</v>
       </c>
       <c r="B66" t="n">
         <v>57513</v>
@@ -8039,10 +8074,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496446</v>
+        <v>496526</v>
       </c>
       <c r="R66" t="n">
-        <v>7018897</v>
+        <v>7018886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8106,7 +8141,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372184</v>
+        <v>124373030</v>
       </c>
       <c r="B67" t="n">
         <v>57513</v>
@@ -8151,10 +8186,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496392</v>
+        <v>496538</v>
       </c>
       <c r="R67" t="n">
-        <v>7018873</v>
+        <v>7018895</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8218,7 +8253,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376085</v>
+        <v>124372826</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -8263,10 +8298,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496204</v>
+        <v>496446</v>
       </c>
       <c r="R68" t="n">
-        <v>7018992</v>
+        <v>7018884</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8330,7 +8365,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372406</v>
+        <v>124373047</v>
       </c>
       <c r="B69" t="n">
         <v>57513</v>
@@ -8375,10 +8410,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496324</v>
+        <v>496551</v>
       </c>
       <c r="R69" t="n">
-        <v>7018859</v>
+        <v>7018894</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8442,7 +8477,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372382</v>
+        <v>124373091</v>
       </c>
       <c r="B70" t="n">
         <v>57513</v>
@@ -8487,10 +8522,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496322</v>
+        <v>496553</v>
       </c>
       <c r="R70" t="n">
-        <v>7018864</v>
+        <v>7018888</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8554,7 +8589,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124373142</v>
+        <v>124372810</v>
       </c>
       <c r="B71" t="n">
         <v>57513</v>
@@ -8593,21 +8628,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496560</v>
+        <v>496460</v>
       </c>
       <c r="R71" t="n">
-        <v>7018917</v>
+        <v>7018885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8637,24 +8667,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8665,31 +8685,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8706,14 +8701,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124366868</v>
+        <v>124372778</v>
       </c>
       <c r="B72" t="n">
         <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8739,29 +8734,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8770,10 +8746,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496023</v>
+        <v>496426</v>
       </c>
       <c r="R72" t="n">
-        <v>7018919</v>
+        <v>7018876</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8803,24 +8779,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8831,11 +8797,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8852,7 +8813,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372343</v>
+        <v>124372234</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -8897,10 +8858,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496345</v>
+        <v>496384</v>
       </c>
       <c r="R73" t="n">
-        <v>7018866</v>
+        <v>7018864</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8964,7 +8925,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124373102</v>
+        <v>124373122</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -9009,10 +8970,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496574</v>
+        <v>496571</v>
       </c>
       <c r="R74" t="n">
-        <v>7018897</v>
+        <v>7018892</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9076,7 +9037,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372353</v>
+        <v>124372245</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -9121,10 +9082,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496338</v>
+        <v>496380</v>
       </c>
       <c r="R75" t="n">
-        <v>7018864</v>
+        <v>7018867</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9188,7 +9149,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372714</v>
+        <v>124372353</v>
       </c>
       <c r="B76" t="n">
         <v>57513</v>
@@ -9233,10 +9194,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496416</v>
+        <v>496338</v>
       </c>
       <c r="R76" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9300,7 +9261,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372196</v>
+        <v>124376085</v>
       </c>
       <c r="B77" t="n">
         <v>57513</v>
@@ -9345,13 +9306,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496444</v>
+        <v>496204</v>
       </c>
       <c r="R77" t="n">
-        <v>7018877</v>
+        <v>7018992</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9378,24 +9339,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9406,31 +9357,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9447,14 +9373,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124372906</v>
+        <v>124366868</v>
       </c>
       <c r="B78" t="n">
         <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9480,10 +9406,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9492,10 +9437,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496496</v>
+        <v>496023</v>
       </c>
       <c r="R78" t="n">
-        <v>7018887</v>
+        <v>7018919</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9525,14 +9470,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9543,6 +9498,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9559,7 +9519,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372868</v>
+        <v>124372184</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -9604,10 +9564,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496485</v>
+        <v>496392</v>
       </c>
       <c r="R79" t="n">
-        <v>7018881</v>
+        <v>7018873</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9671,7 +9631,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124373030</v>
+        <v>124372169</v>
       </c>
       <c r="B80" t="n">
         <v>57513</v>
@@ -9716,10 +9676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496538</v>
+        <v>496446</v>
       </c>
       <c r="R80" t="n">
-        <v>7018895</v>
+        <v>7018897</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9783,7 +9743,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124373091</v>
+        <v>124372382</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -9828,10 +9788,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496553</v>
+        <v>496322</v>
       </c>
       <c r="R81" t="n">
-        <v>7018888</v>
+        <v>7018864</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9895,7 +9855,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372291</v>
+        <v>124372460</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -9931,7 +9891,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9940,10 +9900,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496371</v>
+        <v>496311</v>
       </c>
       <c r="R82" t="n">
-        <v>7018862</v>
+        <v>7018869</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +9967,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372460</v>
+        <v>124372406</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -10052,10 +10012,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496311</v>
+        <v>496324</v>
       </c>
       <c r="R83" t="n">
-        <v>7018869</v>
+        <v>7018859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10079,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372986</v>
+        <v>124373142</v>
       </c>
       <c r="B84" t="n">
         <v>57513</v>
@@ -10158,16 +10118,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496526</v>
+        <v>496560</v>
       </c>
       <c r="R84" t="n">
-        <v>7018886</v>
+        <v>7018917</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10197,14 +10162,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10215,6 +10190,31 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -6874,10 +6874,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372906</v>
+        <v>124373142</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6913,16 +6913,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496496</v>
+        <v>496560</v>
       </c>
       <c r="R56" t="n">
-        <v>7018887</v>
+        <v>7018917</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6952,14 +6957,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6970,6 +6985,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6986,10 +7026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372343</v>
+        <v>124372382</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7031,10 +7071,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496345</v>
+        <v>496322</v>
       </c>
       <c r="R57" t="n">
-        <v>7018866</v>
+        <v>7018864</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,10 +7138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124373102</v>
+        <v>124372714</v>
       </c>
       <c r="B58" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7143,10 +7183,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496574</v>
+        <v>496416</v>
       </c>
       <c r="R58" t="n">
-        <v>7018897</v>
+        <v>7018877</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,10 +7250,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372868</v>
+        <v>124372169</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7255,10 +7295,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496485</v>
+        <v>496446</v>
       </c>
       <c r="R59" t="n">
-        <v>7018881</v>
+        <v>7018897</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,10 +7362,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372196</v>
+        <v>124372234</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7367,13 +7407,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496444</v>
+        <v>496384</v>
       </c>
       <c r="R60" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7400,24 +7440,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7428,31 +7458,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7469,10 +7474,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124372714</v>
+        <v>124373091</v>
       </c>
       <c r="B61" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7514,10 +7519,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496416</v>
+        <v>496553</v>
       </c>
       <c r="R61" t="n">
-        <v>7018877</v>
+        <v>7018888</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7581,10 +7586,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372949</v>
+        <v>124372406</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7626,10 +7631,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496504</v>
+        <v>496324</v>
       </c>
       <c r="R62" t="n">
-        <v>7018879</v>
+        <v>7018859</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7693,10 +7698,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372213</v>
+        <v>124372184</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7741,7 +7746,7 @@
         <v>496392</v>
       </c>
       <c r="R63" t="n">
-        <v>7018866</v>
+        <v>7018873</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7805,10 +7810,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372291</v>
+        <v>124373047</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7841,7 +7846,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7850,10 +7855,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496371</v>
+        <v>496551</v>
       </c>
       <c r="R64" t="n">
-        <v>7018862</v>
+        <v>7018894</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7917,10 +7922,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372891</v>
+        <v>124372778</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7962,10 +7967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496487</v>
+        <v>496426</v>
       </c>
       <c r="R65" t="n">
-        <v>7018890</v>
+        <v>7018876</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8029,10 +8034,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372986</v>
+        <v>124372353</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8074,10 +8079,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496526</v>
+        <v>496338</v>
       </c>
       <c r="R66" t="n">
-        <v>7018886</v>
+        <v>7018864</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8144,7 +8149,7 @@
         <v>124373030</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8253,10 +8258,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372826</v>
+        <v>124372196</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8298,13 +8303,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496446</v>
+        <v>496444</v>
       </c>
       <c r="R68" t="n">
-        <v>7018884</v>
+        <v>7018877</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8331,14 +8336,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8349,6 +8364,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8365,10 +8405,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124373047</v>
+        <v>124372891</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8410,10 +8450,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496551</v>
+        <v>496487</v>
       </c>
       <c r="R69" t="n">
-        <v>7018894</v>
+        <v>7018890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8477,10 +8517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124373091</v>
+        <v>124372810</v>
       </c>
       <c r="B70" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8522,10 +8562,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496553</v>
+        <v>496460</v>
       </c>
       <c r="R70" t="n">
-        <v>7018888</v>
+        <v>7018885</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8589,10 +8629,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372810</v>
+        <v>124372460</v>
       </c>
       <c r="B71" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8634,10 +8674,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496460</v>
+        <v>496311</v>
       </c>
       <c r="R71" t="n">
-        <v>7018885</v>
+        <v>7018869</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8701,10 +8741,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372778</v>
+        <v>124372906</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8746,10 +8786,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496426</v>
+        <v>496496</v>
       </c>
       <c r="R72" t="n">
-        <v>7018876</v>
+        <v>7018887</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8813,10 +8853,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372234</v>
+        <v>124372343</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8858,10 +8898,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496384</v>
+        <v>496345</v>
       </c>
       <c r="R73" t="n">
-        <v>7018864</v>
+        <v>7018866</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8925,10 +8965,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124373122</v>
+        <v>124372949</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8970,10 +9010,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496571</v>
+        <v>496504</v>
       </c>
       <c r="R74" t="n">
-        <v>7018892</v>
+        <v>7018879</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9037,10 +9077,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372245</v>
+        <v>124372986</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9082,10 +9122,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496380</v>
+        <v>496526</v>
       </c>
       <c r="R75" t="n">
-        <v>7018867</v>
+        <v>7018886</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9149,10 +9189,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124372353</v>
+        <v>124373122</v>
       </c>
       <c r="B76" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9194,10 +9234,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496338</v>
+        <v>496571</v>
       </c>
       <c r="R76" t="n">
-        <v>7018864</v>
+        <v>7018892</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9261,10 +9301,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124376085</v>
+        <v>124372291</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9297,7 +9337,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9306,10 +9346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496204</v>
+        <v>496371</v>
       </c>
       <c r="R77" t="n">
-        <v>7018992</v>
+        <v>7018862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9373,14 +9413,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124366868</v>
+        <v>124373102</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9406,29 +9446,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9437,10 +9458,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496023</v>
+        <v>496574</v>
       </c>
       <c r="R78" t="n">
-        <v>7018919</v>
+        <v>7018897</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9470,24 +9491,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9498,11 +9509,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9519,10 +9525,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372184</v>
+        <v>124372213</v>
       </c>
       <c r="B79" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9567,7 +9573,7 @@
         <v>496392</v>
       </c>
       <c r="R79" t="n">
-        <v>7018873</v>
+        <v>7018866</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9631,10 +9637,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372169</v>
+        <v>124372245</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9676,10 +9682,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496446</v>
+        <v>496380</v>
       </c>
       <c r="R80" t="n">
-        <v>7018897</v>
+        <v>7018867</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9743,14 +9749,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124372382</v>
+        <v>124366868</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9776,10 +9782,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9788,10 +9813,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496322</v>
+        <v>496023</v>
       </c>
       <c r="R81" t="n">
-        <v>7018864</v>
+        <v>7018919</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9821,14 +9846,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9839,6 +9874,11 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9855,10 +9895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372460</v>
+        <v>124372826</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9900,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496311</v>
+        <v>496446</v>
       </c>
       <c r="R82" t="n">
-        <v>7018869</v>
+        <v>7018884</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9967,10 +10007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124372406</v>
+        <v>124376085</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10012,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496324</v>
+        <v>496204</v>
       </c>
       <c r="R83" t="n">
-        <v>7018859</v>
+        <v>7018992</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10079,10 +10119,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124373142</v>
+        <v>124372868</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10118,21 +10158,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496560</v>
+        <v>496485</v>
       </c>
       <c r="R84" t="n">
-        <v>7018917</v>
+        <v>7018881</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10162,24 +10197,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10190,31 +10215,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -6874,7 +6874,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124373142</v>
+        <v>124372778</v>
       </c>
       <c r="B56" t="n">
         <v>57635</v>
@@ -6913,21 +6913,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496560</v>
+        <v>496426</v>
       </c>
       <c r="R56" t="n">
-        <v>7018917</v>
+        <v>7018876</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6957,24 +6952,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>19:24</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6985,31 +6970,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7026,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372382</v>
+        <v>124372906</v>
       </c>
       <c r="B57" t="n">
         <v>57635</v>
@@ -7071,10 +7031,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496322</v>
+        <v>496496</v>
       </c>
       <c r="R57" t="n">
-        <v>7018864</v>
+        <v>7018887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7138,7 +7098,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372714</v>
+        <v>124372406</v>
       </c>
       <c r="B58" t="n">
         <v>57635</v>
@@ -7183,10 +7143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496416</v>
+        <v>496324</v>
       </c>
       <c r="R58" t="n">
-        <v>7018877</v>
+        <v>7018859</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7250,7 +7210,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372169</v>
+        <v>124372868</v>
       </c>
       <c r="B59" t="n">
         <v>57635</v>
@@ -7295,10 +7255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496446</v>
+        <v>496485</v>
       </c>
       <c r="R59" t="n">
-        <v>7018897</v>
+        <v>7018881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7362,7 +7322,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372234</v>
+        <v>124372810</v>
       </c>
       <c r="B60" t="n">
         <v>57635</v>
@@ -7407,10 +7367,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496384</v>
+        <v>496460</v>
       </c>
       <c r="R60" t="n">
-        <v>7018864</v>
+        <v>7018885</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7586,7 +7546,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124372406</v>
+        <v>124376085</v>
       </c>
       <c r="B62" t="n">
         <v>57635</v>
@@ -7631,10 +7591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496324</v>
+        <v>496204</v>
       </c>
       <c r="R62" t="n">
-        <v>7018859</v>
+        <v>7018992</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7698,7 +7658,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124372184</v>
+        <v>124373047</v>
       </c>
       <c r="B63" t="n">
         <v>57635</v>
@@ -7743,10 +7703,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496392</v>
+        <v>496551</v>
       </c>
       <c r="R63" t="n">
-        <v>7018873</v>
+        <v>7018894</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7810,7 +7770,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124373047</v>
+        <v>124372213</v>
       </c>
       <c r="B64" t="n">
         <v>57635</v>
@@ -7855,10 +7815,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496551</v>
+        <v>496392</v>
       </c>
       <c r="R64" t="n">
-        <v>7018894</v>
+        <v>7018866</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7922,7 +7882,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372778</v>
+        <v>124372949</v>
       </c>
       <c r="B65" t="n">
         <v>57635</v>
@@ -7967,10 +7927,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496426</v>
+        <v>496504</v>
       </c>
       <c r="R65" t="n">
-        <v>7018876</v>
+        <v>7018879</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8034,7 +7994,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124372353</v>
+        <v>124373102</v>
       </c>
       <c r="B66" t="n">
         <v>57635</v>
@@ -8079,10 +8039,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496338</v>
+        <v>496574</v>
       </c>
       <c r="R66" t="n">
-        <v>7018864</v>
+        <v>7018897</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8146,7 +8106,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124373030</v>
+        <v>124372291</v>
       </c>
       <c r="B67" t="n">
         <v>57635</v>
@@ -8182,7 +8142,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8191,10 +8151,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496538</v>
+        <v>496371</v>
       </c>
       <c r="R67" t="n">
-        <v>7018895</v>
+        <v>7018862</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8258,7 +8218,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372196</v>
+        <v>124372353</v>
       </c>
       <c r="B68" t="n">
         <v>57635</v>
@@ -8303,13 +8263,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496444</v>
+        <v>496338</v>
       </c>
       <c r="R68" t="n">
-        <v>7018877</v>
+        <v>7018864</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8336,24 +8296,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8364,31 +8314,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8405,7 +8330,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372891</v>
+        <v>124372234</v>
       </c>
       <c r="B69" t="n">
         <v>57635</v>
@@ -8450,10 +8375,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496487</v>
+        <v>496384</v>
       </c>
       <c r="R69" t="n">
-        <v>7018890</v>
+        <v>7018864</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8517,7 +8442,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372810</v>
+        <v>124372169</v>
       </c>
       <c r="B70" t="n">
         <v>57635</v>
@@ -8562,10 +8487,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496460</v>
+        <v>496446</v>
       </c>
       <c r="R70" t="n">
-        <v>7018885</v>
+        <v>7018897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8629,7 +8554,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124372460</v>
+        <v>124373030</v>
       </c>
       <c r="B71" t="n">
         <v>57635</v>
@@ -8674,10 +8599,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496311</v>
+        <v>496538</v>
       </c>
       <c r="R71" t="n">
-        <v>7018869</v>
+        <v>7018895</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8741,7 +8666,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124372906</v>
+        <v>124373122</v>
       </c>
       <c r="B72" t="n">
         <v>57635</v>
@@ -8786,10 +8711,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496496</v>
+        <v>496571</v>
       </c>
       <c r="R72" t="n">
-        <v>7018887</v>
+        <v>7018892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8853,7 +8778,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372343</v>
+        <v>124372184</v>
       </c>
       <c r="B73" t="n">
         <v>57635</v>
@@ -8898,10 +8823,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496345</v>
+        <v>496392</v>
       </c>
       <c r="R73" t="n">
-        <v>7018866</v>
+        <v>7018873</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8965,7 +8890,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372949</v>
+        <v>124372343</v>
       </c>
       <c r="B74" t="n">
         <v>57635</v>
@@ -9010,10 +8935,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496504</v>
+        <v>496345</v>
       </c>
       <c r="R74" t="n">
-        <v>7018879</v>
+        <v>7018866</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9077,7 +9002,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372986</v>
+        <v>124372196</v>
       </c>
       <c r="B75" t="n">
         <v>57635</v>
@@ -9122,13 +9047,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496526</v>
+        <v>496444</v>
       </c>
       <c r="R75" t="n">
-        <v>7018886</v>
+        <v>7018877</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9155,14 +9080,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9173,6 +9108,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9189,7 +9149,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124373122</v>
+        <v>124373142</v>
       </c>
       <c r="B76" t="n">
         <v>57635</v>
@@ -9228,16 +9188,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496571</v>
+        <v>496560</v>
       </c>
       <c r="R76" t="n">
-        <v>7018892</v>
+        <v>7018917</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9267,14 +9232,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9285,6 +9260,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9301,7 +9301,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124372291</v>
+        <v>124372826</v>
       </c>
       <c r="B77" t="n">
         <v>57635</v>
@@ -9337,7 +9337,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496371</v>
+        <v>496446</v>
       </c>
       <c r="R77" t="n">
-        <v>7018862</v>
+        <v>7018884</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9413,7 +9413,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124373102</v>
+        <v>124372891</v>
       </c>
       <c r="B78" t="n">
         <v>57635</v>
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496574</v>
+        <v>496487</v>
       </c>
       <c r="R78" t="n">
-        <v>7018897</v>
+        <v>7018890</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9525,14 +9525,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124372213</v>
+        <v>124366868</v>
       </c>
       <c r="B79" t="n">
         <v>57635</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9558,10 +9558,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9570,10 +9589,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496392</v>
+        <v>496023</v>
       </c>
       <c r="R79" t="n">
-        <v>7018866</v>
+        <v>7018919</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9603,14 +9622,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9621,6 +9650,11 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9637,7 +9671,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124372245</v>
+        <v>124372460</v>
       </c>
       <c r="B80" t="n">
         <v>57635</v>
@@ -9682,10 +9716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496380</v>
+        <v>496311</v>
       </c>
       <c r="R80" t="n">
-        <v>7018867</v>
+        <v>7018869</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9749,14 +9783,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124366868</v>
+        <v>124372245</v>
       </c>
       <c r="B81" t="n">
         <v>57635</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9782,29 +9816,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9813,10 +9828,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496023</v>
+        <v>496380</v>
       </c>
       <c r="R81" t="n">
-        <v>7018919</v>
+        <v>7018867</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9846,24 +9861,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9874,11 +9879,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9895,7 +9895,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124372826</v>
+        <v>124372382</v>
       </c>
       <c r="B82" t="n">
         <v>57635</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496446</v>
+        <v>496322</v>
       </c>
       <c r="R82" t="n">
-        <v>7018884</v>
+        <v>7018864</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124376085</v>
+        <v>124372986</v>
       </c>
       <c r="B83" t="n">
         <v>57635</v>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496204</v>
+        <v>496526</v>
       </c>
       <c r="R83" t="n">
-        <v>7018992</v>
+        <v>7018886</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124372868</v>
+        <v>124372714</v>
       </c>
       <c r="B84" t="n">
         <v>57635</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496485</v>
+        <v>496416</v>
       </c>
       <c r="R84" t="n">
-        <v>7018881</v>
+        <v>7018877</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -8890,7 +8890,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124372343</v>
+        <v>124373142</v>
       </c>
       <c r="B74" t="n">
         <v>57635</v>
@@ -8929,16 +8929,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496345</v>
+        <v>496560</v>
       </c>
       <c r="R74" t="n">
-        <v>7018866</v>
+        <v>7018917</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8968,14 +8973,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8986,6 +9001,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9002,7 +9042,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372196</v>
+        <v>124372343</v>
       </c>
       <c r="B75" t="n">
         <v>57635</v>
@@ -9047,13 +9087,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496444</v>
+        <v>496345</v>
       </c>
       <c r="R75" t="n">
-        <v>7018877</v>
+        <v>7018866</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9080,24 +9120,14 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>19:09</t>
-        </is>
-      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9108,31 +9138,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9149,7 +9154,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124373142</v>
+        <v>124372196</v>
       </c>
       <c r="B76" t="n">
         <v>57635</v>
@@ -9188,24 +9193,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496560</v>
+        <v>496444</v>
       </c>
       <c r="R76" t="n">
-        <v>7018917</v>
+        <v>7018877</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>

--- a/artfynd/A 15382-2025 artfynd.xlsx
+++ b/artfynd/A 15382-2025 artfynd.xlsx
@@ -6874,16 +6874,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124372778</v>
+        <v>124376085</v>
       </c>
       <c r="B56" t="n">
         <v>57635</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6919,10 +6914,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496426</v>
+        <v>496204</v>
       </c>
       <c r="R56" t="n">
-        <v>7018876</v>
+        <v>7018992</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6986,16 +6981,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124372906</v>
+        <v>124372868</v>
       </c>
       <c r="B57" t="n">
         <v>57635</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7031,10 +7021,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496496</v>
+        <v>496485</v>
       </c>
       <c r="R57" t="n">
-        <v>7018887</v>
+        <v>7018881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7098,16 +7088,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124372406</v>
+        <v>124372213</v>
       </c>
       <c r="B58" t="n">
         <v>57635</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7143,10 +7128,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496324</v>
+        <v>496392</v>
       </c>
       <c r="R58" t="n">
-        <v>7018859</v>
+        <v>7018866</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7210,16 +7195,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124372868</v>
+        <v>124372986</v>
       </c>
       <c r="B59" t="n">
         <v>57635</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7255,10 +7235,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>496485</v>
+        <v>496526</v>
       </c>
       <c r="R59" t="n">
-        <v>7018881</v>
+        <v>7018886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7322,16 +7302,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124372810</v>
+        <v>124372169</v>
       </c>
       <c r="B60" t="n">
         <v>57635</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7367,10 +7342,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>496460</v>
+        <v>496446</v>
       </c>
       <c r="R60" t="n">
-        <v>7018885</v>
+        <v>7018897</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7434,16 +7409,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124373091</v>
+        <v>124372406</v>
       </c>
       <c r="B61" t="n">
         <v>57635</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7479,10 +7449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496553</v>
+        <v>496324</v>
       </c>
       <c r="R61" t="n">
-        <v>7018888</v>
+        <v>7018859</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7546,16 +7516,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376085</v>
+        <v>124372245</v>
       </c>
       <c r="B62" t="n">
         <v>57635</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7591,10 +7556,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496204</v>
+        <v>496380</v>
       </c>
       <c r="R62" t="n">
-        <v>7018992</v>
+        <v>7018867</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7658,16 +7623,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124373047</v>
+        <v>124372906</v>
       </c>
       <c r="B63" t="n">
         <v>57635</v>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7703,10 +7663,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496551</v>
+        <v>496496</v>
       </c>
       <c r="R63" t="n">
-        <v>7018894</v>
+        <v>7018887</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7770,16 +7730,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124372213</v>
+        <v>124372778</v>
       </c>
       <c r="B64" t="n">
         <v>57635</v>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7815,10 +7770,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496392</v>
+        <v>496426</v>
       </c>
       <c r="R64" t="n">
-        <v>7018866</v>
+        <v>7018876</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7882,16 +7837,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124372949</v>
+        <v>124372353</v>
       </c>
       <c r="B65" t="n">
         <v>57635</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>NT</t>
@@ -7927,10 +7877,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496504</v>
+        <v>496338</v>
       </c>
       <c r="R65" t="n">
-        <v>7018879</v>
+        <v>7018864</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7994,16 +7944,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124373102</v>
+        <v>124373091</v>
       </c>
       <c r="B66" t="n">
         <v>57635</v>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8039,10 +7984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496574</v>
+        <v>496553</v>
       </c>
       <c r="R66" t="n">
-        <v>7018897</v>
+        <v>7018888</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8106,16 +8051,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124372291</v>
+        <v>124372184</v>
       </c>
       <c r="B67" t="n">
         <v>57635</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8142,7 +8082,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8151,10 +8091,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496371</v>
+        <v>496392</v>
       </c>
       <c r="R67" t="n">
-        <v>7018862</v>
+        <v>7018873</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8218,16 +8158,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124372353</v>
+        <v>124372891</v>
       </c>
       <c r="B68" t="n">
         <v>57635</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8263,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496338</v>
+        <v>496487</v>
       </c>
       <c r="R68" t="n">
-        <v>7018864</v>
+        <v>7018890</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8330,16 +8265,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124372234</v>
+        <v>124373102</v>
       </c>
       <c r="B69" t="n">
         <v>57635</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8375,10 +8305,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496384</v>
+        <v>496574</v>
       </c>
       <c r="R69" t="n">
-        <v>7018864</v>
+        <v>7018897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8442,16 +8372,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124372169</v>
+        <v>124373142</v>
       </c>
       <c r="B70" t="n">
         <v>57635</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8481,16 +8406,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blekmyren, Blekmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496446</v>
+        <v>496560</v>
       </c>
       <c r="R70" t="n">
-        <v>7018897</v>
+        <v>7018917</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8520,14 +8450,24 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8538,6 +8478,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8554,16 +8519,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124373030</v>
+        <v>124372343</v>
       </c>
       <c r="B71" t="n">
         <v>57635</v>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8599,10 +8559,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496538</v>
+        <v>496345</v>
       </c>
       <c r="R71" t="n">
-        <v>7018895</v>
+        <v>7018866</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8666,16 +8626,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124373122</v>
+        <v>124372234</v>
       </c>
       <c r="B72" t="n">
         <v>57635</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8711,10 +8666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496571</v>
+        <v>496384</v>
       </c>
       <c r="R72" t="n">
-        <v>7018892</v>
+        <v>7018864</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8778,16 +8733,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124372184</v>
+        <v>124372810</v>
       </c>
       <c r="B73" t="n">
         <v>57635</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8823,10 +8773,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496392</v>
+        <v>496460</v>
       </c>
       <c r="R73" t="n">
-        <v>7018873</v>
+        <v>7018885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8890,16 +8840,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124373142</v>
+        <v>124366868</v>
       </c>
       <c r="B74" t="n">
         <v>57635</v>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>NT</t>
@@ -8923,10 +8868,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8940,10 +8899,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496560</v>
+        <v>496023</v>
       </c>
       <c r="R74" t="n">
-        <v>7018917</v>
+        <v>7018919</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8975,7 +8934,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8985,12 +8944,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran i gammal granskog med mycket högt livsmiljövärde för tretåig hackspett. På fyndplatsen finns minst 20 st stående döda granar med full längd där många av de döda stammarna har minst 20 cm i brösthöjdsdiameter.</t>
+          <t>Hona som sågs födosöka på en stående döende gran med toppbrott. På fyndplatsen finns mycket högt livsmiljövärde för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9005,26 +8964,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9042,16 +8981,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124372343</v>
+        <v>124372196</v>
       </c>
       <c r="B75" t="n">
         <v>57635</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>NT</t>
@@ -9087,13 +9021,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-      